--- a/STX.xlsx
+++ b/STX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93374C7B-969A-4F47-9999-C3C8756CF3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BC896A-3A51-B248-A27D-9FDA859464A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="429">
   <si>
     <t>Ticker</t>
   </si>
@@ -1424,6 +1424,39 @@
   </si>
   <si>
     <t>Edge &amp; IoT</t>
+  </si>
+  <si>
+    <t>Kioxia Holdings</t>
+  </si>
+  <si>
+    <t>Micron</t>
+  </si>
+  <si>
+    <t>Samsung Electronics</t>
+  </si>
+  <si>
+    <t>Sandisk</t>
+  </si>
+  <si>
+    <t>SK Hynix</t>
+  </si>
+  <si>
+    <t>Western Digital</t>
+  </si>
+  <si>
+    <t>Toshiba Corporation</t>
+  </si>
+  <si>
+    <t>Datacenter represents high capacity nearline products sold to clouds and enterprise customers</t>
+  </si>
+  <si>
+    <t>Edge &amp; IoT includes consumer and client markets</t>
+  </si>
+  <si>
+    <t>Erns &amp; young</t>
+  </si>
+  <si>
+    <t>Enable enterprises and end-users to confidently store and unlock value of their data</t>
   </si>
 </sst>
 </file>
@@ -2352,6 +2385,9 @@
     <xf numFmtId="37" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="171" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2361,15 +2397,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2377,6 +2404,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13439,7 +13472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I71"/>
+  <dimension ref="B1:I74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -13456,18 +13489,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="243" t="s">
+      <c r="B2" s="244" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="244"/>
-      <c r="E2" s="243" t="s">
+      <c r="C2" s="245"/>
+      <c r="E2" s="244" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="244"/>
-      <c r="H2" s="243" t="s">
+      <c r="F2" s="245"/>
+      <c r="H2" s="244" t="s">
         <v>332</v>
       </c>
-      <c r="I2" s="244"/>
+      <c r="I2" s="245"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13735,10 +13768,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="245" t="s">
+      <c r="B17" s="246" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="245"/>
+      <c r="C17" s="246"/>
       <c r="E17" s="184" t="s">
         <v>300</v>
       </c>
@@ -13811,14 +13844,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="245" t="s">
+      <c r="B25" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="245"/>
-      <c r="E25" s="243" t="s">
+      <c r="C25" s="246"/>
+      <c r="E25" s="244" t="s">
         <v>345</v>
       </c>
-      <c r="F25" s="244"/>
+      <c r="F25" s="245"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -13867,120 +13900,144 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="246" t="s">
+      <c r="B33" s="243" t="s">
         <v>340</v>
       </c>
-      <c r="C33" s="246"/>
-      <c r="D33" s="246"/>
-      <c r="E33" s="246"/>
-      <c r="F33" s="246"/>
-      <c r="G33" s="246"/>
-      <c r="H33" s="246"/>
+      <c r="C33" s="243"/>
+      <c r="D33" s="243"/>
+      <c r="E33" s="243"/>
+      <c r="F33" s="243"/>
+      <c r="G33" s="243"/>
+      <c r="H33" s="243"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
         <v>341</v>
       </c>
+      <c r="C35" s="1" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="16" t="s">
         <v>342</v>
       </c>
+      <c r="C36" s="1" t="s">
+        <v>427</v>
+      </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="16" t="s">
         <v>407</v>
       </c>
+      <c r="C37" s="1" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="16"/>
+      <c r="C38" s="1" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B39" s="16"/>
+      <c r="B39" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B40" s="16" t="s">
-        <v>408</v>
+      <c r="B40" s="16"/>
+      <c r="C40" s="1" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="16"/>
+      <c r="C41" s="1" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="16"/>
+      <c r="C42" s="1" t="s">
+        <v>421</v>
+      </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="16"/>
+      <c r="C43" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B44" s="16"/>
+      <c r="C44" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B45" s="16"/>
+      <c r="C45" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B46" s="16" t="s">
         <v>409</v>
       </c>
-      <c r="C43" s="90"/>
-    </row>
-    <row r="46" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="246"/>
-      <c r="C46" s="246"/>
-      <c r="D46" s="246"/>
-      <c r="E46" s="246"/>
-      <c r="F46" s="246"/>
-      <c r="G46" s="246"/>
-      <c r="H46" s="246"/>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="246" t="s">
+      <c r="C46" s="90">
+        <v>3273</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="243"/>
+      <c r="C49" s="243"/>
+      <c r="D49" s="243"/>
+      <c r="E49" s="243"/>
+      <c r="F49" s="243"/>
+      <c r="G49" s="243"/>
+      <c r="H49" s="243"/>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B52" s="243" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="246"/>
-      <c r="D49" s="246"/>
-      <c r="E49" s="246"/>
-      <c r="F49" s="246"/>
-      <c r="G49" s="246"/>
-      <c r="H49" s="246"/>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B51" s="41" t="s">
+      <c r="C52" s="243"/>
+      <c r="D52" s="243"/>
+      <c r="E52" s="243"/>
+      <c r="F52" s="243"/>
+      <c r="G52" s="243"/>
+      <c r="H52" s="243"/>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B54" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="C51" s="41" t="s">
+      <c r="C54" s="41" t="s">
         <v>396</v>
       </c>
-      <c r="D51" s="41"/>
-      <c r="E51" s="41" t="s">
+      <c r="D54" s="41"/>
+      <c r="E54" s="41" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B55" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B53" s="1" t="s">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C56" s="1" t="s">
         <v>405</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B54" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B56" s="41" t="s">
-        <v>344</v>
-      </c>
-      <c r="C56" s="41" t="s">
-        <v>396</v>
-      </c>
-      <c r="D56" s="41"/>
-      <c r="E56" s="41" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
@@ -13988,64 +14045,84 @@
         <v>398</v>
       </c>
       <c r="C57" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B59" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="C59" s="41" t="s">
+        <v>396</v>
+      </c>
+      <c r="D59" s="41"/>
+      <c r="E59" s="41" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B60" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="61" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="246"/>
-      <c r="C61" s="246"/>
-      <c r="D61" s="246"/>
-      <c r="E61" s="246"/>
-      <c r="F61" s="246"/>
-      <c r="G61" s="246"/>
-      <c r="H61" s="246"/>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B64" s="246" t="s">
+    <row r="64" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="243"/>
+      <c r="C64" s="243"/>
+      <c r="D64" s="243"/>
+      <c r="E64" s="243"/>
+      <c r="F64" s="243"/>
+      <c r="G64" s="243"/>
+      <c r="H64" s="243"/>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B67" s="243" t="s">
         <v>108</v>
       </c>
-      <c r="C64" s="246"/>
-      <c r="D64" s="246"/>
-      <c r="E64" s="246"/>
-      <c r="F64" s="246"/>
-      <c r="G64" s="246"/>
-      <c r="H64" s="246"/>
-    </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B66" s="41" t="s">
+      <c r="C67" s="243"/>
+      <c r="D67" s="243"/>
+      <c r="E67" s="243"/>
+      <c r="F67" s="243"/>
+      <c r="G67" s="243"/>
+      <c r="H67" s="243"/>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B69" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="C66" s="41" t="s">
+      <c r="C69" s="41" t="s">
         <v>364</v>
       </c>
-      <c r="D66" s="41"/>
-      <c r="E66" s="41" t="s">
+      <c r="D69" s="41"/>
+      <c r="E69" s="41" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="71" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="246"/>
-      <c r="C71" s="246"/>
-      <c r="D71" s="246"/>
-      <c r="E71" s="246"/>
-      <c r="F71" s="246"/>
-      <c r="G71" s="246"/>
-      <c r="H71" s="246"/>
+    <row r="74" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="243"/>
+      <c r="C74" s="243"/>
+      <c r="D74" s="243"/>
+      <c r="E74" s="243"/>
+      <c r="F74" s="243"/>
+      <c r="G74" s="243"/>
+      <c r="H74" s="243"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B64:H64"/>
-    <mergeCell ref="B71:H71"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B61:H61"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B67:H67"/>
+    <mergeCell ref="B74:H74"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B64:H64"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14115,36 +14192,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="255"/>
       <c r="H2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="246" t="s">
+      <c r="S2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="246"/>
-      <c r="U2" s="246"/>
-      <c r="V2" s="246"/>
-      <c r="W2" s="246"/>
-      <c r="X2" s="246"/>
-      <c r="Y2" s="246"/>
-      <c r="Z2" s="246"/>
-      <c r="AA2" s="246" t="s">
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
+      <c r="AA2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="246"/>
-      <c r="AC2" s="246"/>
+      <c r="AB2" s="243"/>
+      <c r="AC2" s="243"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -15647,35 +15724,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="255"/>
       <c r="H2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
-      <c r="P2" s="246" t="s">
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="P2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="246"/>
-      <c r="R2" s="246"/>
-      <c r="S2" s="246"/>
-      <c r="T2" s="246"/>
-      <c r="U2" s="246"/>
-      <c r="V2" s="246"/>
-      <c r="W2" s="246"/>
-      <c r="X2" s="246" t="s">
+      <c r="Q2" s="243"/>
+      <c r="R2" s="243"/>
+      <c r="S2" s="243"/>
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="246"/>
-      <c r="Z2" s="246"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -16907,20 +16984,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="E3" s="246"/>
-      <c r="F3" s="246"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
       <c r="G3" s="255"/>
       <c r="H3" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="246"/>
-      <c r="J3" s="246"/>
-      <c r="K3" s="246"/>
-      <c r="L3" s="246"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="257"/>
       <c r="Q3" s="257"/>
       <c r="R3" s="257"/>
@@ -18313,12 +18390,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18326,6 +18397,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18363,20 +18440,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="255"/>
       <c r="H2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
       <c r="S2" s="257"/>
       <c r="T2" s="257"/>
       <c r="U2" s="257"/>
@@ -19385,16 +19462,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19457,10 +19534,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="246" t="s">
+      <c r="B4" s="243" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="246"/>
+      <c r="C4" s="243"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19545,10 +19622,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="246" t="s">
+      <c r="B15" s="243" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="246"/>
+      <c r="C15" s="243"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19637,20 +19714,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="E3" s="246"/>
-      <c r="F3" s="246"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
       <c r="G3" s="255"/>
       <c r="H3" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="246"/>
-      <c r="J3" s="246"/>
-      <c r="K3" s="246"/>
-      <c r="L3" s="246"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="257"/>
       <c r="Q3" s="257"/>
       <c r="R3" s="257"/>
@@ -19936,10 +20013,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="246" t="s">
+      <c r="B13" s="243" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="246"/>
+      <c r="C13" s="243"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19959,10 +20036,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="246" t="s">
+      <c r="B18" s="243" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="246"/>
+      <c r="C18" s="243"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20076,20 +20153,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="255"/>
       <c r="H2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21021,10 +21098,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="246" t="s">
+      <c r="B37" s="243" t="s">
         <v>204</v>
       </c>
-      <c r="C37" s="246"/>
+      <c r="C37" s="243"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21117,10 +21194,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="246" t="s">
+      <c r="B49" s="243" t="s">
         <v>209</v>
       </c>
-      <c r="C49" s="246"/>
+      <c r="C49" s="243"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21176,10 +21253,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="246" t="s">
+      <c r="B57" s="243" t="s">
         <v>326</v>
       </c>
-      <c r="C57" s="246"/>
+      <c r="C57" s="243"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21319,10 +21396,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="246" t="s">
+      <c r="B4" s="243" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="246"/>
+      <c r="C4" s="243"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21441,20 +21518,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="255"/>
       <c r="H2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21817,10 +21894,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="246" t="s">
+      <c r="B20" s="243" t="s">
         <v>377</v>
       </c>
-      <c r="C20" s="246"/>
+      <c r="C20" s="243"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -21921,20 +21998,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="E3" s="246"/>
-      <c r="F3" s="246"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
       <c r="G3" s="255"/>
       <c r="H3" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="246"/>
-      <c r="J3" s="246"/>
-      <c r="K3" s="246"/>
-      <c r="L3" s="246"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="257"/>
       <c r="Q3" s="257"/>
       <c r="R3" s="257"/>
@@ -22833,17 +22910,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32313,94 +32390,61 @@
       <c r="K190" s="81"/>
       <c r="L190" s="81"/>
       <c r="M190" s="81">
-        <f>IF(L185=0,
+        <f t="shared" ref="M190:Q191" si="107">IF(L185=0,
 IF(M185=0,0,IF(M185&gt;0,1,-1)),
 (M185-L185)/ABS(L185)
 )</f>
         <v>0</v>
       </c>
       <c r="N190" s="81">
-        <f>IF(M185=0,
-IF(N185=0,0,IF(N185&gt;0,1,-1)),
-(N185-M185)/ABS(M185)
-)</f>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="O190" s="81">
-        <f>IF(N185=0,
-IF(O185=0,0,IF(O185&gt;0,1,-1)),
-(O185-N185)/ABS(N185)
-)</f>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="P190" s="81">
-        <f>IF(O185=0,
-IF(P185=0,0,IF(P185&gt;0,1,-1)),
-(P185-O185)/ABS(O185)
-)</f>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="Q190" s="81">
-        <f>IF(P185=0,
-IF(Q185=0,0,IF(Q185&gt;0,1,-1)),
-(Q185-P185)/ABS(P185)
-)</f>
+        <f t="shared" si="107"/>
         <v>1</v>
       </c>
       <c r="T190" s="81">
-        <f>IF(S185=0,
+        <f t="shared" ref="T190:AA191" si="108">IF(S185=0,
 IF(T185=0,0,IF(T185&gt;0,1,-1)),
 (T185-S185)/ABS(S185)
 )</f>
         <v>0</v>
       </c>
       <c r="U190" s="81">
-        <f>IF(T185=0,
-IF(U185=0,0,IF(U185&gt;0,1,-1)),
-(U185-T185)/ABS(T185)
-)</f>
+        <f t="shared" si="108"/>
         <v>1</v>
       </c>
       <c r="V190" s="81">
-        <f>IF(U185=0,
-IF(V185=0,0,IF(V185&gt;0,1,-1)),
-(V185-U185)/ABS(U185)
-)</f>
+        <f t="shared" si="108"/>
         <v>9.7345132743362831E-2</v>
       </c>
       <c r="W190" s="81">
-        <f>IF(V185=0,
-IF(W185=0,0,IF(W185&gt;0,1,-1)),
-(W185-V185)/ABS(V185)
-)</f>
+        <f t="shared" si="108"/>
         <v>-6.9700460829493091E-2</v>
       </c>
       <c r="X190" s="81">
-        <f>IF(W185=0,
-IF(X185=0,0,IF(X185&gt;0,1,-1)),
-(X185-W185)/ABS(W185)
-)</f>
+        <f t="shared" si="108"/>
         <v>0.15356037151702787</v>
       </c>
       <c r="Y190" s="81">
-        <f>IF(X185=0,
-IF(Y185=0,0,IF(Y185&gt;0,1,-1)),
-(Y185-X185)/ABS(X185)
-)</f>
+        <f t="shared" si="108"/>
         <v>0.13472893183038109</v>
       </c>
       <c r="Z190" s="81">
-        <f>IF(Y185=0,
-IF(Z185=0,0,IF(Z185&gt;0,1,-1)),
-(Z185-Y185)/ABS(Y185)
-)</f>
+        <f t="shared" si="108"/>
         <v>5.2034058656575212E-2</v>
       </c>
       <c r="AA190" s="81">
-        <f>IF(Z185=0,
-IF(AA185=0,0,IF(AA185&gt;0,1,-1)),
-(AA185-Z185)/ABS(Z185)
-)</f>
+        <f t="shared" si="108"/>
         <v>0.12410071942446044</v>
       </c>
       <c r="AC190" s="49"/>
@@ -32411,94 +32455,55 @@
         <v>Edge &amp; IoT</v>
       </c>
       <c r="M191" s="81">
-        <f>IF(L186=0,
-IF(M186=0,0,IF(M186&gt;0,1,-1)),
-(M186-L186)/ABS(L186)
-)</f>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="N191" s="81">
-        <f>IF(M186=0,
-IF(N186=0,0,IF(N186&gt;0,1,-1)),
-(N186-M186)/ABS(M186)
-)</f>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="O191" s="81">
-        <f>IF(N186=0,
-IF(O186=0,0,IF(O186&gt;0,1,-1)),
-(O186-N186)/ABS(N186)
-)</f>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="P191" s="81">
-        <f>IF(O186=0,
-IF(P186=0,0,IF(P186&gt;0,1,-1)),
-(P186-O186)/ABS(O186)
-)</f>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="Q191" s="81">
-        <f>IF(P186=0,
-IF(Q186=0,0,IF(Q186&gt;0,1,-1)),
-(Q186-P186)/ABS(P186)
-)</f>
+        <f t="shared" si="107"/>
         <v>1</v>
       </c>
       <c r="T191" s="81">
-        <f>IF(S186=0,
-IF(T186=0,0,IF(T186&gt;0,1,-1)),
-(T186-S186)/ABS(S186)
-)</f>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="U191" s="81">
-        <f>IF(T186=0,
-IF(U186=0,0,IF(U186&gt;0,1,-1)),
-(U186-T186)/ABS(T186)
-)</f>
+        <f t="shared" si="108"/>
         <v>1</v>
       </c>
       <c r="V191" s="81">
-        <f>IF(U186=0,
-IF(V186=0,0,IF(V186&gt;0,1,-1)),
-(V186-U186)/ABS(U186)
-)</f>
+        <f t="shared" si="108"/>
         <v>6.8376068376068376E-3</v>
       </c>
       <c r="W191" s="81">
-        <f>IF(V186=0,
-IF(W186=0,0,IF(W186&gt;0,1,-1)),
-(W186-V186)/ABS(V186)
-)</f>
+        <f t="shared" si="108"/>
         <v>-7.4702886247877756E-2</v>
       </c>
       <c r="X191" s="81">
-        <f>IF(W186=0,
-IF(X186=0,0,IF(X186&gt;0,1,-1)),
-(X186-W186)/ABS(W186)
-)</f>
+        <f t="shared" si="108"/>
         <v>6.6055045871559637E-2</v>
       </c>
       <c r="Y191" s="81">
-        <f>IF(X186=0,
-IF(Y186=0,0,IF(Y186&gt;0,1,-1)),
-(Y186-X186)/ABS(X186)
-)</f>
+        <f t="shared" si="108"/>
         <v>-0.11359724612736662</v>
       </c>
       <c r="Z191" s="81">
-        <f>IF(Y186=0,
-IF(Z186=0,0,IF(Z186&gt;0,1,-1)),
-(Z186-Y186)/ABS(Y186)
-)</f>
+        <f t="shared" si="108"/>
         <v>0.16699029126213591</v>
       </c>
       <c r="AA191" s="81">
-        <f>IF(Z186=0,
-IF(AA186=0,0,IF(AA186&gt;0,1,-1)),
-(AA186-Z186)/ABS(Z186)
-)</f>
+        <f t="shared" si="108"/>
         <v>1.8302828618968387E-2</v>
       </c>
       <c r="AC191" s="49"/>
@@ -32851,7 +32856,7 @@
         <v>175.4</v>
       </c>
       <c r="AC206" s="62">
-        <f t="shared" ref="AC206:AC207" si="107">SUM(X206:AA206)</f>
+        <f t="shared" ref="AC206:AC207" si="109">SUM(X206:AA206)</f>
         <v>636.4</v>
       </c>
     </row>
@@ -32909,7 +32914,7 @@
         <v>24</v>
       </c>
       <c r="AC207" s="62">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>97</v>
       </c>
     </row>
@@ -32955,19 +32960,19 @@
       <c r="K209" s="62"/>
       <c r="L209" s="62"/>
       <c r="M209" s="63" t="e">
-        <f t="shared" ref="M209:Q209" si="108">M185/M206</f>
+        <f t="shared" ref="M209:P209" si="110">M185/M206</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N209" s="63" t="e">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O209" s="63" t="e">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P209" s="63" t="e">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q209" s="63">
@@ -32975,39 +32980,39 @@
         <v>13.685058397100281</v>
       </c>
       <c r="T209" s="63">
-        <f t="shared" ref="T209:AC209" si="109">T185/T206</f>
+        <f t="shared" ref="T209:AC209" si="111">T185/T206</f>
         <v>0</v>
       </c>
       <c r="U209" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>13.87719298245614</v>
       </c>
       <c r="V209" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>13.777777777777779</v>
       </c>
       <c r="W209" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>13.503344481605351</v>
       </c>
       <c r="X209" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>13.598540145985401</v>
       </c>
       <c r="Y209" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>13.29559748427673</v>
       </c>
       <c r="Z209" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>13.478787878787879</v>
       </c>
       <c r="AA209" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>14.253135689851767</v>
       </c>
       <c r="AC209" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>13.672218730358265</v>
       </c>
     </row>
@@ -33092,15 +33097,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="246" t="s">
+      <c r="B4" s="243" t="s">
         <v>237</v>
       </c>
-      <c r="C4" s="246"/>
-      <c r="E4" s="246" t="s">
+      <c r="C4" s="243"/>
+      <c r="E4" s="243" t="s">
         <v>244</v>
       </c>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33237,14 +33242,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="246" t="s">
+      <c r="B15" s="243" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="246"/>
-      <c r="E15" s="246" t="s">
+      <c r="C15" s="243"/>
+      <c r="E15" s="243" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="246"/>
+      <c r="F15" s="243"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33295,14 +33300,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="246" t="s">
+      <c r="B21" s="243" t="s">
         <v>249</v>
       </c>
-      <c r="C21" s="246"/>
-      <c r="E21" s="246" t="s">
+      <c r="C21" s="243"/>
+      <c r="E21" s="243" t="s">
         <v>253</v>
       </c>
-      <c r="F21" s="246"/>
+      <c r="F21" s="243"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33371,14 +33376,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="246" t="s">
+      <c r="B29" s="243" t="s">
         <v>254</v>
       </c>
-      <c r="C29" s="246"/>
-      <c r="E29" s="246" t="s">
+      <c r="C29" s="243"/>
+      <c r="E29" s="243" t="s">
         <v>260</v>
       </c>
-      <c r="F29" s="246"/>
+      <c r="F29" s="243"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33454,14 +33459,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="246" t="s">
+      <c r="B37" s="243" t="s">
         <v>272</v>
       </c>
-      <c r="C37" s="246"/>
-      <c r="E37" s="246" t="s">
+      <c r="C37" s="243"/>
+      <c r="E37" s="243" t="s">
         <v>275</v>
       </c>
-      <c r="F37" s="246"/>
+      <c r="F37" s="243"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33530,14 +33535,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="246" t="s">
+      <c r="B45" s="243" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="246"/>
-      <c r="E45" s="246" t="s">
+      <c r="C45" s="243"/>
+      <c r="E45" s="243" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="246"/>
+      <c r="F45" s="243"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33574,14 +33579,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="246" t="s">
+      <c r="B51" s="243" t="s">
         <v>286</v>
       </c>
-      <c r="C51" s="246"/>
-      <c r="E51" s="246" t="s">
+      <c r="C51" s="243"/>
+      <c r="E51" s="243" t="s">
         <v>307</v>
       </c>
-      <c r="F51" s="246"/>
+      <c r="F51" s="243"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35539,14 +35544,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="247" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="250"/>
-      <c r="F3" s="251" t="s">
+      <c r="D3" s="248"/>
+      <c r="F3" s="249" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="250"/>
+      <c r="G3" s="248"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35613,19 +35618,19 @@
       <c r="B7" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="247">
+      <c r="C7" s="250">
         <f>Statement!AA88</f>
         <v>0.10159292035398231</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="F7" s="247">
+      <c r="D7" s="251"/>
+      <c r="F7" s="250">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.44074074074074077</v>
       </c>
-      <c r="G7" s="248"/>
+      <c r="G7" s="251"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -35652,19 +35657,19 @@
       <c r="B9" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="247">
+      <c r="C9" s="250">
         <f>Statement!AA89</f>
         <v>9.7028502122498486E-3</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="F9" s="247">
+      <c r="D9" s="251"/>
+      <c r="F9" s="250">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.18928571428571428</v>
       </c>
-      <c r="G9" s="248"/>
+      <c r="G9" s="251"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -35691,19 +35696,19 @@
       <c r="B11" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="247">
+      <c r="C11" s="250">
         <f>Statement!AA90</f>
         <v>0.23044217687074831</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="F11" s="247">
+      <c r="D11" s="251"/>
+      <c r="F11" s="250">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.90394736842105261</v>
       </c>
-      <c r="G11" s="248"/>
+      <c r="G11" s="251"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -35730,19 +35735,19 @@
       <c r="B13" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="247">
+      <c r="C13" s="250">
         <f>Statement!AA93</f>
         <v>0.34834834834834832</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="F13" s="247">
+      <c r="D13" s="251"/>
+      <c r="F13" s="250">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.36474164133738601</v>
       </c>
-      <c r="G13" s="248"/>
+      <c r="G13" s="251"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -35769,19 +35774,19 @@
       <c r="B15" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="247">
+      <c r="C15" s="250">
         <f>Statement!AA94</f>
         <v>0.18386714116251482</v>
       </c>
-      <c r="D15" s="248"/>
-      <c r="F15" s="247">
+      <c r="D15" s="251"/>
+      <c r="F15" s="250">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.3155452436194897</v>
       </c>
-      <c r="G15" s="248"/>
+      <c r="G15" s="251"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -35808,19 +35813,19 @@
       <c r="B17" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="247">
+      <c r="C17" s="250">
         <f>Statement!AA96</f>
         <v>0.26138279932546377</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="F17" s="247">
+      <c r="D17" s="251"/>
+      <c r="F17" s="250">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2</v>
       </c>
-      <c r="G17" s="248"/>
+      <c r="G17" s="251"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -35847,22 +35852,22 @@
       <c r="B19" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="247">
+      <c r="C19" s="250">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.3859649122807015E-3</v>
       </c>
-      <c r="D19" s="248"/>
-      <c r="F19" s="247">
+      <c r="D19" s="251"/>
+      <c r="F19" s="250">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>6.0185185185185182E-2</v>
       </c>
-      <c r="G19" s="248"/>
+      <c r="G19" s="251"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -35889,22 +35894,22 @@
       <c r="B21" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="247">
+      <c r="C21" s="250">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.25769230769230766</v>
       </c>
-      <c r="D21" s="248"/>
-      <c r="F21" s="247">
+      <c r="D21" s="251"/>
+      <c r="F21" s="250">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.0828025477707006</v>
       </c>
-      <c r="G21" s="248"/>
+      <c r="G21" s="251"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35953,22 +35958,22 @@
       <c r="B25" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="247">
+      <c r="C25" s="250">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.12410071942446044</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="F25" s="247">
+      <c r="D25" s="251"/>
+      <c r="F25" s="250">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.54798761609907121</v>
       </c>
-      <c r="G25" s="248"/>
+      <c r="G25" s="251"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -35996,47 +36001,47 @@
       <c r="B27" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="247">
+      <c r="C27" s="250">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>1.8302828618968387E-2</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="F27" s="247">
+      <c r="D27" s="251"/>
+      <c r="F27" s="250">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.12293577981651377</v>
       </c>
-      <c r="G27" s="248"/>
+      <c r="G27" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dumitrasadrian/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BC896A-3A51-B248-A27D-9FDA859464A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6490C790-E03F-D04B-A0C7-ABF7C6A758C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="400" windowWidth="20480" windowHeight="12860" firstSheet="13" activeTab="20" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="426">
   <si>
     <t>Ticker</t>
   </si>
@@ -1360,18 +1360,9 @@
     <t>Opex</t>
   </si>
   <si>
-    <t>23.07.2025</t>
-  </si>
-  <si>
-    <t>FY 2025</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Revenue data for FY 2025, 2024 and 2023 now reflects only the HDD business without Sandisk</t>
-  </si>
-  <si>
     <t>Exabytes</t>
   </si>
   <si>
@@ -1384,15 +1375,6 @@
     <t>Price per Exabyte</t>
   </si>
   <si>
-    <t>Q4 gross margin will be 51%-52%</t>
-  </si>
-  <si>
-    <t>Q4 OpEx will be 385M-395M</t>
-  </si>
-  <si>
-    <t>Q4 diluted avg shares will be 385M</t>
-  </si>
-  <si>
     <t>Business units:</t>
   </si>
   <si>
@@ -1402,12 +1384,6 @@
     <t>Patents:</t>
   </si>
   <si>
-    <t>Client Growth Rate</t>
-  </si>
-  <si>
-    <t>Consumer Growth Rate</t>
-  </si>
-  <si>
     <t>Nearline exabytes * price per exabyte</t>
   </si>
   <si>
@@ -1457,6 +1433,21 @@
   </si>
   <si>
     <t>Enable enterprises and end-users to confidently store and unlock value of their data</t>
+  </si>
+  <si>
+    <t>Q4 operating margin will be 40%-44%</t>
+  </si>
+  <si>
+    <t>Q4 OpEx will be about 295M</t>
+  </si>
+  <si>
+    <t>Q4 diluted avg shares will be 231M</t>
+  </si>
+  <si>
+    <t>27.04.2026</t>
+  </si>
+  <si>
+    <t>Edge &amp; IoT Growth Rate</t>
   </si>
 </sst>
 </file>
@@ -1464,15 +1455,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
-    <numFmt numFmtId="167" formatCode="0.00_);\(0.00\)"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.0_);\(0.0\)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
+    <numFmt numFmtId="168" formatCode="0.00_);\(0.00\)"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0_);\(#,##0.0\)"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="172" formatCode="0.0_);\(0.0\)"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -2064,7 +2055,7 @@
   <cellXfs count="261">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2102,10 +2093,10 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="38" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2116,9 +2107,9 @@
     <xf numFmtId="38" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="7" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -2133,7 +2124,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2141,10 +2132,10 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="8" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2153,15 +2144,15 @@
     </xf>
     <xf numFmtId="37" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="7" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="7" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="10" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2193,16 +2184,16 @@
     <xf numFmtId="37" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="18" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="18" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="19" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="20" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="20" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="20" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="20" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="38" fontId="21" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="21" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2220,14 +2211,14 @@
     <xf numFmtId="37" fontId="19" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="21" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="19" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="37" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="18" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="18" fillId="12" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="18" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="18" fillId="12" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="37" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="7" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2248,11 +2239,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -2260,9 +2251,9 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2273,7 +2264,7 @@
     <xf numFmtId="37" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2283,21 +2274,21 @@
     <xf numFmtId="2" fontId="10" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="7" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2306,13 +2297,13 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="17" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="17" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="18" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -2341,9 +2332,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="17" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="10" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="10" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
@@ -2379,15 +2370,12 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="37" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2397,6 +2385,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2404,12 +2401,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2442,7 +2433,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -2482,7 +2473,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2976,7 +2967,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3271,7 +3262,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3620,7 +3611,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4054,7 +4045,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4470,7 +4461,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4894,7 +4885,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5256,7 +5247,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5707,7 +5698,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6158,7 +6149,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12625,10 +12616,10 @@
     <v>1145</v>
     <v>138.30000000000001</v>
     <v>2.0962000000000001</v>
-    <v>-61.67</v>
-    <v>-6.7519999999999997E-2</v>
-    <v>-11.75</v>
-    <v>-1.3795999999999999E-2</v>
+    <v>-69.69</v>
+    <v>-8.5300999999999988E-2</v>
+    <v>50.1</v>
+    <v>6.7041000000000003E-2</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12636,25 +12627,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>121 Woodlands Avenue 5, 739009 SG</v>
-    <v>906</v>
+    <v>777.1</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46227.999859606251</v>
+    <v>46231.99999451328</v>
     <v>0</v>
-    <v>835.5</v>
-    <v>192696651049</v>
+    <v>698.99</v>
+    <v>169078194330</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
-    <v>879.21</v>
-    <v>86.726100000000002</v>
-    <v>913.36</v>
-    <v>851.69</v>
-    <v>839.94</v>
+    <v>774.80499999999995</v>
+    <v>70.957899999999995</v>
+    <v>816.99</v>
+    <v>747.3</v>
+    <v>797.4</v>
     <v>226252100</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>5226252</v>
-    <v>5259737</v>
+    <v>8941628</v>
+    <v>5133795</v>
     <v>2017</v>
   </rv>
   <rv s="2">
@@ -12678,17 +12669,17 @@
     <v>Powered by Refinitiv</v>
     <v>47.14</v>
     <v>39.47</v>
-    <v>-0.24</v>
-    <v>-5.1029999999999999E-3</v>
+    <v>-0.37</v>
+    <v>-7.9719999999999999E-3</v>
     <v>US</v>
-    <v>46.91</v>
+    <v>46.35</v>
     <v>Index</v>
     <v>3</v>
-    <v>46.51</v>
+    <v>45.88</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.83</v>
-    <v>47.03</v>
-    <v>46.79</v>
+    <v>46.3</v>
+    <v>46.41</v>
+    <v>46.04</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13035,7 +13026,7 @@
       <x:numFmt numFmtId="0" formatCode="General"/>
     </x:dxf>
     <x:dxf>
-      <x:numFmt numFmtId="27" formatCode="m/d/yy\ h:mm"/>
+      <x:numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
     </x:dxf>
     <x:dxf>
       <x:numFmt numFmtId="14" formatCode="0.00%"/>
@@ -13472,7 +13463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I74"/>
+  <dimension ref="B1:I69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -13489,18 +13480,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="244" t="s">
+      <c r="B2" s="243" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="245"/>
-      <c r="E2" s="244" t="s">
+      <c r="C2" s="244"/>
+      <c r="E2" s="243" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="245"/>
-      <c r="H2" s="244" t="s">
+      <c r="F2" s="244"/>
+      <c r="H2" s="243" t="s">
         <v>332</v>
       </c>
-      <c r="I2" s="245"/>
+      <c r="I2" s="244"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13515,15 +13506,15 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC151</f>
-        <v>197592.08000000002</v>
+        <v>173373.59999999998</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
         <v>DCF price</v>
       </c>
-      <c r="I3" s="211" t="e">
+      <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>#REF!</v>
+        <v>107.4836552408526</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13539,15 +13530,15 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC152</f>
-        <v>200309.08000000002</v>
+        <v>176090.59999999998</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
         <v>EV/EBIT price</v>
       </c>
-      <c r="I4" s="211" t="e">
+      <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>#REF!</v>
+        <v>91.516102019765427</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13556,7 +13547,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>851.69</v>
+        <v>747.3</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>247</v>
@@ -13569,9 +13560,9 @@
         <f>'AVG target price'!B7</f>
         <v>PS price</v>
       </c>
-      <c r="I5" s="211" t="e">
+      <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>#REF!</v>
+        <v>90.660639619070309</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13580,22 +13571,22 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>839.94</v>
+        <v>797.4</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC148</f>
-        <v>80.805502846299817</v>
+        <v>70.901328273244786</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
         <v>EV/FCFF price</v>
       </c>
-      <c r="I6" s="211" t="e">
+      <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>#REF!</v>
+        <v>107.9793727792898</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13604,22 +13595,22 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-61.67</v>
+        <v>-69.69</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC149</f>
-        <v>17.424448001816529</v>
+        <v>15.28876702997275</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
         <v>AVG price</v>
       </c>
-      <c r="I7" s="212" t="e">
+      <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>#REF!</v>
+        <v>99.409942414744535</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13628,22 +13619,22 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-11.75</v>
+        <v>50.1</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC159</f>
-        <v>1.1103683912836991E-2</v>
+        <v>1.2654752511339675E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
         <v>Upside/Downside</v>
       </c>
-      <c r="I8" s="213" t="e">
+      <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>#REF!</v>
+        <v>-0.8669745183798413</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13652,14 +13643,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-6.7519999999999997E-2</v>
+        <v>-8.5300999999999988E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC160</f>
-        <v>1.2375394803273489E-2</v>
+        <v>1.4104108122574602E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13668,21 +13659,21 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.3795999999999999E-2</v>
+        <v>6.7041000000000003E-2</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>2.9859496392770394E-4</v>
+        <v>3.4030555978534221E-4</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>372</v>
       </c>
       <c r="I10" s="212">
         <f ca="1">DDM!C26</f>
-        <v>35.419711193124122</v>
+        <v>24.473078616587326</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13698,7 +13689,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC161</f>
-        <v>3.4284774976810809E-3</v>
+        <v>3.9073999732369864E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13739,7 +13730,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5259737</v>
+        <v>5133795</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>104</v>
@@ -13755,7 +13746,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-1.3750551135450368E-2</v>
+        <v>-1.56713594226572E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13768,10 +13759,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="246" t="s">
+      <c r="B17" s="245" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="246"/>
+      <c r="C17" s="245"/>
       <c r="E17" s="184" t="s">
         <v>300</v>
       </c>
@@ -13844,14 +13835,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="246" t="s">
+      <c r="B25" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="246"/>
-      <c r="E25" s="244" t="s">
+      <c r="C25" s="245"/>
+      <c r="E25" s="243" t="s">
         <v>345</v>
       </c>
-      <c r="F25" s="245"/>
+      <c r="F25" s="244"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -13865,7 +13856,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>46.79</v>
+        <v>46.04</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13880,7 +13871,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.6789999999999998E-2</v>
+        <v>4.6039999999999998E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13900,22 +13891,22 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="243" t="s">
+      <c r="B33" s="246" t="s">
         <v>340</v>
       </c>
-      <c r="C33" s="243"/>
-      <c r="D33" s="243"/>
-      <c r="E33" s="243"/>
-      <c r="F33" s="243"/>
-      <c r="G33" s="243"/>
-      <c r="H33" s="243"/>
+      <c r="C33" s="246"/>
+      <c r="D33" s="246"/>
+      <c r="E33" s="246"/>
+      <c r="F33" s="246"/>
+      <c r="G33" s="246"/>
+      <c r="H33" s="246"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
         <v>341</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
@@ -13923,101 +13914,101 @@
         <v>342</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="16" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="16"/>
       <c r="C38" s="1" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="16" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="16"/>
       <c r="C40" s="1" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="16"/>
       <c r="C41" s="1" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="16"/>
       <c r="C42" s="1" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="16"/>
       <c r="C43" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="16"/>
       <c r="C44" s="1" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="16"/>
       <c r="C45" s="1" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="16" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C46" s="90">
         <v>3273</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="243"/>
-      <c r="C49" s="243"/>
-      <c r="D49" s="243"/>
-      <c r="E49" s="243"/>
-      <c r="F49" s="243"/>
-      <c r="G49" s="243"/>
-      <c r="H49" s="243"/>
+      <c r="B49" s="246"/>
+      <c r="C49" s="246"/>
+      <c r="D49" s="246"/>
+      <c r="E49" s="246"/>
+      <c r="F49" s="246"/>
+      <c r="G49" s="246"/>
+      <c r="H49" s="246"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="243" t="s">
+      <c r="B52" s="246" t="s">
         <v>343</v>
       </c>
-      <c r="C52" s="243"/>
-      <c r="D52" s="243"/>
-      <c r="E52" s="243"/>
-      <c r="F52" s="243"/>
-      <c r="G52" s="243"/>
-      <c r="H52" s="243"/>
+      <c r="C52" s="246"/>
+      <c r="D52" s="246"/>
+      <c r="E52" s="246"/>
+      <c r="F52" s="246"/>
+      <c r="G52" s="246"/>
+      <c r="H52" s="246"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
         <v>344</v>
       </c>
       <c r="C54" s="41" t="s">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="D54" s="41"/>
       <c r="E54" s="41" t="s">
@@ -14026,103 +14017,83 @@
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B59" s="41" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="246"/>
+      <c r="C59" s="246"/>
+      <c r="D59" s="246"/>
+      <c r="E59" s="246"/>
+      <c r="F59" s="246"/>
+      <c r="G59" s="246"/>
+      <c r="H59" s="246"/>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B62" s="246" t="s">
+        <v>108</v>
+      </c>
+      <c r="C62" s="246"/>
+      <c r="D62" s="246"/>
+      <c r="E62" s="246"/>
+      <c r="F62" s="246"/>
+      <c r="G62" s="246"/>
+      <c r="H62" s="246"/>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B64" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="C59" s="41" t="s">
-        <v>396</v>
-      </c>
-      <c r="D59" s="41"/>
-      <c r="E59" s="41" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="243"/>
-      <c r="C64" s="243"/>
-      <c r="D64" s="243"/>
-      <c r="E64" s="243"/>
-      <c r="F64" s="243"/>
-      <c r="G64" s="243"/>
-      <c r="H64" s="243"/>
-    </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B67" s="243" t="s">
-        <v>108</v>
-      </c>
-      <c r="C67" s="243"/>
-      <c r="D67" s="243"/>
-      <c r="E67" s="243"/>
-      <c r="F67" s="243"/>
-      <c r="G67" s="243"/>
-      <c r="H67" s="243"/>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B69" s="41" t="s">
-        <v>344</v>
-      </c>
-      <c r="C69" s="41" t="s">
+      <c r="C64" s="41" t="s">
         <v>364</v>
       </c>
-      <c r="D69" s="41"/>
-      <c r="E69" s="41" t="s">
+      <c r="D64" s="41"/>
+      <c r="E64" s="41" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="74" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="243"/>
-      <c r="C74" s="243"/>
-      <c r="D74" s="243"/>
-      <c r="E74" s="243"/>
-      <c r="F74" s="243"/>
-      <c r="G74" s="243"/>
-      <c r="H74" s="243"/>
+    <row r="69" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="246"/>
+      <c r="C69" s="246"/>
+      <c r="D69" s="246"/>
+      <c r="E69" s="246"/>
+      <c r="F69" s="246"/>
+      <c r="G69" s="246"/>
+      <c r="H69" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B67:H67"/>
-    <mergeCell ref="B74:H74"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B64:H64"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14162,7 +14133,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66282D1-ADA2-D843-8696-3FC058E17FA6}">
-  <dimension ref="A1:AE25"/>
+  <dimension ref="A1:AE23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -14192,36 +14163,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
       <c r="G2" s="255"/>
       <c r="H2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="243" t="s">
+      <c r="S2" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243"/>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
-      <c r="AA2" s="243" t="s">
+      <c r="T2" s="246"/>
+      <c r="U2" s="246"/>
+      <c r="V2" s="246"/>
+      <c r="W2" s="246"/>
+      <c r="X2" s="246"/>
+      <c r="Y2" s="246"/>
+      <c r="Z2" s="246"/>
+      <c r="AA2" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="243"/>
-      <c r="AC2" s="243"/>
+      <c r="AB2" s="246"/>
+      <c r="AC2" s="246"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -14380,11 +14351,11 @@
         <v>6796</v>
       </c>
       <c r="H6" s="64">
-        <f>H21*H22</f>
+        <f>H19*H20</f>
         <v>9004.7000000000007</v>
       </c>
       <c r="I6" s="64">
-        <f t="shared" ref="I6:L6" si="1">I21*I22</f>
+        <f t="shared" ref="I6:L6" si="1">I19*I20</f>
         <v>12291.415500000001</v>
       </c>
       <c r="J6" s="64">
@@ -14400,11 +14371,11 @@
         <v>10432.968840669377</v>
       </c>
       <c r="N6" s="90" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="O6" s="5"/>
       <c r="Q6" s="90" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="R6" s="1" t="str">
         <f>B6</f>
@@ -14443,7 +14414,7 @@
         <v>2500</v>
       </c>
       <c r="AA6" s="64">
-        <f>AA21*AA22</f>
+        <f>AA19*AA20</f>
         <v>2703.7500000000005</v>
       </c>
       <c r="AB6" s="64"/>
@@ -14479,34 +14450,34 @@
         <v>2300</v>
       </c>
       <c r="H7" s="64">
-        <f t="shared" ref="H7:L7" si="2">G7*(1+H14)</f>
+        <f>G7*(1+H13)</f>
         <v>2829</v>
       </c>
       <c r="I7" s="64">
-        <f t="shared" si="2"/>
+        <f>H7*(1+I13)</f>
         <v>3394.7999999999997</v>
       </c>
       <c r="J7" s="64">
-        <f t="shared" si="2"/>
+        <f>I7*(1+J13)</f>
         <v>3734.28</v>
       </c>
       <c r="K7" s="64">
-        <f t="shared" si="2"/>
+        <f>J7*(1+K13)</f>
         <v>3920.9940000000006</v>
       </c>
       <c r="L7" s="64">
-        <f t="shared" si="2"/>
+        <f>K7*(1+L13)</f>
         <v>3528.8946000000005</v>
       </c>
       <c r="N7" s="90" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="O7" s="5"/>
       <c r="Q7" s="90" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="R7" s="1" t="str">
-        <f t="shared" ref="R7:R8" si="3">B7</f>
+        <f t="shared" ref="R7" si="2">B7</f>
         <v>Edge &amp; IoT</v>
       </c>
       <c r="S7" s="88">
@@ -14542,1146 +14513,969 @@
         <v>612</v>
       </c>
       <c r="AA7" s="64">
-        <f t="shared" ref="AA7:AA8" si="4">Z7*(1+AA14)</f>
+        <f>Z7*(1+AA13)</f>
         <v>642.6</v>
       </c>
       <c r="AB7" s="64"/>
       <c r="AC7" s="64"/>
       <c r="AE7" s="64">
-        <f t="shared" ref="AE7:AE8" si="5">SUM(X7:AA7)</f>
+        <f t="shared" ref="AE7" si="3">SUM(X7:AA7)</f>
         <v>2370.6</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B8" s="1" t="e">
-        <f>Statement!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C8" s="88" t="e">
-        <f>Statement!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D8" s="88" t="e">
-        <f>Statement!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E8" s="88" t="e">
-        <f>Statement!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F8" s="88" t="e">
-        <f>Statement!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G8" s="89" t="e">
-        <f>Statement!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H8" s="64" t="e">
-        <f t="shared" ref="H8:L8" si="6">G8*(1+H15)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I8" s="64" t="e">
-        <f t="shared" si="6"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J8" s="64" t="e">
-        <f t="shared" si="6"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K8" s="64" t="e">
-        <f t="shared" si="6"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L8" s="64" t="e">
-        <f t="shared" si="6"/>
-        <v>#REF!</v>
-      </c>
-      <c r="N8" s="90" t="s">
-        <v>411</v>
-      </c>
-      <c r="O8" s="5"/>
-      <c r="Q8" s="90" t="s">
-        <v>411</v>
-      </c>
-      <c r="R8" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#REF!</v>
-      </c>
-      <c r="S8" s="88" t="e">
-        <f>Statement!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="T8" s="88" t="e">
-        <f>Statement!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U8" s="88" t="e">
-        <f>Statement!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="V8" s="88" t="e">
-        <f>Statement!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="W8" s="88" t="e">
-        <f>Statement!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="X8" s="88" t="e">
-        <f>Statement!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Y8" s="88" t="e">
-        <f>Statement!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z8" s="89" t="e">
-        <f>Statement!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA8" s="64" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="AB8" s="64"/>
-      <c r="AC8" s="64"/>
-      <c r="AE8" s="64" t="e">
-        <f t="shared" si="5"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B9" s="16" t="s">
+      <c r="B8" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="C9" s="92">
+      <c r="C8" s="92">
         <f>Statement!M5</f>
         <v>10681</v>
       </c>
-      <c r="D9" s="92">
+      <c r="D8" s="92">
         <f>Statement!N5</f>
         <v>11661</v>
       </c>
-      <c r="E9" s="92">
+      <c r="E8" s="92">
         <f>Statement!O5</f>
         <v>7384</v>
       </c>
-      <c r="F9" s="92">
+      <c r="F8" s="92">
         <f>Statement!P5</f>
         <v>6551</v>
       </c>
-      <c r="G9" s="93">
+      <c r="G8" s="93">
         <f>Statement!Q5</f>
         <v>9097</v>
       </c>
-      <c r="H9" s="94" t="e">
-        <f>SUM(H6:H8)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I9" s="94" t="e">
-        <f t="shared" ref="I9:L9" si="7">SUM(I6:I8)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J9" s="94" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K9" s="94" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L9" s="94" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
-      </c>
-      <c r="O9" s="5"/>
-      <c r="R9" s="16" t="s">
+      <c r="H8" s="94">
+        <f>SUM(H6:H7)</f>
+        <v>11833.7</v>
+      </c>
+      <c r="I8" s="94">
+        <f>SUM(I6:I7)</f>
+        <v>15686.2155</v>
+      </c>
+      <c r="J8" s="94">
+        <f>SUM(J6:J7)</f>
+        <v>16578.809197500002</v>
+      </c>
+      <c r="K8" s="94">
+        <f>SUM(K6:K7)</f>
+        <v>16123.296737625002</v>
+      </c>
+      <c r="L8" s="94">
+        <f>SUM(L6:L7)</f>
+        <v>13961.863440669378</v>
+      </c>
+      <c r="O8" s="5"/>
+      <c r="R8" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="S9" s="92">
+      <c r="S8" s="92">
         <f>Statement!T5</f>
         <v>1887</v>
       </c>
-      <c r="T9" s="92">
+      <c r="T8" s="92">
         <f>Statement!U5</f>
         <v>2168</v>
       </c>
-      <c r="U9" s="92">
+      <c r="U8" s="92">
         <f>Statement!V5</f>
         <v>2325</v>
       </c>
-      <c r="V9" s="92">
+      <c r="V8" s="92">
         <f>Statement!W5</f>
         <v>2160</v>
       </c>
-      <c r="W9" s="92">
+      <c r="W8" s="92">
         <f>Statement!X5</f>
         <v>2444</v>
       </c>
-      <c r="X9" s="92">
+      <c r="X8" s="92">
         <f>Statement!Y5</f>
         <v>2629</v>
       </c>
-      <c r="Y9" s="92">
+      <c r="Y8" s="92">
         <f>Statement!Z5</f>
         <v>2825</v>
       </c>
-      <c r="Z9" s="93">
+      <c r="Z8" s="93">
         <f>Statement!AA5</f>
         <v>3112</v>
       </c>
-      <c r="AA9" s="94" t="e">
-        <f>SUM(AA6:AA8)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AB9" s="94"/>
-      <c r="AC9" s="94"/>
-      <c r="AE9" s="94" t="e">
-        <f>SUM(X9:AA9)</f>
-        <v>#REF!</v>
-      </c>
+      <c r="AA8" s="94">
+        <f>SUM(AA6:AA7)</f>
+        <v>3346.3500000000004</v>
+      </c>
+      <c r="AB8" s="94"/>
+      <c r="AC8" s="94"/>
+      <c r="AE8" s="94">
+        <f>SUM(X8:AA8)</f>
+        <v>11912.35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="O9" s="5"/>
+      <c r="Q9" s="91"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="C10" s="252" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="252"/>
+      <c r="E10" s="252"/>
+      <c r="F10" s="252"/>
+      <c r="G10" s="252"/>
+      <c r="H10" s="252"/>
+      <c r="I10" s="252"/>
+      <c r="J10" s="252"/>
+      <c r="K10" s="252"/>
+      <c r="L10" s="252"/>
       <c r="O10" s="5"/>
       <c r="Q10" s="91"/>
+      <c r="S10" s="253" t="s">
+        <v>121</v>
+      </c>
+      <c r="T10" s="254"/>
+      <c r="U10" s="254"/>
+      <c r="V10" s="254"/>
+      <c r="W10" s="254"/>
+      <c r="X10" s="254"/>
+      <c r="Y10" s="254"/>
+      <c r="Z10" s="254"/>
+      <c r="AA10" s="254"/>
+      <c r="AB10" s="254"/>
+      <c r="AC10" s="254"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="252" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" s="252"/>
-      <c r="E11" s="252"/>
-      <c r="F11" s="252"/>
-      <c r="G11" s="252"/>
-      <c r="H11" s="252"/>
-      <c r="I11" s="252"/>
-      <c r="J11" s="252"/>
-      <c r="K11" s="252"/>
-      <c r="L11" s="252"/>
+      <c r="B11" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="12">
+        <f>C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D11" s="12">
+        <f>D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E11" s="12">
+        <f>E5</f>
+        <v>2023</v>
+      </c>
+      <c r="F11" s="12">
+        <f>F5</f>
+        <v>2024</v>
+      </c>
+      <c r="G11" s="12">
+        <f>G5</f>
+        <v>2025</v>
+      </c>
+      <c r="H11" s="12">
+        <f>H5</f>
+        <v>2026</v>
+      </c>
+      <c r="I11" s="12">
+        <f>I5</f>
+        <v>2027</v>
+      </c>
+      <c r="J11" s="12">
+        <f>J5</f>
+        <v>2028</v>
+      </c>
+      <c r="K11" s="12">
+        <f>K5</f>
+        <v>2029</v>
+      </c>
+      <c r="L11" s="12">
+        <f>L5</f>
+        <v>2030</v>
+      </c>
       <c r="O11" s="5"/>
       <c r="Q11" s="91"/>
-      <c r="S11" s="253" t="s">
-        <v>121</v>
-      </c>
-      <c r="T11" s="254"/>
-      <c r="U11" s="254"/>
-      <c r="V11" s="254"/>
-      <c r="W11" s="254"/>
-      <c r="X11" s="254"/>
-      <c r="Y11" s="254"/>
-      <c r="Z11" s="254"/>
-      <c r="AA11" s="254"/>
-      <c r="AB11" s="254"/>
-      <c r="AC11" s="254"/>
+      <c r="R11" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="S11" s="12" t="str">
+        <f>S5</f>
+        <v>Q4 2024</v>
+      </c>
+      <c r="T11" s="12" t="str">
+        <f>T5</f>
+        <v>Q1 2025</v>
+      </c>
+      <c r="U11" s="12" t="str">
+        <f>U5</f>
+        <v>Q2 2025</v>
+      </c>
+      <c r="V11" s="12" t="str">
+        <f>V5</f>
+        <v>Q3 2025</v>
+      </c>
+      <c r="W11" s="12" t="str">
+        <f>W5</f>
+        <v>Q4 2025</v>
+      </c>
+      <c r="X11" s="12" t="str">
+        <f>X5</f>
+        <v>Q1 2026</v>
+      </c>
+      <c r="Y11" s="12" t="str">
+        <f>Y5</f>
+        <v>Q2 2026</v>
+      </c>
+      <c r="Z11" s="12" t="str">
+        <f>Z5</f>
+        <v>Q3 2026</v>
+      </c>
+      <c r="AA11" s="12" t="str">
+        <f>AA5</f>
+        <v>FQ1</v>
+      </c>
+      <c r="AB11" s="12" t="str">
+        <f>AB5</f>
+        <v>FQ2</v>
+      </c>
+      <c r="AC11" s="12" t="str">
+        <f>AC5</f>
+        <v>FQ3</v>
+      </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B12" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="12">
-        <f t="shared" ref="C12:L12" si="8">C5</f>
-        <v>2021</v>
-      </c>
-      <c r="D12" s="12">
-        <f t="shared" si="8"/>
-        <v>2022</v>
-      </c>
-      <c r="E12" s="12">
-        <f t="shared" si="8"/>
-        <v>2023</v>
-      </c>
-      <c r="F12" s="12">
-        <f t="shared" si="8"/>
-        <v>2024</v>
-      </c>
-      <c r="G12" s="12">
-        <f t="shared" si="8"/>
-        <v>2025</v>
-      </c>
-      <c r="H12" s="12">
-        <f t="shared" si="8"/>
-        <v>2026</v>
-      </c>
-      <c r="I12" s="12">
-        <f t="shared" si="8"/>
-        <v>2027</v>
-      </c>
-      <c r="J12" s="12">
-        <f t="shared" si="8"/>
-        <v>2028</v>
-      </c>
-      <c r="K12" s="12">
-        <f t="shared" si="8"/>
-        <v>2029</v>
-      </c>
-      <c r="L12" s="12">
-        <f t="shared" si="8"/>
-        <v>2030</v>
+      <c r="B12" s="1" t="str">
+        <f>B6</f>
+        <v>Datacenter</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="95" t="e">
+        <f>D6/C6-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E12" s="95" t="e">
+        <f>E6/D6-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F12" s="95" t="e">
+        <f>F6/E6-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G12" s="96" t="e">
+        <f>G6/F6-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H12" s="95">
+        <f>H6/G6-1</f>
+        <v>0.32500000000000018</v>
+      </c>
+      <c r="I12" s="95">
+        <f>I6/H6-1</f>
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="J12" s="95">
+        <f>J6/I6-1</f>
+        <v>4.5000000000000151E-2</v>
+      </c>
+      <c r="K12" s="95">
+        <f>K6/J6-1</f>
+        <v>-5.0000000000000044E-2</v>
+      </c>
+      <c r="L12" s="95">
+        <f>L6/K6-1</f>
+        <v>-0.14499999999999991</v>
       </c>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
-      <c r="R12" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="S12" s="12" t="str">
-        <f t="shared" ref="S12:AC12" si="9">S5</f>
-        <v>Q4 2024</v>
-      </c>
-      <c r="T12" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v>Q1 2025</v>
-      </c>
-      <c r="U12" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v>Q2 2025</v>
-      </c>
-      <c r="V12" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v>Q3 2025</v>
-      </c>
-      <c r="W12" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v>Q4 2025</v>
-      </c>
-      <c r="X12" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v>Q1 2026</v>
-      </c>
-      <c r="Y12" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v>Q2 2026</v>
-      </c>
-      <c r="Z12" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v>Q3 2026</v>
-      </c>
-      <c r="AA12" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v>FQ1</v>
-      </c>
-      <c r="AB12" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v>FQ2</v>
-      </c>
-      <c r="AC12" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v>FQ3</v>
-      </c>
+      <c r="R12" s="1" t="str">
+        <f>R6</f>
+        <v>Datacenter</v>
+      </c>
+      <c r="S12" s="47"/>
+      <c r="T12" s="95" t="e">
+        <f>T6/S6-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U12" s="95">
+        <f>U6/T6-1</f>
+        <v>9.7345132743362761E-2</v>
+      </c>
+      <c r="V12" s="95">
+        <f>V6/U6-1</f>
+        <v>-6.9700460829493105E-2</v>
+      </c>
+      <c r="W12" s="95">
+        <f>W6/V6-1</f>
+        <v>0.15356037151702795</v>
+      </c>
+      <c r="X12" s="95">
+        <f>X6/W6-1</f>
+        <v>0.13472893183038104</v>
+      </c>
+      <c r="Y12" s="95">
+        <f>Y6/X6-1</f>
+        <v>5.2034058656575288E-2</v>
+      </c>
+      <c r="Z12" s="96">
+        <f>Z6/Y6-1</f>
+        <v>0.12410071942446033</v>
+      </c>
+      <c r="AA12" s="95">
+        <f>AA6/Z6-1</f>
+        <v>8.1500000000000128E-2</v>
+      </c>
+      <c r="AB12" s="95"/>
+      <c r="AC12" s="95"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="str">
-        <f>B6</f>
-        <v>Datacenter</v>
+        <f>B7</f>
+        <v>Edge &amp; IoT</v>
       </c>
       <c r="C13" s="47"/>
       <c r="D13" s="95" t="e">
-        <f t="shared" ref="D13:G13" si="10">D6/C6-1</f>
+        <f>D7/C7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E13" s="95" t="e">
-        <f t="shared" si="10"/>
+        <f>E7/D7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F13" s="95" t="e">
-        <f t="shared" si="10"/>
+        <f>F7/E7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G13" s="96" t="e">
-        <f t="shared" si="10"/>
+        <f>G7/F7-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H13" s="95">
-        <f t="shared" ref="H13" si="11">H6/G6-1</f>
-        <v>0.32500000000000018</v>
-      </c>
-      <c r="I13" s="95">
-        <f t="shared" ref="I13" si="12">I6/H6-1</f>
-        <v>0.36499999999999999</v>
-      </c>
-      <c r="J13" s="95">
-        <f t="shared" ref="J13" si="13">J6/I6-1</f>
-        <v>4.5000000000000151E-2</v>
-      </c>
-      <c r="K13" s="95">
-        <f t="shared" ref="K13" si="14">K6/J6-1</f>
-        <v>-5.0000000000000044E-2</v>
-      </c>
-      <c r="L13" s="95">
-        <f t="shared" ref="L13" si="15">L6/K6-1</f>
-        <v>-0.14499999999999991</v>
+      <c r="H13" s="97">
+        <v>0.23</v>
+      </c>
+      <c r="I13" s="97">
+        <v>0.2</v>
+      </c>
+      <c r="J13" s="97">
+        <v>0.1</v>
+      </c>
+      <c r="K13" s="97">
+        <v>0.05</v>
+      </c>
+      <c r="L13" s="97">
+        <v>-0.1</v>
       </c>
       <c r="O13" s="5"/>
       <c r="Q13" s="91"/>
       <c r="R13" s="1" t="str">
-        <f>R6</f>
-        <v>Datacenter</v>
+        <f>R7</f>
+        <v>Edge &amp; IoT</v>
       </c>
       <c r="S13" s="47"/>
       <c r="T13" s="95" t="e">
-        <f t="shared" ref="T13:AA16" si="16">T6/S6-1</f>
+        <f>T7/S7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U13" s="95">
-        <f t="shared" si="16"/>
-        <v>9.7345132743362761E-2</v>
+        <f>U7/T7-1</f>
+        <v>6.8376068376068133E-3</v>
       </c>
       <c r="V13" s="95">
-        <f t="shared" si="16"/>
-        <v>-6.9700460829493105E-2</v>
+        <f>V7/U7-1</f>
+        <v>-7.4702886247877798E-2</v>
       </c>
       <c r="W13" s="95">
-        <f t="shared" si="16"/>
-        <v>0.15356037151702795</v>
+        <f>W7/V7-1</f>
+        <v>6.6055045871559637E-2</v>
       </c>
       <c r="X13" s="95">
-        <f t="shared" si="16"/>
-        <v>0.13472893183038104</v>
+        <f>X7/W7-1</f>
+        <v>-0.11359724612736666</v>
       </c>
       <c r="Y13" s="95">
-        <f t="shared" si="16"/>
-        <v>5.2034058656575288E-2</v>
+        <f>Y7/X7-1</f>
+        <v>0.16699029126213594</v>
       </c>
       <c r="Z13" s="96">
-        <f t="shared" si="16"/>
-        <v>0.12410071942446033</v>
-      </c>
-      <c r="AA13" s="95">
-        <f t="shared" si="16"/>
-        <v>8.1500000000000128E-2</v>
+        <f>Z7/Y7-1</f>
+        <v>1.830282861896837E-2</v>
+      </c>
+      <c r="AA13" s="97">
+        <v>0.05</v>
       </c>
       <c r="AB13" s="95"/>
       <c r="AC13" s="95"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B14" s="1" t="str">
-        <f>B7</f>
-        <v>Edge &amp; IoT</v>
+      <c r="B14" s="16" t="str">
+        <f>B8</f>
+        <v>Total</v>
       </c>
       <c r="C14" s="47"/>
-      <c r="D14" s="95" t="e">
-        <f t="shared" ref="D14:G14" si="17">D7/C7-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E14" s="95" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F14" s="95" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G14" s="96" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H14" s="97">
-        <v>0.23</v>
-      </c>
-      <c r="I14" s="97">
-        <v>0.2</v>
-      </c>
-      <c r="J14" s="97">
-        <v>0.1</v>
-      </c>
-      <c r="K14" s="97">
-        <v>0.05</v>
-      </c>
-      <c r="L14" s="97">
-        <v>-0.1</v>
+      <c r="D14" s="103">
+        <f>D8/C8-1</f>
+        <v>9.1751708641512941E-2</v>
+      </c>
+      <c r="E14" s="103">
+        <f>E8/D8-1</f>
+        <v>-0.36677814938684505</v>
+      </c>
+      <c r="F14" s="103">
+        <f>F8/E8-1</f>
+        <v>-0.11281148429035748</v>
+      </c>
+      <c r="G14" s="104">
+        <f>G8/F8-1</f>
+        <v>0.38864295527400405</v>
+      </c>
+      <c r="H14" s="103">
+        <f>H8/G8-1</f>
+        <v>0.30083544025502928</v>
+      </c>
+      <c r="I14" s="103">
+        <f>I8/H8-1</f>
+        <v>0.32555460253344259</v>
+      </c>
+      <c r="J14" s="103">
+        <f>J8/I8-1</f>
+        <v>5.6903062277832595E-2</v>
+      </c>
+      <c r="K14" s="103">
+        <f>K8/J8-1</f>
+        <v>-2.747558370740466E-2</v>
+      </c>
+      <c r="L14" s="103">
+        <f>L8/K8-1</f>
+        <v>-0.13405653521911221</v>
       </c>
       <c r="O14" s="5"/>
       <c r="Q14" s="91"/>
-      <c r="R14" s="1" t="str">
-        <f>R7</f>
-        <v>Edge &amp; IoT</v>
+      <c r="R14" s="16" t="str">
+        <f>R8</f>
+        <v>Total</v>
       </c>
       <c r="S14" s="47"/>
-      <c r="T14" s="95" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U14" s="95">
-        <f t="shared" si="16"/>
-        <v>6.8376068376068133E-3</v>
-      </c>
-      <c r="V14" s="95">
-        <f t="shared" si="16"/>
-        <v>-7.4702886247877798E-2</v>
-      </c>
-      <c r="W14" s="95">
-        <f t="shared" si="16"/>
-        <v>6.6055045871559637E-2</v>
-      </c>
-      <c r="X14" s="95">
-        <f t="shared" si="16"/>
-        <v>-0.11359724612736666</v>
-      </c>
-      <c r="Y14" s="95">
-        <f t="shared" si="16"/>
-        <v>0.16699029126213594</v>
-      </c>
-      <c r="Z14" s="96">
-        <f t="shared" si="16"/>
-        <v>1.830282861896837E-2</v>
-      </c>
-      <c r="AA14" s="97">
-        <v>0.05</v>
-      </c>
-      <c r="AB14" s="95"/>
-      <c r="AC14" s="95"/>
+      <c r="T14" s="103">
+        <f>T8/S8-1</f>
+        <v>0.14891361950185478</v>
+      </c>
+      <c r="U14" s="103">
+        <f>U8/T8-1</f>
+        <v>7.2416974169741799E-2</v>
+      </c>
+      <c r="V14" s="103">
+        <f>V8/U8-1</f>
+        <v>-7.096774193548383E-2</v>
+      </c>
+      <c r="W14" s="103">
+        <f>W8/V8-1</f>
+        <v>0.13148148148148153</v>
+      </c>
+      <c r="X14" s="103">
+        <f>X8/W8-1</f>
+        <v>7.5695581014729951E-2</v>
+      </c>
+      <c r="Y14" s="103">
+        <f>Y8/X8-1</f>
+        <v>7.4553062000760839E-2</v>
+      </c>
+      <c r="Z14" s="104">
+        <f>Z8/Y8-1</f>
+        <v>0.10159292035398226</v>
+      </c>
+      <c r="AA14" s="103">
+        <f>AA8/Z8-1</f>
+        <v>7.5305269922879337E-2</v>
+      </c>
+      <c r="AB14" s="103"/>
+      <c r="AC14" s="103"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B15" s="1" t="e">
-        <f>B8</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="95" t="e">
-        <f t="shared" ref="D15:G15" si="18">D8/C8-1</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E15" s="95" t="e">
-        <f t="shared" si="18"/>
-        <v>#REF!</v>
-      </c>
-      <c r="F15" s="95" t="e">
-        <f t="shared" si="18"/>
-        <v>#REF!</v>
-      </c>
-      <c r="G15" s="96" t="e">
-        <f t="shared" si="18"/>
-        <v>#REF!</v>
-      </c>
-      <c r="H15" s="97">
-        <v>0.13</v>
-      </c>
-      <c r="I15" s="97">
-        <v>0.12</v>
-      </c>
-      <c r="J15" s="97">
-        <v>0.15</v>
-      </c>
-      <c r="K15" s="97">
-        <v>-0.1</v>
-      </c>
-      <c r="L15" s="97">
-        <v>-0.05</v>
-      </c>
       <c r="O15" s="5"/>
       <c r="Q15" s="91"/>
-      <c r="R15" s="1" t="e">
-        <f>R8</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S15" s="47"/>
-      <c r="T15" s="95" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
-      </c>
-      <c r="U15" s="95" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
-      </c>
-      <c r="V15" s="95" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
-      </c>
-      <c r="W15" s="95" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
-      </c>
-      <c r="X15" s="95" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
-      </c>
-      <c r="Y15" s="95" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
-      </c>
-      <c r="Z15" s="96" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
-      </c>
-      <c r="AA15" s="97">
-        <v>0.03</v>
-      </c>
-      <c r="AB15" s="95"/>
-      <c r="AC15" s="95"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B16" s="16" t="str">
-        <f>B9</f>
-        <v>Total</v>
-      </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="103">
-        <f t="shared" ref="D16:L16" si="19">D9/C9-1</f>
-        <v>9.1751708641512941E-2</v>
-      </c>
-      <c r="E16" s="103">
-        <f t="shared" si="19"/>
-        <v>-0.36677814938684505</v>
-      </c>
-      <c r="F16" s="103">
-        <f t="shared" si="19"/>
-        <v>-0.11281148429035748</v>
-      </c>
-      <c r="G16" s="104">
-        <f t="shared" si="19"/>
-        <v>0.38864295527400405</v>
-      </c>
-      <c r="H16" s="103" t="e">
-        <f t="shared" si="19"/>
-        <v>#REF!</v>
-      </c>
-      <c r="I16" s="103" t="e">
-        <f t="shared" si="19"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J16" s="103" t="e">
-        <f t="shared" si="19"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K16" s="103" t="e">
-        <f t="shared" si="19"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L16" s="103" t="e">
-        <f t="shared" si="19"/>
-        <v>#REF!</v>
-      </c>
       <c r="O16" s="5"/>
       <c r="Q16" s="91"/>
-      <c r="R16" s="16" t="str">
-        <f>R9</f>
-        <v>Total</v>
-      </c>
-      <c r="S16" s="47"/>
-      <c r="T16" s="103">
-        <f t="shared" si="16"/>
-        <v>0.14891361950185478</v>
-      </c>
-      <c r="U16" s="103">
-        <f t="shared" si="16"/>
-        <v>7.2416974169741799E-2</v>
-      </c>
-      <c r="V16" s="103">
-        <f t="shared" si="16"/>
-        <v>-7.096774193548383E-2</v>
-      </c>
-      <c r="W16" s="103">
-        <f t="shared" si="16"/>
-        <v>0.13148148148148153</v>
-      </c>
-      <c r="X16" s="103">
-        <f t="shared" si="16"/>
-        <v>7.5695581014729951E-2</v>
-      </c>
-      <c r="Y16" s="103">
-        <f t="shared" si="16"/>
-        <v>7.4553062000760839E-2</v>
-      </c>
-      <c r="Z16" s="104">
-        <f t="shared" si="16"/>
-        <v>0.10159292035398226</v>
-      </c>
-      <c r="AA16" s="103" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
-      </c>
-      <c r="AB16" s="103"/>
-      <c r="AC16" s="103"/>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="86"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="252" t="s">
+        <v>405</v>
+      </c>
+      <c r="D17" s="252"/>
+      <c r="E17" s="252"/>
+      <c r="F17" s="252"/>
+      <c r="G17" s="252"/>
+      <c r="H17" s="252"/>
+      <c r="I17" s="252"/>
+      <c r="J17" s="252"/>
+      <c r="K17" s="252"/>
+      <c r="L17" s="252"/>
       <c r="O17" s="5"/>
-      <c r="Q17" s="91"/>
+      <c r="S17" s="253" t="s">
+        <v>115</v>
+      </c>
+      <c r="T17" s="254"/>
+      <c r="U17" s="254"/>
+      <c r="V17" s="254"/>
+      <c r="W17" s="254"/>
+      <c r="X17" s="254"/>
+      <c r="Y17" s="254"/>
+      <c r="Z17" s="254"/>
+      <c r="AA17" s="254"/>
+      <c r="AB17" s="254"/>
+      <c r="AC17" s="254"/>
+      <c r="AE17" s="87"/>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="O18" s="5"/>
-      <c r="Q18" s="91"/>
-    </row>
-    <row r="19" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="86"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="252" t="s">
-        <v>413</v>
-      </c>
-      <c r="D19" s="252"/>
-      <c r="E19" s="252"/>
-      <c r="F19" s="252"/>
-      <c r="G19" s="252"/>
-      <c r="H19" s="252"/>
-      <c r="I19" s="252"/>
-      <c r="J19" s="252"/>
-      <c r="K19" s="252"/>
-      <c r="L19" s="252"/>
-      <c r="O19" s="5"/>
-      <c r="S19" s="253" t="s">
-        <v>115</v>
-      </c>
-      <c r="T19" s="254"/>
-      <c r="U19" s="254"/>
-      <c r="V19" s="254"/>
-      <c r="W19" s="254"/>
-      <c r="X19" s="254"/>
-      <c r="Y19" s="254"/>
-      <c r="Z19" s="254"/>
-      <c r="AA19" s="254"/>
-      <c r="AB19" s="254"/>
-      <c r="AC19" s="254"/>
-      <c r="AE19" s="87"/>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B20" s="16"/>
-      <c r="C20" s="12">
+      <c r="B18" s="16"/>
+      <c r="C18" s="12">
         <f>C5</f>
         <v>2021</v>
       </c>
-      <c r="D20" s="12">
-        <f t="shared" ref="D20:L20" si="20">D5</f>
+      <c r="D18" s="12">
+        <f>D5</f>
         <v>2022</v>
       </c>
-      <c r="E20" s="12">
-        <f t="shared" si="20"/>
+      <c r="E18" s="12">
+        <f>E5</f>
         <v>2023</v>
       </c>
-      <c r="F20" s="12">
-        <f t="shared" si="20"/>
+      <c r="F18" s="12">
+        <f>F5</f>
         <v>2024</v>
       </c>
-      <c r="G20" s="12">
-        <f t="shared" si="20"/>
+      <c r="G18" s="12">
+        <f>G5</f>
         <v>2025</v>
       </c>
-      <c r="H20" s="12">
-        <f t="shared" si="20"/>
+      <c r="H18" s="12">
+        <f>H5</f>
         <v>2026</v>
       </c>
-      <c r="I20" s="12">
-        <f t="shared" si="20"/>
+      <c r="I18" s="12">
+        <f>I5</f>
         <v>2027</v>
       </c>
-      <c r="J20" s="12">
-        <f t="shared" si="20"/>
+      <c r="J18" s="12">
+        <f>J5</f>
         <v>2028</v>
       </c>
-      <c r="K20" s="12">
-        <f t="shared" si="20"/>
+      <c r="K18" s="12">
+        <f>K5</f>
         <v>2029</v>
       </c>
-      <c r="L20" s="12">
-        <f t="shared" si="20"/>
+      <c r="L18" s="12">
+        <f>L5</f>
         <v>2030</v>
       </c>
-      <c r="O20" s="5"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="12" t="str">
+      <c r="O18" s="5"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="12" t="str">
         <f>S5</f>
         <v>Q4 2024</v>
       </c>
-      <c r="T20" s="12" t="str">
-        <f t="shared" ref="T20:AC20" si="21">T5</f>
+      <c r="T18" s="12" t="str">
+        <f>T5</f>
         <v>Q1 2025</v>
       </c>
-      <c r="U20" s="12" t="str">
-        <f t="shared" si="21"/>
+      <c r="U18" s="12" t="str">
+        <f>U5</f>
         <v>Q2 2025</v>
       </c>
-      <c r="V20" s="12" t="str">
-        <f t="shared" si="21"/>
+      <c r="V18" s="12" t="str">
+        <f>V5</f>
         <v>Q3 2025</v>
       </c>
-      <c r="W20" s="12" t="str">
-        <f t="shared" si="21"/>
+      <c r="W18" s="12" t="str">
+        <f>W5</f>
         <v>Q4 2025</v>
       </c>
-      <c r="X20" s="12" t="str">
-        <f t="shared" si="21"/>
+      <c r="X18" s="12" t="str">
+        <f>X5</f>
         <v>Q1 2026</v>
       </c>
-      <c r="Y20" s="12" t="str">
-        <f t="shared" si="21"/>
+      <c r="Y18" s="12" t="str">
+        <f>Y5</f>
         <v>Q2 2026</v>
       </c>
-      <c r="Z20" s="12" t="str">
-        <f t="shared" si="21"/>
+      <c r="Z18" s="12" t="str">
+        <f>Z5</f>
         <v>Q3 2026</v>
       </c>
-      <c r="AA20" s="12" t="str">
-        <f t="shared" si="21"/>
+      <c r="AA18" s="12" t="str">
+        <f>AA5</f>
         <v>FQ1</v>
       </c>
-      <c r="AB20" s="12" t="str">
-        <f t="shared" si="21"/>
+      <c r="AB18" s="12" t="str">
+        <f>AB5</f>
         <v>FQ2</v>
       </c>
-      <c r="AC20" s="12" t="str">
-        <f t="shared" si="21"/>
+      <c r="AC18" s="12" t="str">
+        <f>AC5</f>
         <v>FQ3</v>
       </c>
-      <c r="AE20" s="8" t="str">
+      <c r="AE18" s="8" t="str">
         <f>AE5</f>
         <v>FQ1</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B21" s="1" t="str">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B19" s="1" t="str">
         <f>Statement!B206&amp;" exabytes"</f>
         <v>Nearline exabytes</v>
       </c>
-      <c r="C21" s="88">
+      <c r="C19" s="88">
         <f>Statement!M206</f>
         <v>0</v>
       </c>
-      <c r="D21" s="88">
+      <c r="D19" s="88">
         <f>Statement!N206</f>
         <v>0</v>
       </c>
-      <c r="E21" s="88">
+      <c r="E19" s="88">
         <f>Statement!O206</f>
         <v>0</v>
       </c>
-      <c r="F21" s="88">
+      <c r="F19" s="88">
         <f>Statement!P206</f>
         <v>0</v>
       </c>
-      <c r="G21" s="89">
+      <c r="G19" s="89">
         <f>Statement!Q206</f>
         <v>496.6</v>
       </c>
-      <c r="H21" s="240">
-        <f>G21*(1+H23)</f>
+      <c r="H19" s="240">
+        <f>G19*(1+H21)</f>
         <v>620.75</v>
       </c>
-      <c r="I21" s="240">
-        <f t="shared" ref="I21:L21" si="22">H21*(1+I23)</f>
+      <c r="I19" s="240">
+        <f t="shared" ref="I19:L19" si="4">H19*(1+I21)</f>
         <v>806.97500000000002</v>
       </c>
-      <c r="J21" s="240">
-        <f t="shared" si="22"/>
+      <c r="J19" s="240">
+        <f t="shared" si="4"/>
         <v>887.67250000000013</v>
       </c>
-      <c r="K21" s="240">
-        <f t="shared" si="22"/>
+      <c r="K19" s="240">
+        <f t="shared" si="4"/>
         <v>887.67250000000013</v>
       </c>
-      <c r="L21" s="240">
-        <f t="shared" si="22"/>
+      <c r="L19" s="240">
+        <f t="shared" si="4"/>
         <v>798.90525000000014</v>
       </c>
-      <c r="N21" s="90" t="s">
-        <v>414</v>
-      </c>
-      <c r="O21" s="5"/>
-      <c r="Q21" s="90" t="s">
-        <v>414</v>
-      </c>
-      <c r="R21" s="1" t="str">
-        <f>B21</f>
+      <c r="N19" s="90" t="s">
+        <v>406</v>
+      </c>
+      <c r="O19" s="5"/>
+      <c r="Q19" s="90" t="s">
+        <v>406</v>
+      </c>
+      <c r="R19" s="1" t="str">
+        <f>B19</f>
         <v>Nearline exabytes</v>
       </c>
-      <c r="S21" s="88">
+      <c r="S19" s="88">
         <f>Statement!T206</f>
         <v>90</v>
       </c>
-      <c r="T21" s="88">
+      <c r="T19" s="88">
         <f>Statement!U206</f>
         <v>114</v>
       </c>
-      <c r="U21" s="88">
+      <c r="U19" s="88">
         <f>Statement!V206</f>
         <v>126</v>
       </c>
-      <c r="V21" s="88">
+      <c r="V19" s="88">
         <f>Statement!W206</f>
         <v>119.6</v>
       </c>
-      <c r="W21" s="88">
+      <c r="W19" s="88">
         <f>Statement!X206</f>
         <v>137</v>
       </c>
-      <c r="X21" s="88">
+      <c r="X19" s="88">
         <f>Statement!Y206</f>
         <v>159</v>
       </c>
-      <c r="Y21" s="88">
+      <c r="Y19" s="88">
         <f>Statement!Z206</f>
         <v>165</v>
       </c>
-      <c r="Z21" s="89">
+      <c r="Z19" s="89">
         <f>Statement!AA206</f>
         <v>175.4</v>
       </c>
-      <c r="AA21" s="64">
-        <f>Z21*(1+AA23)</f>
+      <c r="AA19" s="64">
+        <f>Z19*(1+AA21)</f>
         <v>184.17000000000002</v>
       </c>
-      <c r="AB21" s="64"/>
-      <c r="AC21" s="64"/>
-      <c r="AE21" s="64">
-        <f>SUM(X21:AA21)</f>
+      <c r="AB19" s="64"/>
+      <c r="AC19" s="64"/>
+      <c r="AE19" s="64">
+        <f>SUM(X19:AA19)</f>
         <v>683.56999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B22" s="1" t="str">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="str">
         <f>Statement!B209</f>
         <v>Price per Exabyte</v>
       </c>
-      <c r="C22" s="237" t="e">
+      <c r="C20" s="237" t="e">
         <f>Statement!M209</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D22" s="237" t="e">
+      <c r="D20" s="237" t="e">
         <f>Statement!N209</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E22" s="237" t="e">
+      <c r="E20" s="237" t="e">
         <f>Statement!O209</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F22" s="237" t="e">
+      <c r="F20" s="237" t="e">
         <f>Statement!P209</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="238">
+      <c r="G20" s="238">
         <f>Statement!Q209</f>
         <v>13.685058397100281</v>
       </c>
-      <c r="H22" s="241">
-        <f>G22*(1+H24)</f>
+      <c r="H20" s="241">
+        <f>G20*(1+H22)</f>
         <v>14.506161900926299</v>
       </c>
-      <c r="I22" s="241">
-        <f t="shared" ref="I22:L22" si="23">H22*(1+I24)</f>
+      <c r="I20" s="241">
+        <f t="shared" ref="I20:L20" si="5">H20*(1+I22)</f>
         <v>15.231469995972615</v>
       </c>
-      <c r="J22" s="241">
-        <f t="shared" si="23"/>
+      <c r="J20" s="241">
+        <f t="shared" si="5"/>
         <v>14.469896496173984</v>
       </c>
-      <c r="K22" s="241">
-        <f t="shared" si="23"/>
+      <c r="K20" s="241">
+        <f t="shared" si="5"/>
         <v>13.746401671365284</v>
       </c>
-      <c r="L22" s="241">
-        <f t="shared" si="23"/>
+      <c r="L20" s="241">
+        <f t="shared" si="5"/>
         <v>13.059081587797019</v>
       </c>
-      <c r="N22" s="90" t="s">
-        <v>415</v>
-      </c>
-      <c r="O22" s="5"/>
-      <c r="Q22" s="90" t="s">
-        <v>415</v>
-      </c>
-      <c r="R22" s="1" t="str">
-        <f t="shared" ref="R22" si="24">B22</f>
+      <c r="N20" s="90" t="s">
+        <v>407</v>
+      </c>
+      <c r="O20" s="5"/>
+      <c r="Q20" s="90" t="s">
+        <v>407</v>
+      </c>
+      <c r="R20" s="1" t="str">
+        <f t="shared" ref="R20" si="6">B20</f>
         <v>Price per Exabyte</v>
       </c>
-      <c r="S22" s="237">
+      <c r="S20" s="237">
         <f>Statement!T209</f>
         <v>0</v>
       </c>
-      <c r="T22" s="237">
+      <c r="T20" s="237">
         <f>Statement!U209</f>
         <v>13.87719298245614</v>
       </c>
-      <c r="U22" s="237">
+      <c r="U20" s="237">
         <f>Statement!V209</f>
         <v>13.777777777777779</v>
       </c>
-      <c r="V22" s="237">
+      <c r="V20" s="237">
         <f>Statement!W209</f>
         <v>13.503344481605351</v>
       </c>
-      <c r="W22" s="237">
+      <c r="W20" s="237">
         <f>Statement!X209</f>
         <v>13.598540145985401</v>
       </c>
-      <c r="X22" s="237">
+      <c r="X20" s="237">
         <f>Statement!Y209</f>
         <v>13.29559748427673</v>
       </c>
-      <c r="Y22" s="237">
+      <c r="Y20" s="237">
         <f>Statement!Z209</f>
         <v>13.478787878787879</v>
       </c>
-      <c r="Z22" s="238">
+      <c r="Z20" s="238">
         <f>Statement!AA209</f>
         <v>14.253135689851767</v>
       </c>
-      <c r="AA22" s="239">
-        <f>Z22*(1+AA24)</f>
+      <c r="AA20" s="239">
+        <f>Z20*(1+AA22)</f>
         <v>14.680729760547321</v>
       </c>
-      <c r="AB22" s="64"/>
-      <c r="AC22" s="64"/>
-      <c r="AE22" s="239">
-        <f>AE6/AE21</f>
+      <c r="AB20" s="64"/>
+      <c r="AC20" s="64"/>
+      <c r="AE20" s="239">
+        <f>AE6/AE19</f>
         <v>13.958702108050383</v>
       </c>
     </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B21" s="122" t="str">
+        <f>B19&amp;" growth"</f>
+        <v>Nearline exabytes growth</v>
+      </c>
+      <c r="C21" s="47"/>
+      <c r="D21" s="95" t="e">
+        <f>D19/C19-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E21" s="95" t="e">
+        <f t="shared" ref="E21:F21" si="7">E19/D19-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F21" s="95" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G21" s="96" t="e">
+        <f>G19/F19-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H21" s="97">
+        <v>0.25</v>
+      </c>
+      <c r="I21" s="97">
+        <v>0.3</v>
+      </c>
+      <c r="J21" s="97">
+        <v>0.1</v>
+      </c>
+      <c r="K21" s="97">
+        <v>0</v>
+      </c>
+      <c r="L21" s="97">
+        <v>-0.1</v>
+      </c>
+      <c r="O21" s="5"/>
+      <c r="R21" s="122" t="str">
+        <f>R19&amp;" growth"</f>
+        <v>Nearline exabytes growth</v>
+      </c>
+      <c r="S21" s="47"/>
+      <c r="T21" s="95">
+        <f>T19/S19-1</f>
+        <v>0.26666666666666661</v>
+      </c>
+      <c r="U21" s="95">
+        <f t="shared" ref="U21:Y21" si="8">U19/T19-1</f>
+        <v>0.10526315789473695</v>
+      </c>
+      <c r="V21" s="95">
+        <f t="shared" si="8"/>
+        <v>-5.0793650793650835E-2</v>
+      </c>
+      <c r="W21" s="95">
+        <f t="shared" si="8"/>
+        <v>0.14548494983277593</v>
+      </c>
+      <c r="X21" s="95">
+        <f t="shared" si="8"/>
+        <v>0.16058394160583944</v>
+      </c>
+      <c r="Y21" s="95">
+        <f t="shared" si="8"/>
+        <v>3.7735849056603765E-2</v>
+      </c>
+      <c r="Z21" s="96">
+        <f t="shared" ref="Z21" si="9">Z19/Y19-1</f>
+        <v>6.3030303030302992E-2</v>
+      </c>
+      <c r="AA21" s="97">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B22" s="122" t="str">
+        <f>B20&amp;" growth"</f>
+        <v>Price per Exabyte growth</v>
+      </c>
+      <c r="C22" s="47"/>
+      <c r="D22" s="95" t="e">
+        <f t="shared" ref="D22:F22" si="10">D20/C20-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E22" s="95" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F22" s="95" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G22" s="96" t="e">
+        <f>G20/F20-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H22" s="97">
+        <v>0.06</v>
+      </c>
+      <c r="I22" s="97">
+        <v>0.05</v>
+      </c>
+      <c r="J22" s="97">
+        <v>-0.05</v>
+      </c>
+      <c r="K22" s="97">
+        <v>-0.05</v>
+      </c>
+      <c r="L22" s="97">
+        <v>-0.05</v>
+      </c>
+      <c r="O22" s="5"/>
+      <c r="R22" s="122" t="str">
+        <f>R20&amp;" growth"</f>
+        <v>Price per Exabyte growth</v>
+      </c>
+      <c r="S22" s="47"/>
+      <c r="T22" s="95" t="e">
+        <f t="shared" ref="T22:Y22" si="11">T20/S20-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U22" s="95">
+        <f t="shared" si="11"/>
+        <v>-7.1639275179097295E-3</v>
+      </c>
+      <c r="V22" s="95">
+        <f t="shared" si="11"/>
+        <v>-1.9918545689934231E-2</v>
+      </c>
+      <c r="W22" s="95">
+        <f t="shared" si="11"/>
+        <v>7.0497841856680399E-3</v>
+      </c>
+      <c r="X22" s="95">
+        <f t="shared" si="11"/>
+        <v>-2.2277587039231328E-2</v>
+      </c>
+      <c r="Y22" s="95">
+        <f t="shared" si="11"/>
+        <v>1.3778274705426918E-2</v>
+      </c>
+      <c r="Z22" s="96">
+        <f t="shared" ref="Z22" si="12">Z20/Y20-1</f>
+        <v>5.7449365479110392E-2</v>
+      </c>
+      <c r="AA22" s="97">
+        <v>0.03</v>
+      </c>
+    </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B23" s="122" t="str">
-        <f>B21&amp;" growth"</f>
-        <v>Nearline exabytes growth</v>
-      </c>
-      <c r="C23" s="47"/>
-      <c r="D23" s="95" t="e">
-        <f>D21/C21-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E23" s="95" t="e">
-        <f t="shared" ref="E23:F23" si="25">E21/D21-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F23" s="95" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G23" s="96" t="e">
-        <f>G21/F21-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H23" s="97">
-        <v>0.25</v>
-      </c>
-      <c r="I23" s="97">
-        <v>0.3</v>
-      </c>
-      <c r="J23" s="97">
-        <v>0.1</v>
-      </c>
-      <c r="K23" s="97">
-        <v>0</v>
-      </c>
-      <c r="L23" s="97">
-        <v>-0.1</v>
-      </c>
       <c r="O23" s="5"/>
-      <c r="R23" s="122" t="str">
-        <f>R21&amp;" growth"</f>
-        <v>Nearline exabytes growth</v>
-      </c>
-      <c r="S23" s="47"/>
-      <c r="T23" s="95">
-        <f>T21/S21-1</f>
-        <v>0.26666666666666661</v>
-      </c>
-      <c r="U23" s="95">
-        <f t="shared" ref="U23:Y23" si="26">U21/T21-1</f>
-        <v>0.10526315789473695</v>
-      </c>
-      <c r="V23" s="95">
-        <f t="shared" si="26"/>
-        <v>-5.0793650793650835E-2</v>
-      </c>
-      <c r="W23" s="95">
-        <f t="shared" si="26"/>
-        <v>0.14548494983277593</v>
-      </c>
-      <c r="X23" s="95">
-        <f t="shared" si="26"/>
-        <v>0.16058394160583944</v>
-      </c>
-      <c r="Y23" s="95">
-        <f t="shared" si="26"/>
-        <v>3.7735849056603765E-2</v>
-      </c>
-      <c r="Z23" s="96">
-        <f t="shared" ref="Z23" si="27">Z21/Y21-1</f>
-        <v>6.3030303030302992E-2</v>
-      </c>
-      <c r="AA23" s="97">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B24" s="122" t="str">
-        <f>B22&amp;" growth"</f>
-        <v>Price per Exabyte growth</v>
-      </c>
-      <c r="C24" s="47"/>
-      <c r="D24" s="95" t="e">
-        <f t="shared" ref="D24:F24" si="28">D22/C22-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E24" s="95" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F24" s="95" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G24" s="96" t="e">
-        <f>G22/F22-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H24" s="97">
-        <v>0.06</v>
-      </c>
-      <c r="I24" s="97">
-        <v>0.05</v>
-      </c>
-      <c r="J24" s="97">
-        <v>-0.05</v>
-      </c>
-      <c r="K24" s="97">
-        <v>-0.05</v>
-      </c>
-      <c r="L24" s="97">
-        <v>-0.05</v>
-      </c>
-      <c r="O24" s="5"/>
-      <c r="R24" s="122" t="str">
-        <f>R22&amp;" growth"</f>
-        <v>Price per Exabyte growth</v>
-      </c>
-      <c r="S24" s="47"/>
-      <c r="T24" s="95" t="e">
-        <f t="shared" ref="T24:Y24" si="29">T22/S22-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U24" s="95">
-        <f t="shared" si="29"/>
-        <v>-7.1639275179097295E-3</v>
-      </c>
-      <c r="V24" s="95">
-        <f t="shared" si="29"/>
-        <v>-1.9918545689934231E-2</v>
-      </c>
-      <c r="W24" s="95">
-        <f t="shared" si="29"/>
-        <v>7.0497841856680399E-3</v>
-      </c>
-      <c r="X24" s="95">
-        <f t="shared" si="29"/>
-        <v>-2.2277587039231328E-2</v>
-      </c>
-      <c r="Y24" s="95">
-        <f t="shared" si="29"/>
-        <v>1.3778274705426918E-2</v>
-      </c>
-      <c r="Z24" s="96">
-        <f t="shared" ref="Z24" si="30">Z22/Y22-1</f>
-        <v>5.7449365479110392E-2</v>
-      </c>
-      <c r="AA24" s="97">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="O25" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="S19:AC19"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="S11:AC11"/>
+    <mergeCell ref="C17:L17"/>
+    <mergeCell ref="S17:AC17"/>
+    <mergeCell ref="C10:L10"/>
+    <mergeCell ref="S10:AC10"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
@@ -15690,9 +15484,6 @@
     <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="AE8" evalError="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -15724,35 +15515,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
       <c r="G2" s="255"/>
       <c r="H2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
-      <c r="P2" s="243" t="s">
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
+      <c r="P2" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="243"/>
-      <c r="R2" s="243"/>
-      <c r="S2" s="243"/>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243" t="s">
+      <c r="Q2" s="246"/>
+      <c r="R2" s="246"/>
+      <c r="S2" s="246"/>
+      <c r="T2" s="246"/>
+      <c r="U2" s="246"/>
+      <c r="V2" s="246"/>
+      <c r="W2" s="246"/>
+      <c r="X2" s="246" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
+      <c r="Y2" s="246"/>
+      <c r="Z2" s="246"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -15887,90 +15678,90 @@
         <v>19</v>
       </c>
       <c r="C6" s="92">
-        <f>Revenue!C9</f>
+        <f>Revenue!C8</f>
         <v>10681</v>
       </c>
       <c r="D6" s="92">
-        <f>Revenue!D9</f>
+        <f>Revenue!D8</f>
         <v>11661</v>
       </c>
       <c r="E6" s="92">
-        <f>Revenue!E9</f>
+        <f>Revenue!E8</f>
         <v>7384</v>
       </c>
       <c r="F6" s="92">
-        <f>Revenue!F9</f>
+        <f>Revenue!F8</f>
         <v>6551</v>
       </c>
       <c r="G6" s="93">
-        <f>Revenue!G9</f>
+        <f>Revenue!G8</f>
         <v>9097</v>
       </c>
-      <c r="H6" s="92" t="e">
-        <f>Revenue!H9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I6" s="92" t="e">
-        <f>Revenue!I9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J6" s="92" t="e">
-        <f>Revenue!J9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K6" s="92" t="e">
-        <f>Revenue!K9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L6" s="92" t="e">
-        <f>Revenue!L9</f>
-        <v>#REF!</v>
+      <c r="H6" s="92">
+        <f>Revenue!H8</f>
+        <v>11833.7</v>
+      </c>
+      <c r="I6" s="92">
+        <f>Revenue!I8</f>
+        <v>15686.2155</v>
+      </c>
+      <c r="J6" s="92">
+        <f>Revenue!J8</f>
+        <v>16578.809197500002</v>
+      </c>
+      <c r="K6" s="92">
+        <f>Revenue!K8</f>
+        <v>16123.296737625002</v>
+      </c>
+      <c r="L6" s="92">
+        <f>Revenue!L8</f>
+        <v>13961.863440669378</v>
       </c>
       <c r="N6" s="91"/>
       <c r="O6" s="16" t="s">
         <v>19</v>
       </c>
       <c r="P6" s="92">
-        <f>Revenue!S9</f>
+        <f>Revenue!S8</f>
         <v>1887</v>
       </c>
       <c r="Q6" s="92">
-        <f>Revenue!T9</f>
+        <f>Revenue!T8</f>
         <v>2168</v>
       </c>
       <c r="R6" s="92">
-        <f>Revenue!U9</f>
+        <f>Revenue!U8</f>
         <v>2325</v>
       </c>
       <c r="S6" s="92">
-        <f>Revenue!V9</f>
+        <f>Revenue!V8</f>
         <v>2160</v>
       </c>
       <c r="T6" s="92">
-        <f>Revenue!W9</f>
+        <f>Revenue!W8</f>
         <v>2444</v>
       </c>
       <c r="U6" s="92">
-        <f>Revenue!X9</f>
+        <f>Revenue!X8</f>
         <v>2629</v>
       </c>
       <c r="V6" s="92">
-        <f>Revenue!Y9</f>
+        <f>Revenue!Y8</f>
         <v>2825</v>
       </c>
       <c r="W6" s="93">
-        <f>Revenue!Z9</f>
+        <f>Revenue!Z8</f>
         <v>3112</v>
       </c>
-      <c r="X6" s="92" t="e">
-        <f>Revenue!AA9</f>
-        <v>#REF!</v>
+      <c r="X6" s="92">
+        <f>Revenue!AA8</f>
+        <v>3346.3500000000004</v>
       </c>
       <c r="Y6" s="94"/>
       <c r="Z6" s="94"/>
-      <c r="AB6" s="92" t="e">
-        <f>Revenue!AE9</f>
-        <v>#REF!</v>
+      <c r="AB6" s="92">
+        <f>Revenue!AE8</f>
+        <v>11912.35</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.2">
@@ -16133,25 +15924,25 @@
         <f>Statement!Q6</f>
         <v>5897</v>
       </c>
-      <c r="H11" s="108" t="e">
+      <c r="H11" s="108">
         <f>H6*H19</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I11" s="108" t="e">
+        <v>6508.5350000000008</v>
+      </c>
+      <c r="I11" s="108">
         <f t="shared" ref="I11:L11" si="3">I6*I19</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J11" s="108" t="e">
+        <v>7529.3834399999996</v>
+      </c>
+      <c r="J11" s="108">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K11" s="108" t="e">
+        <v>7792.0403228250007</v>
+      </c>
+      <c r="K11" s="108">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L11" s="108" t="e">
+        <v>7900.4154014362502</v>
+      </c>
+      <c r="L11" s="108">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>7679.0248923681584</v>
       </c>
       <c r="N11" s="91"/>
       <c r="O11" s="16" t="str">
@@ -16190,15 +15981,15 @@
         <f>Statement!AA6</f>
         <v>1665</v>
       </c>
-      <c r="X11" s="108" t="e">
+      <c r="X11" s="108">
         <f>X6*X19</f>
-        <v>#REF!</v>
+        <v>1505.8575000000003</v>
       </c>
       <c r="Y11" s="108"/>
       <c r="Z11" s="108"/>
-      <c r="AB11" s="108" t="e">
+      <c r="AB11" s="108">
         <f>SUM(U11:X11)</f>
-        <v>#REF!</v>
+        <v>6411.8575000000001</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.2">
@@ -16226,25 +16017,25 @@
         <f>Statement!Q8</f>
         <v>724</v>
       </c>
-      <c r="H12" s="24" t="e">
+      <c r="H12" s="24">
         <f>H6*H20</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I12" s="24" t="e">
+        <v>946.69600000000003</v>
+      </c>
+      <c r="I12" s="24">
         <f>I6*I20</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J12" s="24" t="e">
+        <v>1254.89724</v>
+      </c>
+      <c r="J12" s="24">
         <f>J6*J20</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K12" s="24" t="e">
+        <v>1492.0928277750002</v>
+      </c>
+      <c r="K12" s="24">
         <f>K6*K20</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L12" s="24" t="e">
+        <v>1451.0967063862502</v>
+      </c>
+      <c r="L12" s="24">
         <f>L6*L20</f>
-        <v>#REF!</v>
+        <v>1396.1863440669379</v>
       </c>
       <c r="N12" s="91"/>
       <c r="O12" s="39" t="str">
@@ -16283,15 +16074,15 @@
         <f>Statement!AA8</f>
         <v>194</v>
       </c>
-      <c r="X12" s="25" t="e">
+      <c r="X12" s="25">
         <f>X20*X$6</f>
-        <v>#REF!</v>
+        <v>167.31750000000002</v>
       </c>
       <c r="Y12" s="24"/>
       <c r="Z12" s="24"/>
-      <c r="AB12" s="24" t="e">
+      <c r="AB12" s="24">
         <f t="shared" ref="AB12:AB14" si="5">SUM(U12:X12)</f>
-        <v>#REF!</v>
+        <v>734.3175</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.2">
@@ -16319,25 +16110,25 @@
         <f>Statement!Q9</f>
         <v>561</v>
       </c>
-      <c r="H13" s="24" t="e">
+      <c r="H13" s="24">
         <f>H6*H21</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I13" s="24" t="e">
+        <v>532.51650000000006</v>
+      </c>
+      <c r="I13" s="24">
         <f>I6*I21</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J13" s="24" t="e">
+        <v>784.31077500000004</v>
+      </c>
+      <c r="J13" s="24">
         <f>J6*J21</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K13" s="24" t="e">
+        <v>994.72855185000014</v>
+      </c>
+      <c r="K13" s="24">
         <f>K6*K21</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L13" s="24" t="e">
+        <v>1289.8637390100002</v>
+      </c>
+      <c r="L13" s="24">
         <f>L6*L21</f>
-        <v>#REF!</v>
+        <v>1535.8049784736315</v>
       </c>
       <c r="M13" s="90"/>
       <c r="N13" s="90"/>
@@ -16377,15 +16168,15 @@
         <f>Statement!AA9</f>
         <v>143</v>
       </c>
-      <c r="X13" s="25" t="e">
+      <c r="X13" s="25">
         <f>X21*X$6</f>
-        <v>#REF!</v>
+        <v>133.85400000000001</v>
       </c>
       <c r="Y13" s="24"/>
       <c r="Z13" s="24"/>
-      <c r="AB13" s="24" t="e">
+      <c r="AB13" s="24">
         <f t="shared" si="5"/>
-        <v>#REF!</v>
+        <v>563.85400000000004</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.2">
@@ -16412,25 +16203,25 @@
         <f>Statement!Q10</f>
         <v>1310</v>
       </c>
-      <c r="H14" s="108" t="e">
+      <c r="H14" s="108">
         <f>SUM(H12:H13)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I14" s="108" t="e">
+        <v>1479.2125000000001</v>
+      </c>
+      <c r="I14" s="108">
         <f>SUM(I12:I13)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J14" s="108" t="e">
+        <v>2039.2080150000002</v>
+      </c>
+      <c r="J14" s="108">
         <f>SUM(J12:J13)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K14" s="108" t="e">
+        <v>2486.8213796250002</v>
+      </c>
+      <c r="K14" s="108">
         <f>SUM(K12:K13)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L14" s="108" t="e">
+        <v>2740.9604453962502</v>
+      </c>
+      <c r="L14" s="108">
         <f>SUM(L12:L13)</f>
-        <v>#REF!</v>
+        <v>2931.9913225405694</v>
       </c>
       <c r="M14" s="90"/>
       <c r="N14" s="90"/>
@@ -16470,15 +16261,15 @@
         <f>Statement!AA10</f>
         <v>449</v>
       </c>
-      <c r="X14" s="108" t="e">
+      <c r="X14" s="108">
         <f>SUM(X12:X13)</f>
-        <v>#REF!</v>
+        <v>301.17150000000004</v>
       </c>
       <c r="Y14" s="108"/>
       <c r="Z14" s="108"/>
-      <c r="AB14" s="108" t="e">
+      <c r="AB14" s="108">
         <f t="shared" si="5"/>
-        <v>#REF!</v>
+        <v>1426.1714999999999</v>
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
@@ -16626,7 +16417,7 @@
         <v>0.64823568209299764</v>
       </c>
       <c r="H19" s="97">
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I19" s="97">
         <v>0.48</v>
@@ -16677,7 +16468,7 @@
         <v>0.53502570694087404</v>
       </c>
       <c r="X19" s="97">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="Y19" s="97"/>
       <c r="Z19" s="97"/>
@@ -16708,7 +16499,7 @@
         <v>7.9586676926459266E-2</v>
       </c>
       <c r="H20" s="97">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="I20" s="97">
         <v>0.08</v>
@@ -16759,7 +16550,7 @@
         <v>6.2339331619537273E-2</v>
       </c>
       <c r="X20" s="97">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="Y20" s="97"/>
       <c r="Z20" s="97"/>
@@ -16871,25 +16662,25 @@
         <f t="shared" si="11"/>
         <v>0.14400351764317906</v>
       </c>
-      <c r="H22" s="103" t="e">
+      <c r="H22" s="103">
         <f t="shared" si="11"/>
-        <v>#REF!</v>
-      </c>
-      <c r="I22" s="103" t="e">
+        <v>0.125</v>
+      </c>
+      <c r="I22" s="103">
         <f t="shared" si="11"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J22" s="103" t="e">
+        <v>0.13</v>
+      </c>
+      <c r="J22" s="103">
         <f t="shared" si="11"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K22" s="103" t="e">
+        <v>0.15</v>
+      </c>
+      <c r="K22" s="103">
         <f t="shared" si="11"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L22" s="103" t="e">
+        <v>0.16999999999999998</v>
+      </c>
+      <c r="L22" s="103">
         <f t="shared" si="11"/>
-        <v>#REF!</v>
+        <v>0.21</v>
       </c>
       <c r="O22" s="16" t="str">
         <f t="shared" ref="O22" si="12">O14</f>
@@ -16927,9 +16718,9 @@
         <f t="shared" ref="W22:X22" si="14">W14/W$6</f>
         <v>0.14428020565552699</v>
       </c>
-      <c r="X22" s="103" t="e">
+      <c r="X22" s="103">
         <f t="shared" si="14"/>
-        <v>#REF!</v>
+        <v>0.09</v>
       </c>
       <c r="Y22" s="16"/>
       <c r="Z22" s="16"/>
@@ -16984,20 +16775,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
+      <c r="D3" s="246"/>
+      <c r="E3" s="246"/>
+      <c r="F3" s="246"/>
       <c r="G3" s="255"/>
       <c r="H3" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
+      <c r="I3" s="246"/>
+      <c r="J3" s="246"/>
+      <c r="K3" s="246"/>
+      <c r="L3" s="246"/>
       <c r="P3" s="257"/>
       <c r="Q3" s="257"/>
       <c r="R3" s="257"/>
@@ -17103,44 +16894,44 @@
         <v>19</v>
       </c>
       <c r="C7" s="92">
-        <f>Revenue!C9</f>
+        <f>Revenue!C8</f>
         <v>10681</v>
       </c>
       <c r="D7" s="92">
-        <f>Revenue!D9</f>
+        <f>Revenue!D8</f>
         <v>11661</v>
       </c>
       <c r="E7" s="92">
-        <f>Revenue!E9</f>
+        <f>Revenue!E8</f>
         <v>7384</v>
       </c>
       <c r="F7" s="92">
-        <f>Revenue!F9</f>
+        <f>Revenue!F8</f>
         <v>6551</v>
       </c>
       <c r="G7" s="93">
-        <f>Revenue!G9</f>
+        <f>Revenue!G8</f>
         <v>9097</v>
       </c>
-      <c r="H7" s="92" t="e">
-        <f>Revenue!H9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I7" s="92" t="e">
-        <f>Revenue!I9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J7" s="92" t="e">
-        <f>Revenue!J9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K7" s="92" t="e">
-        <f>Revenue!K9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L7" s="92" t="e">
-        <f>Revenue!L9</f>
-        <v>#REF!</v>
+      <c r="H7" s="92">
+        <f>Revenue!H8</f>
+        <v>11833.7</v>
+      </c>
+      <c r="I7" s="92">
+        <f>Revenue!I8</f>
+        <v>15686.2155</v>
+      </c>
+      <c r="J7" s="92">
+        <f>Revenue!J8</f>
+        <v>16578.809197500002</v>
+      </c>
+      <c r="K7" s="92">
+        <f>Revenue!K8</f>
+        <v>16123.296737625002</v>
+      </c>
+      <c r="L7" s="92">
+        <f>Revenue!L8</f>
+        <v>13961.863440669378</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -17181,25 +16972,25 @@
         <f>'COGS &amp; OpEx'!G11</f>
         <v>5897</v>
       </c>
-      <c r="H8" s="112" t="e">
+      <c r="H8" s="112">
         <f>'COGS &amp; OpEx'!H11</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I8" s="112" t="e">
+        <v>6508.5350000000008</v>
+      </c>
+      <c r="I8" s="112">
         <f>'COGS &amp; OpEx'!I11</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J8" s="112" t="e">
+        <v>7529.3834399999996</v>
+      </c>
+      <c r="J8" s="112">
         <f>'COGS &amp; OpEx'!J11</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K8" s="112" t="e">
+        <v>7792.0403228250007</v>
+      </c>
+      <c r="K8" s="112">
         <f>'COGS &amp; OpEx'!K11</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L8" s="112" t="e">
+        <v>7900.4154014362502</v>
+      </c>
+      <c r="L8" s="112">
         <f>'COGS &amp; OpEx'!L11</f>
-        <v>#REF!</v>
+        <v>7679.0248923681584</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -17332,25 +17123,25 @@
         <f>Statement!Q29</f>
         <v>959</v>
       </c>
-      <c r="H13" s="25" t="e">
+      <c r="H13" s="25">
         <f>H20*H7/365</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I13" s="25" t="e">
+        <v>1134.7383561643835</v>
+      </c>
+      <c r="I13" s="25">
         <f>I20*I7/365</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J13" s="25" t="e">
+        <v>1504.1576506849315</v>
+      </c>
+      <c r="J13" s="25">
         <f>J20*J7/365</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K13" s="25" t="e">
+        <v>1589.7488271575344</v>
+      </c>
+      <c r="K13" s="25">
         <f>K20*K7/365</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L13" s="25" t="e">
+        <v>1546.0695501832192</v>
+      </c>
+      <c r="L13" s="25">
         <f>L20*L7/365</f>
-        <v>#REF!</v>
+        <v>1338.8088230778856</v>
       </c>
       <c r="N13" s="91"/>
       <c r="O13" s="16"/>
@@ -17391,25 +17182,25 @@
         <f>Statement!Q30</f>
         <v>1440</v>
       </c>
-      <c r="H14" s="126" t="e">
+      <c r="H14" s="126">
         <f>H21*H8/365</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I14" s="126" t="e">
+        <v>1248.2121917808222</v>
+      </c>
+      <c r="I14" s="126">
         <f t="shared" ref="I14:L14" si="2">I21*I8/365</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J14" s="126" t="e">
+        <v>1443.9913446575342</v>
+      </c>
+      <c r="J14" s="126">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K14" s="126" t="e">
+        <v>1494.3638975280821</v>
+      </c>
+      <c r="K14" s="126">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L14" s="126" t="e">
+        <v>1515.1481591795548</v>
+      </c>
+      <c r="L14" s="126">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>1472.689705385674</v>
       </c>
       <c r="N14" s="91"/>
       <c r="O14" s="16"/>
@@ -17450,25 +17241,25 @@
         <f>Statement!Q37</f>
         <v>1604</v>
       </c>
-      <c r="H15" s="24" t="e">
+      <c r="H15" s="24">
         <f>H22*H8/365</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I15" s="24" t="e">
+        <v>1783.1602739726031</v>
+      </c>
+      <c r="I15" s="24">
         <f>I22*I8/365</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J15" s="24" t="e">
+        <v>2062.8447780821916</v>
+      </c>
+      <c r="J15" s="24">
         <f>J22*J8/365</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K15" s="24" t="e">
+        <v>2134.8055678972605</v>
+      </c>
+      <c r="K15" s="24">
         <f>K22*K8/365</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L15" s="24" t="e">
+        <v>2164.4973702565067</v>
+      </c>
+      <c r="L15" s="24">
         <f>L22*L8/365</f>
-        <v>#REF!</v>
+        <v>2103.842436265249</v>
       </c>
       <c r="N15" s="91"/>
       <c r="P15" s="117"/>
@@ -17571,19 +17362,19 @@
         <v>38.478069693305486</v>
       </c>
       <c r="H20" s="102">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="I20" s="102">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="J20" s="102">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="K20" s="102">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L20" s="102">
-        <v>58</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
@@ -17611,19 +17402,19 @@
         <v>89.130066135323048</v>
       </c>
       <c r="H21" s="102">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="I21" s="102">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="J21" s="102">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="K21" s="102">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="L21" s="102">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
@@ -17651,19 +17442,19 @@
         <v>99.280990334068164</v>
       </c>
       <c r="H22" s="102">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I22" s="102">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J22" s="102">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="K22" s="102">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="L22" s="102">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.2">
@@ -17692,23 +17483,23 @@
       </c>
       <c r="H23" s="118">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="I23" s="118">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="J23" s="118">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="K23" s="118">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="L23" s="118">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
@@ -17799,25 +17590,25 @@
         <f>Statement!Q54</f>
         <v>-513</v>
       </c>
-      <c r="H28" s="126" t="e">
+      <c r="H28" s="126">
         <f>-(H13-G13)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I28" s="126" t="e">
+        <v>-175.7383561643835</v>
+      </c>
+      <c r="I28" s="126">
         <f t="shared" ref="I28:L29" si="7">-(I13-H13)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J28" s="126" t="e">
+        <v>-369.41929452054796</v>
+      </c>
+      <c r="J28" s="126">
         <f t="shared" si="7"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K28" s="126" t="e">
+        <v>-85.591176472602911</v>
+      </c>
+      <c r="K28" s="126">
         <f t="shared" si="7"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L28" s="126" t="e">
+        <v>43.679276974315144</v>
+      </c>
+      <c r="L28" s="126">
         <f t="shared" si="7"/>
-        <v>#REF!</v>
+        <v>207.26072710533367</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
@@ -17844,25 +17635,25 @@
         <f>Statement!Q55</f>
         <v>-201</v>
       </c>
-      <c r="H29" s="126" t="e">
+      <c r="H29" s="126">
         <f>-(H14-G14)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I29" s="126" t="e">
+        <v>191.7878082191778</v>
+      </c>
+      <c r="I29" s="126">
         <f t="shared" si="7"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J29" s="126" t="e">
+        <v>-195.77915287671203</v>
+      </c>
+      <c r="J29" s="126">
         <f t="shared" si="7"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K29" s="126" t="e">
+        <v>-50.372552870547906</v>
+      </c>
+      <c r="K29" s="126">
         <f t="shared" si="7"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L29" s="126" t="e">
+        <v>-20.784261651472661</v>
+      </c>
+      <c r="L29" s="126">
         <f t="shared" si="7"/>
-        <v>#REF!</v>
+        <v>42.458453793880835</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.2">
@@ -17889,25 +17680,25 @@
         <f>Statement!Q56</f>
         <v>-242</v>
       </c>
-      <c r="H30" s="64" t="e">
+      <c r="H30" s="64">
         <f>H15-G15</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I30" s="64" t="e">
+        <v>179.16027397260314</v>
+      </c>
+      <c r="I30" s="64">
         <f t="shared" ref="I30:L30" si="8">I15-H15</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J30" s="64" t="e">
+        <v>279.68450410958849</v>
+      </c>
+      <c r="J30" s="64">
         <f t="shared" si="8"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K30" s="64" t="e">
+        <v>71.960789815068892</v>
+      </c>
+      <c r="K30" s="64">
         <f t="shared" si="8"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L30" s="64" t="e">
+        <v>29.69180235924614</v>
+      </c>
+      <c r="L30" s="64">
         <f t="shared" si="8"/>
-        <v>#REF!</v>
+        <v>-60.654933991257622</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
@@ -18002,25 +17793,25 @@
         <f>Statement!Q54+Statement!Q55+Statement!Q56+Statement!Q57</f>
         <v>-965</v>
       </c>
-      <c r="H35" s="126" t="e">
+      <c r="H35" s="126">
         <f>H36+H28+H29+H30</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I35" s="126" t="e">
+        <v>431.88372602739742</v>
+      </c>
+      <c r="I35" s="126">
         <f t="shared" ref="I35:L35" si="10">I36+I28+I29+I30</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J35" s="126" t="e">
+        <v>28.210366712328494</v>
+      </c>
+      <c r="J35" s="126">
         <f t="shared" si="10"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K35" s="126" t="e">
+        <v>267.5732444219181</v>
+      </c>
+      <c r="K35" s="126">
         <f t="shared" si="10"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L35" s="126" t="e">
+        <v>375.05275243458868</v>
+      </c>
+      <c r="L35" s="126">
         <f t="shared" si="10"/>
-        <v>#REF!</v>
+        <v>468.30151572134446</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.2">
@@ -18047,25 +17838,25 @@
         <f t="shared" si="11"/>
         <v>-9</v>
       </c>
-      <c r="H36" s="64" t="e">
+      <c r="H36" s="64">
         <f>H7*H37</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I36" s="64" t="e">
+        <v>236.67400000000001</v>
+      </c>
+      <c r="I36" s="64">
         <f>I7*I37</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J36" s="64" t="e">
+        <v>313.72431</v>
+      </c>
+      <c r="J36" s="64">
         <f>J7*J37</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K36" s="64" t="e">
+        <v>331.57618395000003</v>
+      </c>
+      <c r="K36" s="64">
         <f>K7*K37</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L36" s="64" t="e">
+        <v>322.46593475250006</v>
+      </c>
+      <c r="L36" s="64">
         <f>L7*L37</f>
-        <v>#REF!</v>
+        <v>279.23726881338757</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.2">
@@ -18093,19 +17884,19 @@
         <v>-9.8933714411344391E-4</v>
       </c>
       <c r="H37" s="97">
-        <v>-0.12</v>
+        <v>0.02</v>
       </c>
       <c r="I37" s="97">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="J37" s="97">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="K37" s="97">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="L37" s="97">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.2">
@@ -18197,25 +17988,25 @@
         <f>Statement!Q52</f>
         <v>251</v>
       </c>
-      <c r="H42" s="25" t="e">
+      <c r="H42" s="25">
         <f>H7*H43</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I42" s="25" t="e">
+        <v>473.34800000000001</v>
+      </c>
+      <c r="I42" s="25">
         <f>I7*I43</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J42" s="25" t="e">
+        <v>627.44862000000001</v>
+      </c>
+      <c r="J42" s="25">
         <f>J7*J43</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K42" s="25" t="e">
+        <v>663.15236790000006</v>
+      </c>
+      <c r="K42" s="25">
         <f>K7*K43</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L42" s="25" t="e">
+        <v>644.93186950500012</v>
+      </c>
+      <c r="L42" s="25">
         <f>L7*L43</f>
-        <v>#REF!</v>
+        <v>558.47453762677515</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -18243,19 +18034,19 @@
         <v>2.7591513685830495E-2</v>
       </c>
       <c r="H43" s="97">
-        <v>5.5E-2</v>
+        <v>0.04</v>
       </c>
       <c r="I43" s="97">
-        <v>5.5E-2</v>
+        <v>0.04</v>
       </c>
       <c r="J43" s="97">
-        <v>5.5E-2</v>
+        <v>0.04</v>
       </c>
       <c r="K43" s="97">
-        <v>5.5E-2</v>
+        <v>0.04</v>
       </c>
       <c r="L43" s="97">
-        <v>5.5E-2</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.2">
@@ -18282,25 +18073,25 @@
         <f t="shared" si="13"/>
         <v>0.94716981132075473</v>
       </c>
-      <c r="H44" s="123" t="e">
+      <c r="H44" s="123">
         <f t="shared" si="13"/>
-        <v>#REF!</v>
-      </c>
-      <c r="I44" s="123" t="e">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="I44" s="123">
         <f t="shared" si="13"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J44" s="123" t="e">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="J44" s="123">
         <f t="shared" si="13"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K44" s="123" t="e">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="K44" s="123">
         <f t="shared" si="13"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L44" s="123" t="e">
+        <v>0.88888888888888895</v>
+      </c>
+      <c r="L44" s="123">
         <f t="shared" si="13"/>
-        <v>#REF!</v>
+        <v>0.88888888888888895</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -18327,25 +18118,25 @@
         <f>-Statement!Q108</f>
         <v>265</v>
       </c>
-      <c r="H45" s="25" t="e">
+      <c r="H45" s="25">
         <f>H7*H46</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I45" s="25" t="e">
+        <v>532.51650000000006</v>
+      </c>
+      <c r="I45" s="25">
         <f>I7*I46</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J45" s="25" t="e">
+        <v>705.87969750000002</v>
+      </c>
+      <c r="J45" s="25">
         <f>J7*J46</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K45" s="25" t="e">
+        <v>746.04641388750008</v>
+      </c>
+      <c r="K45" s="25">
         <f>K7*K46</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L45" s="25" t="e">
+        <v>725.54835319312508</v>
+      </c>
+      <c r="L45" s="25">
         <f>L7*L46</f>
-        <v>#REF!</v>
+        <v>628.28385483012198</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
@@ -18373,23 +18164,29 @@
         <v>2.9130482576673628E-2</v>
       </c>
       <c r="H46" s="97">
-        <v>0.05</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I46" s="97">
-        <v>0.05</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="J46" s="97">
-        <v>0.05</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="K46" s="97">
-        <v>0.05</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="L46" s="97">
-        <v>0.05</v>
+        <v>4.4999999999999998E-2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18397,12 +18194,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18440,20 +18231,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
       <c r="G2" s="255"/>
       <c r="H2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
       <c r="S2" s="257"/>
       <c r="T2" s="257"/>
       <c r="U2" s="257"/>
@@ -18559,44 +18350,44 @@
         <v>19</v>
       </c>
       <c r="C6" s="92">
-        <f>Revenue!C9</f>
+        <f>Revenue!C8</f>
         <v>10681</v>
       </c>
       <c r="D6" s="92">
-        <f>Revenue!D9</f>
+        <f>Revenue!D8</f>
         <v>11661</v>
       </c>
       <c r="E6" s="92">
-        <f>Revenue!E9</f>
+        <f>Revenue!E8</f>
         <v>7384</v>
       </c>
       <c r="F6" s="92">
-        <f>Revenue!F9</f>
+        <f>Revenue!F8</f>
         <v>6551</v>
       </c>
       <c r="G6" s="93">
-        <f>Revenue!G9</f>
+        <f>Revenue!G8</f>
         <v>9097</v>
       </c>
-      <c r="H6" s="92" t="e">
-        <f>Revenue!H9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I6" s="92" t="e">
-        <f>Revenue!I9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J6" s="92" t="e">
-        <f>Revenue!J9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K6" s="92" t="e">
-        <f>Revenue!K9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L6" s="92" t="e">
-        <f>Revenue!L9</f>
-        <v>#REF!</v>
+      <c r="H6" s="92">
+        <f>Revenue!H8</f>
+        <v>11833.7</v>
+      </c>
+      <c r="I6" s="92">
+        <f>Revenue!I8</f>
+        <v>15686.2155</v>
+      </c>
+      <c r="J6" s="92">
+        <f>Revenue!J8</f>
+        <v>16578.809197500002</v>
+      </c>
+      <c r="K6" s="92">
+        <f>Revenue!K8</f>
+        <v>16123.296737625002</v>
+      </c>
+      <c r="L6" s="92">
+        <f>Revenue!L8</f>
+        <v>13961.863440669378</v>
       </c>
       <c r="N6" s="90" t="s">
         <v>153</v>
@@ -18639,25 +18430,25 @@
         <f>'COGS &amp; OpEx'!G11</f>
         <v>5897</v>
       </c>
-      <c r="H7" s="112" t="e">
+      <c r="H7" s="112">
         <f>'COGS &amp; OpEx'!H11</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I7" s="112" t="e">
+        <v>6508.5350000000008</v>
+      </c>
+      <c r="I7" s="112">
         <f>'COGS &amp; OpEx'!I11</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J7" s="112" t="e">
+        <v>7529.3834399999996</v>
+      </c>
+      <c r="J7" s="112">
         <f>'COGS &amp; OpEx'!J11</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K7" s="112" t="e">
+        <v>7792.0403228250007</v>
+      </c>
+      <c r="K7" s="112">
         <f>'COGS &amp; OpEx'!K11</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L7" s="112" t="e">
+        <v>7900.4154014362502</v>
+      </c>
+      <c r="L7" s="112">
         <f>'COGS &amp; OpEx'!L11</f>
-        <v>#REF!</v>
+        <v>7679.0248923681584</v>
       </c>
       <c r="N7" s="90" t="s">
         <v>154</v>
@@ -18700,25 +18491,25 @@
         <f t="shared" si="1"/>
         <v>3200</v>
       </c>
-      <c r="H8" s="94" t="e">
+      <c r="H8" s="94">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="I8" s="94" t="e">
+        <v>5325.165</v>
+      </c>
+      <c r="I8" s="94">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J8" s="94" t="e">
+        <v>8156.8320600000006</v>
+      </c>
+      <c r="J8" s="94">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K8" s="94" t="e">
+        <v>8786.7688746750027</v>
+      </c>
+      <c r="K8" s="94">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L8" s="94" t="e">
+        <v>8222.8813361887514</v>
+      </c>
+      <c r="L8" s="94">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
+        <v>6282.8385483012198</v>
       </c>
       <c r="N8" s="90"/>
       <c r="Q8" s="90"/>
@@ -18759,25 +18550,25 @@
         <f>'COGS &amp; OpEx'!G14</f>
         <v>1310</v>
       </c>
-      <c r="H9" s="112" t="e">
+      <c r="H9" s="112">
         <f>'COGS &amp; OpEx'!H14</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I9" s="112" t="e">
+        <v>1479.2125000000001</v>
+      </c>
+      <c r="I9" s="112">
         <f>'COGS &amp; OpEx'!I14</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J9" s="112" t="e">
+        <v>2039.2080150000002</v>
+      </c>
+      <c r="J9" s="112">
         <f>'COGS &amp; OpEx'!J14</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K9" s="112" t="e">
+        <v>2486.8213796250002</v>
+      </c>
+      <c r="K9" s="112">
         <f>'COGS &amp; OpEx'!K14</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L9" s="112" t="e">
+        <v>2740.9604453962502</v>
+      </c>
+      <c r="L9" s="112">
         <f>'COGS &amp; OpEx'!L14</f>
-        <v>#REF!</v>
+        <v>2931.9913225405694</v>
       </c>
       <c r="N9" s="128" t="s">
         <v>154</v>
@@ -18820,25 +18611,25 @@
         <f t="shared" si="2"/>
         <v>1890</v>
       </c>
-      <c r="H10" s="94" t="e">
+      <c r="H10" s="94">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="I10" s="94" t="e">
+        <v>3845.9524999999999</v>
+      </c>
+      <c r="I10" s="94">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J10" s="94" t="e">
+        <v>6117.6240450000005</v>
+      </c>
+      <c r="J10" s="94">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K10" s="94" t="e">
+        <v>6299.9474950500025</v>
+      </c>
+      <c r="K10" s="94">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L10" s="94" t="e">
+        <v>5481.9208907925013</v>
+      </c>
+      <c r="L10" s="94">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>3350.8472257606504</v>
       </c>
       <c r="N10" s="90"/>
       <c r="Q10" s="90"/>
@@ -19042,25 +18833,25 @@
         <f>'WC &amp; Investments'!G42</f>
         <v>251</v>
       </c>
-      <c r="H20" s="88" t="e">
+      <c r="H20" s="88">
         <f>'WC &amp; Investments'!H42</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I20" s="88" t="e">
+        <v>473.34800000000001</v>
+      </c>
+      <c r="I20" s="88">
         <f>'WC &amp; Investments'!I42</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J20" s="88" t="e">
+        <v>627.44862000000001</v>
+      </c>
+      <c r="J20" s="88">
         <f>'WC &amp; Investments'!J42</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K20" s="88" t="e">
+        <v>663.15236790000006</v>
+      </c>
+      <c r="K20" s="88">
         <f>'WC &amp; Investments'!K42</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L20" s="88" t="e">
+        <v>644.93186950500012</v>
+      </c>
+      <c r="L20" s="88">
         <f>'WC &amp; Investments'!L42</f>
-        <v>#REF!</v>
+        <v>558.47453762677515</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>159</v>
@@ -19090,25 +18881,25 @@
         <f>'WC &amp; Investments'!G45</f>
         <v>265</v>
       </c>
-      <c r="H21" s="88" t="e">
+      <c r="H21" s="88">
         <f>'WC &amp; Investments'!H45</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I21" s="88" t="e">
+        <v>532.51650000000006</v>
+      </c>
+      <c r="I21" s="88">
         <f>'WC &amp; Investments'!I45</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J21" s="88" t="e">
+        <v>705.87969750000002</v>
+      </c>
+      <c r="J21" s="88">
         <f>'WC &amp; Investments'!J45</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K21" s="88" t="e">
+        <v>746.04641388750008</v>
+      </c>
+      <c r="K21" s="88">
         <f>'WC &amp; Investments'!K45</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L21" s="88" t="e">
+        <v>725.54835319312508</v>
+      </c>
+      <c r="L21" s="88">
         <f>'WC &amp; Investments'!L45</f>
-        <v>#REF!</v>
+        <v>628.28385483012198</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>159</v>
@@ -19138,25 +18929,25 @@
         <f>'WC &amp; Investments'!G35</f>
         <v>-965</v>
       </c>
-      <c r="H22" s="88" t="e">
+      <c r="H22" s="88">
         <f>'WC &amp; Investments'!H35</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I22" s="88" t="e">
+        <v>431.88372602739742</v>
+      </c>
+      <c r="I22" s="88">
         <f>'WC &amp; Investments'!I35</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J22" s="88" t="e">
+        <v>28.210366712328494</v>
+      </c>
+      <c r="J22" s="88">
         <f>'WC &amp; Investments'!J35</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K22" s="88" t="e">
+        <v>267.5732444219181</v>
+      </c>
+      <c r="K22" s="88">
         <f>'WC &amp; Investments'!K35</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L22" s="88" t="e">
+        <v>375.05275243458868</v>
+      </c>
+      <c r="L22" s="88">
         <f>'WC &amp; Investments'!L35</f>
-        <v>#REF!</v>
+        <v>468.30151572134446</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>159</v>
@@ -19245,25 +19036,25 @@
         <f t="shared" si="6"/>
         <v>1944.9636483807005</v>
       </c>
-      <c r="H27" s="126" t="e">
+      <c r="H27" s="126">
         <f t="shared" si="6"/>
-        <v>#REF!</v>
-      </c>
-      <c r="I27" s="126" t="e">
+        <v>3038.302475</v>
+      </c>
+      <c r="I27" s="126">
         <f t="shared" si="6"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J27" s="126" t="e">
+        <v>4832.9229955500005</v>
+      </c>
+      <c r="J27" s="126">
         <f t="shared" si="6"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K27" s="126" t="e">
+        <v>4976.958521089502</v>
+      </c>
+      <c r="K27" s="126">
         <f t="shared" si="6"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L27" s="126" t="e">
+        <v>4330.7175037260758</v>
+      </c>
+      <c r="L27" s="126">
         <f t="shared" si="6"/>
-        <v>#REF!</v>
+        <v>2647.169308350914</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -19290,25 +19081,25 @@
         <f t="shared" si="7"/>
         <v>965.96364838070076</v>
       </c>
-      <c r="H28" s="94" t="e">
+      <c r="H28" s="94">
         <f t="shared" si="7"/>
-        <v>#REF!</v>
-      </c>
-      <c r="I28" s="94" t="e">
+        <v>3411.0177010273974</v>
+      </c>
+      <c r="I28" s="94">
         <f t="shared" si="7"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J28" s="94" t="e">
+        <v>4782.7022847623284</v>
+      </c>
+      <c r="J28" s="94">
         <f t="shared" si="7"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K28" s="94" t="e">
+        <v>5161.6377195239202</v>
+      </c>
+      <c r="K28" s="94">
         <f t="shared" si="7"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L28" s="94" t="e">
+        <v>4625.1537724725395</v>
+      </c>
+      <c r="L28" s="94">
         <f t="shared" si="7"/>
-        <v>#REF!</v>
+        <v>3045.6615068689116</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
@@ -19394,25 +19185,25 @@
         <f>Statement!Q99</f>
         <v>0.3517643179070023</v>
       </c>
-      <c r="H33" s="216" t="e">
+      <c r="H33" s="216">
         <f>H8/H6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I33" s="216" t="e">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="I33" s="216">
         <f t="shared" ref="I33:L33" si="9">I8/I6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J33" s="216" t="e">
+        <v>0.52</v>
+      </c>
+      <c r="J33" s="216">
         <f t="shared" si="9"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K33" s="216" t="e">
+        <v>0.53000000000000014</v>
+      </c>
+      <c r="K33" s="216">
         <f t="shared" si="9"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L33" s="216" t="e">
+        <v>0.51</v>
+      </c>
+      <c r="L33" s="216">
         <f t="shared" si="9"/>
-        <v>#REF!</v>
+        <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
@@ -19439,39 +19230,39 @@
         <f>Statement!Q100</f>
         <v>0.20776080026382324</v>
       </c>
-      <c r="H34" s="216" t="e">
+      <c r="H34" s="216">
         <f>H10/H6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I34" s="216" t="e">
+        <v>0.32499999999999996</v>
+      </c>
+      <c r="I34" s="216">
         <f t="shared" ref="I34:L34" si="10">I10/I6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J34" s="216" t="e">
+        <v>0.39</v>
+      </c>
+      <c r="J34" s="216">
         <f t="shared" si="10"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K34" s="216" t="e">
+        <v>0.38000000000000012</v>
+      </c>
+      <c r="K34" s="216">
         <f t="shared" si="10"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L34" s="216" t="e">
+        <v>0.34</v>
+      </c>
+      <c r="L34" s="216">
         <f t="shared" si="10"/>
-        <v>#REF!</v>
+        <v>0.23999999999999996</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19534,10 +19325,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="246" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="246"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19554,7 +19345,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>851.69</v>
+        <v>747.3</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19563,7 +19354,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>197592.08000000002</v>
+        <v>173373.59999999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19581,7 +19372,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.6789999999999998E-2</v>
+        <v>4.6039999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19622,10 +19413,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="246" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="243"/>
+      <c r="C15" s="246"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19633,7 +19424,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.9175490635430986E-2</v>
+        <v>2.1795723908041569E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19642,7 +19433,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.980824509364569</v>
+        <v>0.97820427609195848</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19660,7 +19451,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14111899999999999</v>
+        <v>0.14036899999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19669,7 +19460,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.13929159491793405</v>
+        <v>0.13830823610021858</v>
       </c>
     </row>
   </sheetData>
@@ -19714,20 +19505,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
+      <c r="D3" s="246"/>
+      <c r="E3" s="246"/>
+      <c r="F3" s="246"/>
       <c r="G3" s="255"/>
       <c r="H3" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
+      <c r="I3" s="246"/>
+      <c r="J3" s="246"/>
+      <c r="K3" s="246"/>
+      <c r="L3" s="246"/>
       <c r="P3" s="257"/>
       <c r="Q3" s="257"/>
       <c r="R3" s="257"/>
@@ -19852,25 +19643,25 @@
         <f>'FCF &amp; Other'!G28</f>
         <v>965.96364838070076</v>
       </c>
-      <c r="H7" s="112" t="e">
+      <c r="H7" s="112">
         <f>'FCF &amp; Other'!H28</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I7" s="112" t="e">
+        <v>3411.0177010273974</v>
+      </c>
+      <c r="I7" s="112">
         <f>'FCF &amp; Other'!I28</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J7" s="112" t="e">
+        <v>4782.7022847623284</v>
+      </c>
+      <c r="J7" s="112">
         <f>'FCF &amp; Other'!J28</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K7" s="112" t="e">
+        <v>5161.6377195239202</v>
+      </c>
+      <c r="K7" s="112">
         <f>'FCF &amp; Other'!K28</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L7" s="112" t="e">
+        <v>4625.1537724725395</v>
+      </c>
+      <c r="L7" s="112">
         <f>'FCF &amp; Other'!L28</f>
-        <v>#REF!</v>
+        <v>3045.6615068689116</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -19918,9 +19709,9 @@
       <c r="K8" s="126">
         <v>0</v>
       </c>
-      <c r="L8" s="126" t="e">
+      <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>#REF!</v>
+        <v>25070.072585901384</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19972,25 +19763,25 @@
       <c r="E10" s="137"/>
       <c r="F10" s="137"/>
       <c r="G10" s="138"/>
-      <c r="H10" s="126" t="e">
+      <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I10" s="126" t="e">
+        <v>2996.5677071030923</v>
+      </c>
+      <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J10" s="126" t="e">
+        <v>3691.0811317747316</v>
+      </c>
+      <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K10" s="126" t="e">
+        <v>3499.5152060894929</v>
+      </c>
+      <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L10" s="126" t="e">
+        <v>2754.7783660289747</v>
+      </c>
+      <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>#REF!</v>
+        <v>1593.6107242397616</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20007,16 +19798,16 @@
       <c r="I11" s="137"/>
       <c r="J11" s="137"/>
       <c r="K11" s="137"/>
-      <c r="L11" s="126" t="e">
+      <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>#REF!</v>
+        <v>13117.654880641754</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="243" t="s">
+      <c r="B13" s="246" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="243"/>
+      <c r="C13" s="246"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20032,40 +19823,40 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13929159491793405</v>
+        <v>0.13830823610021858</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="243" t="s">
+      <c r="B18" s="246" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="243"/>
+      <c r="C18" s="246"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C19" s="64" t="e">
+      <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>#REF!</v>
+        <v>14535.553135236052</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C20" s="64" t="e">
+      <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>#REF!</v>
+        <v>13117.654880641754</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="C21" s="94" t="e">
+      <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>#REF!</v>
+        <v>27653.208015877804</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20090,9 +19881,9 @@
       <c r="B24" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C24" s="94" t="e">
+      <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>#REF!</v>
+        <v>24936.208015877804</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20108,9 +19899,9 @@
       <c r="B26" s="141" t="s">
         <v>191</v>
       </c>
-      <c r="C26" s="142" t="e">
+      <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>#REF!</v>
+        <v>107.4836552408526</v>
       </c>
     </row>
   </sheetData>
@@ -20153,20 +19944,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
       <c r="G2" s="255"/>
       <c r="H2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20235,44 +20026,44 @@
         <v>19</v>
       </c>
       <c r="C6" s="92">
-        <f>Revenue!C9</f>
+        <f>Revenue!C8</f>
         <v>10681</v>
       </c>
       <c r="D6" s="92">
-        <f>Revenue!D9</f>
+        <f>Revenue!D8</f>
         <v>11661</v>
       </c>
       <c r="E6" s="92">
-        <f>Revenue!E9</f>
+        <f>Revenue!E8</f>
         <v>7384</v>
       </c>
       <c r="F6" s="92">
-        <f>Revenue!F9</f>
+        <f>Revenue!F8</f>
         <v>6551</v>
       </c>
       <c r="G6" s="93">
-        <f>Revenue!G9</f>
+        <f>Revenue!G8</f>
         <v>9097</v>
       </c>
-      <c r="H6" s="92" t="e">
-        <f>Revenue!H9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I6" s="92" t="e">
-        <f>Revenue!I9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J6" s="92" t="e">
-        <f>Revenue!J9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K6" s="92" t="e">
-        <f>Revenue!K9</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L6" s="92" t="e">
-        <f>Revenue!L9</f>
-        <v>#REF!</v>
+      <c r="H6" s="92">
+        <f>Revenue!H8</f>
+        <v>11833.7</v>
+      </c>
+      <c r="I6" s="92">
+        <f>Revenue!I8</f>
+        <v>15686.2155</v>
+      </c>
+      <c r="J6" s="92">
+        <f>Revenue!J8</f>
+        <v>16578.809197500002</v>
+      </c>
+      <c r="K6" s="92">
+        <f>Revenue!K8</f>
+        <v>16123.296737625002</v>
+      </c>
+      <c r="L6" s="92">
+        <f>Revenue!L8</f>
+        <v>13961.863440669378</v>
       </c>
       <c r="N6" s="91"/>
     </row>
@@ -20300,25 +20091,25 @@
         <f>'FCF &amp; Other'!G10</f>
         <v>1890</v>
       </c>
-      <c r="H7" s="92" t="e">
+      <c r="H7" s="92">
         <f>'FCF &amp; Other'!H10</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I7" s="92" t="e">
+        <v>3845.9524999999999</v>
+      </c>
+      <c r="I7" s="92">
         <f>'FCF &amp; Other'!I10</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J7" s="92" t="e">
+        <v>6117.6240450000005</v>
+      </c>
+      <c r="J7" s="92">
         <f>'FCF &amp; Other'!J10</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K7" s="92" t="e">
+        <v>6299.9474950500025</v>
+      </c>
+      <c r="K7" s="92">
         <f>'FCF &amp; Other'!K10</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L7" s="92" t="e">
+        <v>5481.9208907925013</v>
+      </c>
+      <c r="L7" s="92">
         <f>'FCF &amp; Other'!L10</f>
-        <v>#REF!</v>
+        <v>3350.8472257606504</v>
       </c>
       <c r="N7" s="91"/>
     </row>
@@ -20346,25 +20137,25 @@
         <f>'FCF &amp; Other'!G28</f>
         <v>965.96364838070076</v>
       </c>
-      <c r="H8" s="92" t="e">
+      <c r="H8" s="92">
         <f>'FCF &amp; Other'!H28</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I8" s="92" t="e">
+        <v>3411.0177010273974</v>
+      </c>
+      <c r="I8" s="92">
         <f>'FCF &amp; Other'!I28</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J8" s="92" t="e">
+        <v>4782.7022847623284</v>
+      </c>
+      <c r="J8" s="92">
         <f>'FCF &amp; Other'!J28</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K8" s="92" t="e">
+        <v>5161.6377195239202</v>
+      </c>
+      <c r="K8" s="92">
         <f>'FCF &amp; Other'!K28</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L8" s="92" t="e">
+        <v>4625.1537724725395</v>
+      </c>
+      <c r="L8" s="92">
         <f>'FCF &amp; Other'!L28</f>
-        <v>#REF!</v>
+        <v>3045.6615068689116</v>
       </c>
       <c r="N8" s="91"/>
     </row>
@@ -20453,25 +20244,25 @@
         <f t="shared" si="1"/>
         <v>0.38864295527400394</v>
       </c>
-      <c r="H12" s="95" t="e">
+      <c r="H12" s="95">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="I12" s="95" t="e">
+        <v>0.30083544025502923</v>
+      </c>
+      <c r="I12" s="95">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J12" s="95" t="e">
+        <v>0.32555460253344254</v>
+      </c>
+      <c r="J12" s="95">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K12" s="95" t="e">
+        <v>5.6903062277832546E-2</v>
+      </c>
+      <c r="K12" s="95">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L12" s="95" t="e">
+        <v>-2.7475583707404612E-2</v>
+      </c>
+      <c r="L12" s="95">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
+        <v>-0.13405653521911223</v>
       </c>
       <c r="N12" s="91"/>
     </row>
@@ -20502,25 +20293,25 @@
         <f t="shared" si="2"/>
         <v>3.1814159292035398</v>
       </c>
-      <c r="H13" s="95" t="e">
+      <c r="H13" s="95">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="I13" s="95" t="e">
+        <v>1.0348955026455027</v>
+      </c>
+      <c r="I13" s="95">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J13" s="95" t="e">
+        <v>0.59066552304013131</v>
+      </c>
+      <c r="J13" s="95">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K13" s="95" t="e">
+        <v>2.980298375788832E-2</v>
+      </c>
+      <c r="K13" s="95">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L13" s="95" t="e">
+        <v>-0.12984657489609897</v>
+      </c>
+      <c r="L13" s="95">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>-0.3887457895664323</v>
       </c>
       <c r="N13" s="91"/>
     </row>
@@ -20551,25 +20342,25 @@
         <f t="shared" si="3"/>
         <v>6.4948570043360304E-3</v>
       </c>
-      <c r="H14" s="95" t="e">
+      <c r="H14" s="95">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
-      </c>
-      <c r="I14" s="95" t="e">
+        <v>2.5312071077886609</v>
+      </c>
+      <c r="I14" s="95">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
-      </c>
-      <c r="J14" s="95" t="e">
+        <v>0.40213352845450789</v>
+      </c>
+      <c r="J14" s="95">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
-      </c>
-      <c r="K14" s="95" t="e">
+        <v>7.9230404110429087E-2</v>
+      </c>
+      <c r="K14" s="95">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
-      </c>
-      <c r="L14" s="95" t="e">
+        <v>-0.10393676894876359</v>
+      </c>
+      <c r="L14" s="95">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>-0.34150048696851315</v>
       </c>
       <c r="N14" s="91"/>
     </row>
@@ -20660,23 +20451,23 @@
       </c>
       <c r="H18" s="143">
         <f>G18*(1+H19)</f>
-        <v>234.36</v>
+        <v>221.34</v>
       </c>
       <c r="I18" s="143">
         <f t="shared" ref="I18:L18" si="5">H18*(1+I19)</f>
-        <v>250.76520000000002</v>
+        <v>225.76680000000002</v>
       </c>
       <c r="J18" s="143">
         <f t="shared" si="5"/>
-        <v>258.28815600000001</v>
+        <v>232.53980400000003</v>
       </c>
       <c r="K18" s="143">
         <f t="shared" si="5"/>
-        <v>263.45391912000002</v>
+        <v>237.19060008000002</v>
       </c>
       <c r="L18" s="143">
         <f t="shared" si="5"/>
-        <v>266.08845831120004</v>
+        <v>239.56250608080003</v>
       </c>
       <c r="N18" s="91"/>
     </row>
@@ -20702,10 +20493,10 @@
         <v>2.3584905660377409E-2</v>
       </c>
       <c r="H19" s="146">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="I19" s="97">
-        <v>7.0000000000000007E-2</v>
+        <v>0.02</v>
       </c>
       <c r="J19" s="97">
         <v>0.03</v>
@@ -21098,19 +20889,19 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="243" t="s">
+      <c r="B37" s="246" t="s">
         <v>204</v>
       </c>
-      <c r="C37" s="243"/>
+      <c r="C37" s="246"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C38" s="64" t="e">
+      <c r="C38" s="64">
         <f>L7</f>
-        <v>#REF!</v>
+        <v>3350.8472257606504</v>
       </c>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
@@ -21119,7 +20910,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13929159491793405</v>
+        <v>0.13830823610021858</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21127,25 +20918,25 @@
         <v>206</v>
       </c>
       <c r="C40" s="105">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C41" s="24" t="e">
+      <c r="C41" s="24">
         <f>(C38*C40)</f>
-        <v>#REF!</v>
+        <v>53613.555612170407</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C42" s="24" t="e">
+      <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>#REF!</v>
+        <v>23948.735668585578</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21170,9 +20961,9 @@
       <c r="B45" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C45" s="24" t="e">
+      <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>#REF!</v>
+        <v>21231.735668585578</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21188,24 +20979,24 @@
       <c r="B47" s="141" t="s">
         <v>208</v>
       </c>
-      <c r="C47" s="142" t="e">
+      <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>#REF!</v>
+        <v>91.516102019765427</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="243" t="s">
+      <c r="B49" s="246" t="s">
         <v>209</v>
       </c>
-      <c r="C49" s="243"/>
+      <c r="C49" s="246"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C50" s="64" t="e">
+      <c r="C50" s="64">
         <f>L6</f>
-        <v>#REF!</v>
+        <v>13961.863440669378</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
@@ -21214,7 +21005,7 @@
       </c>
       <c r="C51" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14111899999999999</v>
+        <v>0.14036899999999999</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21222,7 +21013,7 @@
         <v>211</v>
       </c>
       <c r="C52" s="105">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
@@ -21231,40 +21022,40 @@
       </c>
       <c r="C53" s="24">
         <f>L18</f>
-        <v>266.08845831120004</v>
+        <v>239.56250608080003</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C54" s="24" t="e">
+      <c r="C54" s="24">
         <f>(C50*C52)/C53</f>
-        <v>#REF!</v>
+        <v>174.84201099432855</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="141" t="s">
         <v>208</v>
       </c>
-      <c r="C55" s="142" t="e">
+      <c r="C55" s="142">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>#REF!</v>
+        <v>90.660639619070309</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="243" t="s">
+      <c r="B57" s="246" t="s">
         <v>326</v>
       </c>
-      <c r="C57" s="243"/>
+      <c r="C57" s="246"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C58" s="64" t="e">
+      <c r="C58" s="64">
         <f>L8</f>
-        <v>#REF!</v>
+        <v>3045.6615068689116</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
@@ -21273,7 +21064,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13929159491793405</v>
+        <v>0.13830823610021858</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21281,25 +21072,25 @@
         <v>353</v>
       </c>
       <c r="C60" s="105">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C61" s="24" t="e">
+      <c r="C61" s="24">
         <f>(C58*C60)</f>
-        <v>#REF!</v>
+        <v>60913.230137378232</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B62" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C62" s="24" t="e">
+      <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>#REF!</v>
+        <v>27768.214484795233</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21324,9 +21115,9 @@
       <c r="B65" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C65" s="24" t="e">
+      <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>#REF!</v>
+        <v>25051.214484795233</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21342,9 +21133,9 @@
       <c r="B67" s="141" t="s">
         <v>208</v>
       </c>
-      <c r="C67" s="142" t="e">
+      <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>#REF!</v>
+        <v>107.9793727792898</v>
       </c>
     </row>
   </sheetData>
@@ -21396,55 +21187,55 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="246" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="246"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C5" s="133" t="e">
+      <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>#REF!</v>
+        <v>107.4836552408526</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C6" s="133" t="e">
+      <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>#REF!</v>
+        <v>91.516102019765427</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C7" s="133" t="e">
+      <c r="C7" s="133">
         <f ca="1">Multiples!C55</f>
-        <v>#REF!</v>
+        <v>90.660639619070309</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C8" s="133" t="e">
+      <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>#REF!</v>
+        <v>107.9793727792898</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B9" s="141" t="s">
         <v>218</v>
       </c>
-      <c r="C9" s="142" t="e">
+      <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>#REF!</v>
+        <v>99.409942414744535</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21453,16 +21244,16 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>851.69</v>
+        <v>747.3</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C11" s="154" t="e">
+      <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>#REF!</v>
+        <v>-0.8669745183798413</v>
       </c>
     </row>
   </sheetData>
@@ -21518,20 +21309,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
       <c r="G2" s="255"/>
       <c r="H2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21894,10 +21685,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="243" t="s">
+      <c r="B20" s="246" t="s">
         <v>377</v>
       </c>
-      <c r="C20" s="243"/>
+      <c r="C20" s="246"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -21914,7 +21705,7 @@
         <v>379</v>
       </c>
       <c r="C22" s="233">
-        <v>0.5</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -21923,7 +21714,7 @@
       </c>
       <c r="C23" s="234">
         <f>C21*(1+C22)</f>
-        <v>4.29</v>
+        <v>2.9457999999999998</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.2">
@@ -21932,7 +21723,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14111899999999999</v>
+        <v>0.14036899999999999</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -21949,7 +21740,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C23/(C24-C25)</f>
-        <v>35.419711193124122</v>
+        <v>24.473078616587326</v>
       </c>
     </row>
   </sheetData>
@@ -21998,20 +21789,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
+      <c r="D3" s="246"/>
+      <c r="E3" s="246"/>
+      <c r="F3" s="246"/>
       <c r="G3" s="255"/>
       <c r="H3" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
+      <c r="I3" s="246"/>
+      <c r="J3" s="246"/>
+      <c r="K3" s="246"/>
+      <c r="L3" s="246"/>
       <c r="P3" s="257"/>
       <c r="Q3" s="257"/>
       <c r="R3" s="257"/>
@@ -22138,23 +21929,23 @@
       </c>
       <c r="H7" s="126">
         <f>G7*(1+$C$17)</f>
-        <v>1686.5725300727036</v>
+        <v>1931.9272967614015</v>
       </c>
       <c r="I7" s="126">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>2944.7556375069403</v>
+        <v>3863.854593522803</v>
       </c>
       <c r="J7" s="126">
         <f t="shared" si="0"/>
-        <v>5141.543343087118</v>
+        <v>7727.7091870456061</v>
       </c>
       <c r="K7" s="126">
         <f t="shared" si="0"/>
-        <v>8977.1346770301079</v>
+        <v>15455.418374091212</v>
       </c>
       <c r="L7" s="126">
         <f t="shared" si="0"/>
-        <v>15674.077146094569</v>
+        <v>30910.836748182424</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -22186,7 +21977,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>134020.83105699951</v>
+        <v>254439.60834786072</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22240,23 +22031,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>1480.3695011848056</v>
+        <v>1697.1917056315767</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>2268.7125583989355</v>
+        <v>2981.9545388620963</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>3476.872948623723</v>
+        <v>5239.2742919582288</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>5328.4165312694167</v>
+        <v>9205.3700848334265</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>8165.9649777953018</v>
+        <v>16173.774014621062</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22275,7 +22066,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>69822.893080449547</v>
+        <v>133132.88020354122</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22291,7 +22082,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>851.69</v>
+        <v>747.3</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22300,7 +22091,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>392.08138213268631</v>
+        <v>739.79216446181977</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22308,7 +22099,7 @@
         <v>328</v>
       </c>
       <c r="C17" s="158">
-        <v>0.746</v>
+        <v>1</v>
       </c>
       <c r="E17" s="260" t="s">
         <v>225</v>
@@ -22330,7 +22121,7 @@
         <v>184</v>
       </c>
       <c r="C20" s="160">
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
@@ -22339,7 +22130,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13929159491793405</v>
+        <v>0.13830823610021858</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22357,7 +22148,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>190778.56</v>
+        <v>167395.19999999998</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22384,7 +22175,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>193495.56</v>
+        <v>170112.19999999998</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22400,7 +22191,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>20720.336517272182</v>
+        <v>35297.56463590639</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22409,7 +22200,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>69822.893080449547</v>
+        <v>133132.88020354122</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22418,7 +22209,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>90543.229597721729</v>
+        <v>168430.44483944762</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22445,7 +22236,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>87826.229597721729</v>
+        <v>165713.44483944762</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22463,7 +22254,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>392.08138213268631</v>
+        <v>739.79216446181977</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -22548,23 +22339,23 @@
       </c>
       <c r="H41" s="143">
         <f t="shared" si="2"/>
-        <v>1686.5725300727036</v>
+        <v>1931.9272967614015</v>
       </c>
       <c r="I41" s="143">
         <f t="shared" si="2"/>
-        <v>2944.7556375069403</v>
+        <v>3863.854593522803</v>
       </c>
       <c r="J41" s="143">
         <f t="shared" si="2"/>
-        <v>5141.543343087118</v>
+        <v>7727.7091870456061</v>
       </c>
       <c r="K41" s="143">
         <f t="shared" si="2"/>
-        <v>8977.1346770301079</v>
+        <v>15455.418374091212</v>
       </c>
       <c r="L41" s="143">
         <f t="shared" si="2"/>
-        <v>15674.077146094569</v>
+        <v>30910.836748182424</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
@@ -22593,23 +22384,23 @@
       </c>
       <c r="H42" s="143">
         <f>H41/H43</f>
-        <v>1533.2477546115485</v>
+        <v>1756.2975425103648</v>
       </c>
       <c r="I42" s="143">
         <f t="shared" ref="I42:L42" si="3">I41/I43</f>
-        <v>2677.0505795517638</v>
+        <v>3512.5950850207296</v>
       </c>
       <c r="J42" s="143">
         <f t="shared" si="3"/>
-        <v>4674.1303118973792</v>
+        <v>7025.1901700414592</v>
       </c>
       <c r="K42" s="143">
         <f t="shared" si="3"/>
-        <v>8161.0315245728243</v>
+        <v>14050.380340082918</v>
       </c>
       <c r="L42" s="143">
         <f t="shared" si="3"/>
-        <v>14249.161041904152</v>
+        <v>28100.760680165837</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -22657,44 +22448,44 @@
         <v>19</v>
       </c>
       <c r="C44" s="112">
-        <f>Revenue!C9</f>
+        <f>Revenue!C8</f>
         <v>10681</v>
       </c>
       <c r="D44" s="112">
-        <f>Revenue!D9</f>
+        <f>Revenue!D8</f>
         <v>11661</v>
       </c>
       <c r="E44" s="112">
-        <f>Revenue!E9</f>
+        <f>Revenue!E8</f>
         <v>7384</v>
       </c>
       <c r="F44" s="112">
-        <f>Revenue!F9</f>
+        <f>Revenue!F8</f>
         <v>6551</v>
       </c>
       <c r="G44" s="113">
-        <f>Revenue!G9</f>
+        <f>Revenue!G8</f>
         <v>9097</v>
       </c>
       <c r="H44" s="143">
         <f>H41/H45</f>
-        <v>168657.25300727037</v>
+        <v>193192.72967614015</v>
       </c>
       <c r="I44" s="143">
         <f t="shared" ref="I44:L44" si="5">I41/I45</f>
-        <v>147237.78187534702</v>
+        <v>193192.72967614015</v>
       </c>
       <c r="J44" s="143">
         <f t="shared" si="5"/>
-        <v>122417.69864493137</v>
+        <v>183993.07588203822</v>
       </c>
       <c r="K44" s="143">
         <f t="shared" si="5"/>
-        <v>128244.7811004301</v>
+        <v>220791.69105844587</v>
       </c>
       <c r="L44" s="143">
         <f t="shared" si="5"/>
-        <v>104493.84764063047</v>
+        <v>206072.24498788285</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -22760,23 +22551,23 @@
       </c>
       <c r="H46" s="169">
         <f t="shared" si="7"/>
-        <v>0.746</v>
+        <v>1</v>
       </c>
       <c r="I46" s="169">
         <f t="shared" si="7"/>
-        <v>0.746</v>
+        <v>1</v>
       </c>
       <c r="J46" s="169">
         <f t="shared" si="7"/>
-        <v>0.74600000000000022</v>
+        <v>1</v>
       </c>
       <c r="K46" s="169">
         <f t="shared" si="7"/>
-        <v>0.746</v>
+        <v>1</v>
       </c>
       <c r="L46" s="169">
         <f t="shared" si="7"/>
-        <v>0.746</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.2">
@@ -22802,23 +22593,23 @@
       </c>
       <c r="H47" s="169">
         <f t="shared" si="7"/>
-        <v>-0.18875780179283141</v>
+        <v>-7.0742040999806965E-2</v>
       </c>
       <c r="I47" s="169">
         <f t="shared" si="7"/>
-        <v>0.746</v>
+        <v>1</v>
       </c>
       <c r="J47" s="169">
         <f t="shared" si="7"/>
-        <v>0.74599999999999977</v>
+        <v>1</v>
       </c>
       <c r="K47" s="169">
         <f t="shared" si="7"/>
-        <v>0.746</v>
+        <v>1</v>
       </c>
       <c r="L47" s="169">
         <f t="shared" si="7"/>
-        <v>0.746</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.2">
@@ -22844,23 +22635,23 @@
       </c>
       <c r="H48" s="169">
         <f t="shared" si="8"/>
-        <v>17.539876113803491</v>
+        <v>20.236971493474787</v>
       </c>
       <c r="I48" s="169">
         <f t="shared" si="8"/>
-        <v>-0.12700000000000011</v>
+        <v>0</v>
       </c>
       <c r="J48" s="169">
         <f t="shared" si="8"/>
-        <v>-0.16857142857142859</v>
+        <v>-4.7619047619047783E-2</v>
       </c>
       <c r="K48" s="169">
         <f t="shared" si="8"/>
-        <v>4.7600000000000087E-2</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="L48" s="169">
         <f t="shared" si="8"/>
-        <v>-0.18519999999999981</v>
+        <v>-6.6666666666666541E-2</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
@@ -22889,7 +22680,7 @@
       </c>
       <c r="H49" s="169">
         <f t="shared" si="9"/>
-        <v>9.0909090909090887E-3</v>
+        <v>9.0909090909090905E-3</v>
       </c>
       <c r="I49" s="169">
         <f t="shared" si="9"/>
@@ -22897,7 +22688,7 @@
       </c>
       <c r="J49" s="169">
         <f t="shared" si="9"/>
-        <v>3.8181818181818178E-2</v>
+        <v>3.8181818181818185E-2</v>
       </c>
       <c r="K49" s="169">
         <f t="shared" si="9"/>
@@ -22910,17 +22701,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29429,7 +29220,7 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>851.69</v>
+        <v>747.3</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29476,7 +29267,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>851.69</v>
+        <v>747.3</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30782,7 +30573,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>80.805502846299817</v>
+        <v>70.901328273244786</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -30819,7 +30610,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>17.424448001816529</v>
+        <v>15.28876702997275</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -30856,7 +30647,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>174.22699543378997</v>
+        <v>152.87232876712329</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30893,7 +30684,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="143">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>197592.08000000002</v>
+        <v>173373.59999999998</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30930,7 +30721,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="143">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>200309.08000000002</v>
+        <v>176090.59999999998</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30967,7 +30758,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="183">
         <f ca="1">AC152/AC5</f>
-        <v>18.193376930063579</v>
+        <v>15.993696639418708</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31004,7 +30795,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="183">
         <f ca="1">AC152/AC11</f>
-        <v>64.553361263293596</v>
+        <v>56.748501450209467</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31139,7 +30930,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="95">AC151/AC155</f>
-        <v>90.06020054694622</v>
+        <v>79.021695533272549</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31176,7 +30967,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="95"/>
-        <v>81.050226528490313</v>
+        <v>71.250804105024955</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31213,7 +31004,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="98">AC155/AC151</f>
-        <v>1.1103683912836991E-2</v>
+        <v>1.2654752511339675E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31250,7 +31041,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.2375394803273489E-2</v>
+        <v>1.4104108122574602E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31287,7 +31078,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">AC81/AC115</f>
-        <v>3.4284774976810809E-3</v>
+        <v>3.9073999732369864E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31324,7 +31115,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="154">
         <f ca="1">-AC62/AC151</f>
-        <v>2.9859496392770394E-4</v>
+        <v>3.4030555978534221E-4</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31361,7 +31152,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="154">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>3.4414334825565878E-3</v>
+        <v>3.9221657737971644E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31864,7 +31655,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="154">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-1.3750551135450368E-2</v>
+        <v>-1.56713594226572E-2</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -32214,7 +32005,7 @@
     </row>
     <row r="185" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B185" s="20" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C185" s="62"/>
       <c r="D185" s="62"/>
@@ -32272,7 +32063,7 @@
     </row>
     <row r="186" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B186" s="20" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C186" s="62"/>
       <c r="D186" s="62"/>
@@ -32746,7 +32537,7 @@
     </row>
     <row r="205" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B205" s="20" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C205" s="62"/>
       <c r="D205" s="62"/>
@@ -32804,7 +32595,7 @@
     </row>
     <row r="206" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B206" s="235" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C206" s="62"/>
       <c r="D206" s="62"/>
@@ -32862,7 +32653,7 @@
     </row>
     <row r="207" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B207" s="235" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C207" s="62"/>
       <c r="D207" s="62"/>
@@ -32947,7 +32738,7 @@
     </row>
     <row r="209" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B209" s="236" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C209" s="62"/>
       <c r="D209" s="62"/>
@@ -33097,15 +32888,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="246" t="s">
         <v>237</v>
       </c>
-      <c r="C4" s="243"/>
-      <c r="E4" s="243" t="s">
+      <c r="C4" s="246"/>
+      <c r="E4" s="246" t="s">
         <v>244</v>
       </c>
-      <c r="F4" s="243"/>
-      <c r="G4" s="243"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33113,7 +32904,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>851.69</v>
+        <v>747.3</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33129,7 +32920,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>197592.08000000002</v>
+        <v>173373.59999999998</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33149,7 +32940,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>200309.08000000002</v>
+        <v>176090.59999999998</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33169,7 +32960,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>80.805502846299817</v>
+        <v>70.901328273244786</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -33189,7 +32980,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>17.424448001816529</v>
+        <v>15.28876702997275</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -33209,7 +33000,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>174.22699543378997</v>
+        <v>152.87232876712329</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33229,7 +33020,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>18.193376930063579</v>
+        <v>15.993696639418708</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33238,18 +33029,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>64.553361263293596</v>
+        <v>56.748501450209467</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="246" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="243"/>
-      <c r="E15" s="243" t="s">
+      <c r="C15" s="246"/>
+      <c r="E15" s="246" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="243"/>
+      <c r="F15" s="246"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33300,14 +33091,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="243" t="s">
+      <c r="B21" s="246" t="s">
         <v>249</v>
       </c>
-      <c r="C21" s="243"/>
-      <c r="E21" s="243" t="s">
+      <c r="C21" s="246"/>
+      <c r="E21" s="246" t="s">
         <v>253</v>
       </c>
-      <c r="F21" s="243"/>
+      <c r="F21" s="246"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33376,14 +33167,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="243" t="s">
+      <c r="B29" s="246" t="s">
         <v>254</v>
       </c>
-      <c r="C29" s="243"/>
-      <c r="E29" s="243" t="s">
+      <c r="C29" s="246"/>
+      <c r="E29" s="246" t="s">
         <v>260</v>
       </c>
-      <c r="F29" s="243"/>
+      <c r="F29" s="246"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33459,14 +33250,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="243" t="s">
+      <c r="B37" s="246" t="s">
         <v>272</v>
       </c>
-      <c r="C37" s="243"/>
-      <c r="E37" s="243" t="s">
+      <c r="C37" s="246"/>
+      <c r="E37" s="246" t="s">
         <v>275</v>
       </c>
-      <c r="F37" s="243"/>
+      <c r="F37" s="246"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33474,7 +33265,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>1.2375394803273489E-2</v>
+        <v>1.4104108122574602E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -33490,7 +33281,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC159</f>
-        <v>1.1103683912836991E-2</v>
+        <v>1.2654752511339675E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -33506,7 +33297,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>3.4284774976810809E-3</v>
+        <v>3.9073999732369864E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>277</v>
@@ -33522,7 +33313,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>2.9859496392770394E-4</v>
+        <v>3.4030555978534221E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33531,18 +33322,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>3.4414334825565878E-3</v>
+        <v>3.9221657737971644E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="243" t="s">
+      <c r="B45" s="246" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="243"/>
-      <c r="E45" s="243" t="s">
+      <c r="C45" s="246"/>
+      <c r="E45" s="246" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="243"/>
+      <c r="F45" s="246"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33575,18 +33366,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC174</f>
-        <v>-1.3750551135450368E-2</v>
+        <v>-1.56713594226572E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="243" t="s">
+      <c r="B51" s="246" t="s">
         <v>286</v>
       </c>
-      <c r="C51" s="243"/>
-      <c r="E51" s="243" t="s">
+      <c r="C51" s="246"/>
+      <c r="E51" s="246" t="s">
         <v>307</v>
       </c>
-      <c r="F51" s="243"/>
+      <c r="F51" s="246"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33754,7 +33545,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC114</f>
-        <v>851.69</v>
+        <v>747.3</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33783,7 +33574,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>197592.08000000002</v>
+        <v>173373.59999999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33812,7 +33603,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>200309.08000000002</v>
+        <v>176090.59999999998</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33841,7 +33632,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>80.805502846299817</v>
+        <v>70.901328273244786</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33870,7 +33661,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>17.424448001816529</v>
+        <v>15.28876702997275</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33899,7 +33690,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>174.22699543378997</v>
+        <v>152.87232876712329</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33928,7 +33719,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>18.193376930063579</v>
+        <v>15.993696639418708</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33957,7 +33748,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>64.553361263293596</v>
+        <v>56.748501450209467</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34730,7 +34521,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>1.2375394803273489E-2</v>
+        <v>1.4104108122574602E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34759,7 +34550,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC159</f>
-        <v>1.1103683912836991E-2</v>
+        <v>1.2654752511339675E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34788,7 +34579,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>3.4284774976810809E-3</v>
+        <v>3.9073999732369864E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34817,7 +34608,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>2.9859496392770394E-4</v>
+        <v>3.4030555978534221E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34846,7 +34637,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>3.4414334825565878E-3</v>
+        <v>3.9221657737971644E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35082,7 +34873,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC174</f>
-        <v>-1.3750551135450368E-2</v>
+        <v>-1.56713594226572E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35544,14 +35335,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="247" t="s">
+      <c r="C3" s="249" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="F3" s="249" t="s">
+      <c r="D3" s="250"/>
+      <c r="F3" s="251" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="248"/>
+      <c r="G3" s="250"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35618,19 +35409,19 @@
       <c r="B7" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="250">
+      <c r="C7" s="247">
         <f>Statement!AA88</f>
         <v>0.10159292035398231</v>
       </c>
-      <c r="D7" s="251"/>
-      <c r="F7" s="250">
+      <c r="D7" s="248"/>
+      <c r="F7" s="247">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.44074074074074077</v>
       </c>
-      <c r="G7" s="251"/>
+      <c r="G7" s="248"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -35657,19 +35448,19 @@
       <c r="B9" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="250">
+      <c r="C9" s="247">
         <f>Statement!AA89</f>
         <v>9.7028502122498486E-3</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="F9" s="250">
+      <c r="D9" s="248"/>
+      <c r="F9" s="247">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.18928571428571428</v>
       </c>
-      <c r="G9" s="251"/>
+      <c r="G9" s="248"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -35696,19 +35487,19 @@
       <c r="B11" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="250">
+      <c r="C11" s="247">
         <f>Statement!AA90</f>
         <v>0.23044217687074831</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="F11" s="250">
+      <c r="D11" s="248"/>
+      <c r="F11" s="247">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.90394736842105261</v>
       </c>
-      <c r="G11" s="251"/>
+      <c r="G11" s="248"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -35735,19 +35526,19 @@
       <c r="B13" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="250">
+      <c r="C13" s="247">
         <f>Statement!AA93</f>
         <v>0.34834834834834832</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="F13" s="250">
+      <c r="D13" s="248"/>
+      <c r="F13" s="247">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.36474164133738601</v>
       </c>
-      <c r="G13" s="251"/>
+      <c r="G13" s="248"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -35774,19 +35565,19 @@
       <c r="B15" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="250">
+      <c r="C15" s="247">
         <f>Statement!AA94</f>
         <v>0.18386714116251482</v>
       </c>
-      <c r="D15" s="251"/>
-      <c r="F15" s="250">
+      <c r="D15" s="248"/>
+      <c r="F15" s="247">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.3155452436194897</v>
       </c>
-      <c r="G15" s="251"/>
+      <c r="G15" s="248"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -35813,19 +35604,19 @@
       <c r="B17" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="250">
+      <c r="C17" s="247">
         <f>Statement!AA96</f>
         <v>0.26138279932546377</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="F17" s="250">
+      <c r="D17" s="248"/>
+      <c r="F17" s="247">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2</v>
       </c>
-      <c r="G17" s="251"/>
+      <c r="G17" s="248"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -35852,22 +35643,22 @@
       <c r="B19" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="250">
+      <c r="C19" s="247">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.3859649122807015E-3</v>
       </c>
-      <c r="D19" s="251"/>
-      <c r="F19" s="250">
+      <c r="D19" s="248"/>
+      <c r="F19" s="247">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>6.0185185185185182E-2</v>
       </c>
-      <c r="G19" s="251"/>
+      <c r="G19" s="248"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -35894,22 +35685,22 @@
       <c r="B21" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="250">
+      <c r="C21" s="247">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.25769230769230766</v>
       </c>
-      <c r="D21" s="251"/>
-      <c r="F21" s="250">
+      <c r="D21" s="248"/>
+      <c r="F21" s="247">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.0828025477707006</v>
       </c>
-      <c r="G21" s="251"/>
+      <c r="G21" s="248"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35958,22 +35749,22 @@
       <c r="B25" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="250">
+      <c r="C25" s="247">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.12410071942446044</v>
       </c>
-      <c r="D25" s="251"/>
-      <c r="F25" s="250">
+      <c r="D25" s="248"/>
+      <c r="F25" s="247">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.54798761609907121</v>
       </c>
-      <c r="G25" s="251"/>
+      <c r="G25" s="248"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36001,25 +35792,37 @@
       <c r="B27" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="250">
+      <c r="C27" s="247">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>1.8302828618968387E-2</v>
       </c>
-      <c r="D27" s="251"/>
-      <c r="F27" s="250">
+      <c r="D27" s="248"/>
+      <c r="F27" s="247">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.12293577981651377</v>
       </c>
-      <c r="G27" s="251"/>
+      <c r="G27" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
@@ -36030,18 +35833,6 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dumitrasadrian/MyStockData/Finance-StockLists/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6490C790-E03F-D04B-A0C7-ABF7C6A758C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB67C1B-6CD6-394D-A84B-01824F4B75CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="400" windowWidth="20480" windowHeight="12860" firstSheet="13" activeTab="20" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,7 +148,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -158,12 +179,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -1455,15 +1485,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
-    <numFmt numFmtId="168" formatCode="0.00_);\(0.00\)"/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0_);\(#,##0.0\)"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
-    <numFmt numFmtId="172" formatCode="0.0_);\(0.0\)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
+    <numFmt numFmtId="167" formatCode="0.00_);\(0.00\)"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="0.0_);\(0.0\)"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -2055,7 +2085,7 @@
   <cellXfs count="261">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2093,10 +2123,10 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="38" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2107,9 +2137,9 @@
     <xf numFmtId="38" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="7" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -2124,7 +2154,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2132,10 +2162,10 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="8" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2144,15 +2174,15 @@
     </xf>
     <xf numFmtId="37" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="7" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="7" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="7" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="7" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="10" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2184,16 +2214,16 @@
     <xf numFmtId="37" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="18" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="18" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="19" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="20" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="20" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="20" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="20" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="38" fontId="21" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="21" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2211,14 +2241,14 @@
     <xf numFmtId="37" fontId="19" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="21" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="19" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="37" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="18" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="18" fillId="12" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="37" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="7" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2239,11 +2269,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -2251,9 +2281,9 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2264,7 +2294,7 @@
     <xf numFmtId="37" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2274,21 +2304,21 @@
     <xf numFmtId="2" fontId="10" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="7" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="7" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2297,13 +2327,13 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="17" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="17" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="18" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -2332,9 +2362,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="17" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="10" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
@@ -2370,11 +2400,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="170" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="37" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2388,10 +2418,10 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2433,7 +2463,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -2473,7 +2503,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2967,7 +2997,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3262,7 +3292,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3611,7 +3641,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4045,7 +4075,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4461,7 +4491,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4885,7 +4915,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5247,7 +5277,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5698,7 +5728,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6149,7 +6179,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12596,7 +12626,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a23rjc&amp;q=XNAS%3aSTX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12614,12 +12644,10 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>1145</v>
-    <v>138.30000000000001</v>
-    <v>2.0962000000000001</v>
-    <v>-69.69</v>
-    <v>-8.5300999999999988E-2</v>
-    <v>50.1</v>
-    <v>6.7041000000000003E-2</v>
+    <v>144.75</v>
+    <v>2.1261000000000001</v>
+    <v>18.899899999999999</v>
+    <v>2.2191000000000002E-2</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12627,35 +12655,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>121 Woodlands Avenue 5, 739009 SG</v>
-    <v>777.1</v>
+    <v>921.77549999999997</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46231.99999451328</v>
+    <v>46234.70431959453</v>
     <v>0</v>
-    <v>698.99</v>
-    <v>169078194330</v>
+    <v>837.72839999999997</v>
+    <v>197621637300</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
-    <v>774.80499999999995</v>
-    <v>70.957899999999995</v>
-    <v>816.99</v>
-    <v>747.3</v>
-    <v>797.4</v>
-    <v>226252100</v>
+    <v>900.44</v>
+    <v>62.614100000000001</v>
+    <v>851.68</v>
+    <v>870.57989999999995</v>
+    <v>227000000</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>8941628</v>
-    <v>5133795</v>
+    <v>3232234</v>
+    <v>5503992</v>
     <v>2017</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12669,28 +12711,28 @@
     <v>Powered by Refinitiv</v>
     <v>47.14</v>
     <v>39.47</v>
-    <v>-0.37</v>
-    <v>-7.9719999999999999E-3</v>
+    <v>0.41</v>
+    <v>8.8710000000000004E-3</v>
     <v>US</v>
-    <v>46.35</v>
+    <v>46.86</v>
     <v>Index</v>
-    <v>3</v>
-    <v>45.88</v>
+    <v>6</v>
+    <v>46.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.3</v>
-    <v>46.41</v>
-    <v>46.04</v>
+    <v>46.69</v>
+    <v>46.22</v>
+    <v>46.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12712,8 +12754,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12734,7 +12774,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12744,6 +12783,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12779,7 +12823,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12790,16 +12834,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12893,19 +12934,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -12977,9 +13012,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -12987,9 +13019,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13026,7 +13055,7 @@
       <x:numFmt numFmtId="0" formatCode="General"/>
     </x:dxf>
     <x:dxf>
-      <x:numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+      <x:numFmt numFmtId="27" formatCode="m/d/yy\ h:mm"/>
     </x:dxf>
     <x:dxf>
       <x:numFmt numFmtId="14" formatCode="0.00%"/>
@@ -13506,7 +13535,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC151</f>
-        <v>173373.59999999998</v>
+        <v>201974.5368</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13514,7 +13543,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>107.4836552408526</v>
+        <v>105.64014591596252</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13530,7 +13559,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC152</f>
-        <v>176090.59999999998</v>
+        <v>204691.5368</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13538,7 +13567,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>91.516102019765427</v>
+        <v>90.361973679717593</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13547,7 +13576,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>747.3</v>
+        <v>870.57989999999995</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>247</v>
@@ -13562,23 +13591,23 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>90.660639619070309</v>
+        <v>89.895169309350294</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>797.4</v>
+      <c r="C6" s="208" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC148</f>
-        <v>70.901328273244786</v>
+        <v>82.597713472485765</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13586,7 +13615,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>107.9793727792898</v>
+        <v>106.66810579871586</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13595,14 +13624,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-69.69</v>
+        <v>18.899899999999999</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC149</f>
-        <v>15.28876702997275</v>
+        <v>17.810910306539508</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13610,23 +13639,23 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>99.409942414744535</v>
+        <v>98.14134867593657</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>50.1</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC159</f>
-        <v>1.2654752511339675E-2</v>
+        <v>1.0862755448091711E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13634,7 +13663,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.8669745183798413</v>
+        <v>-0.88726899314360852</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13643,37 +13672,37 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-8.5300999999999988E-2</v>
+        <v>2.2191000000000002E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC160</f>
-        <v>1.4104108122574602E-2</v>
+        <v>1.210687267188227E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>6.7041000000000003E-2</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>3.4030555978534221E-4</v>
+        <v>2.9211603073719738E-4</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>372</v>
       </c>
       <c r="I10" s="212">
         <f ca="1">DDM!C26</f>
-        <v>24.473078616587326</v>
+        <v>24.08578588686434</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13689,7 +13718,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC161</f>
-        <v>3.9073999732369864E-3</v>
+        <v>3.3540861671628305E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13698,7 +13727,7 @@
       </c>
       <c r="C12" s="209" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>138.30000000000001</v>
+        <v>144.75</v>
       </c>
       <c r="E12" s="185" t="s">
         <v>101</v>
@@ -13714,7 +13743,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.0962000000000001</v>
+        <v>2.1261000000000001</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>103</v>
@@ -13730,7 +13759,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5133795</v>
+        <v>5503992</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>104</v>
@@ -13746,7 +13775,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-1.56713594226572E-2</v>
+        <v>-1.345219077140619E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13851,12 +13880,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="2">
+      <c r="E26" s="185" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>46.04</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13871,7 +13900,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.6039999999999998E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14652,43 +14681,43 @@
         <v>122</v>
       </c>
       <c r="C11" s="12">
-        <f>C5</f>
+        <f t="shared" ref="C11:L11" si="4">C5</f>
         <v>2021</v>
       </c>
       <c r="D11" s="12">
-        <f>D5</f>
+        <f t="shared" si="4"/>
         <v>2022</v>
       </c>
       <c r="E11" s="12">
-        <f>E5</f>
+        <f t="shared" si="4"/>
         <v>2023</v>
       </c>
       <c r="F11" s="12">
-        <f>F5</f>
+        <f t="shared" si="4"/>
         <v>2024</v>
       </c>
       <c r="G11" s="12">
-        <f>G5</f>
+        <f t="shared" si="4"/>
         <v>2025</v>
       </c>
       <c r="H11" s="12">
-        <f>H5</f>
+        <f t="shared" si="4"/>
         <v>2026</v>
       </c>
       <c r="I11" s="12">
-        <f>I5</f>
+        <f t="shared" si="4"/>
         <v>2027</v>
       </c>
       <c r="J11" s="12">
-        <f>J5</f>
+        <f t="shared" si="4"/>
         <v>2028</v>
       </c>
       <c r="K11" s="12">
-        <f>K5</f>
+        <f t="shared" si="4"/>
         <v>2029</v>
       </c>
       <c r="L11" s="12">
-        <f>L5</f>
+        <f t="shared" si="4"/>
         <v>2030</v>
       </c>
       <c r="O11" s="5"/>
@@ -14697,47 +14726,47 @@
         <v>122</v>
       </c>
       <c r="S11" s="12" t="str">
-        <f>S5</f>
+        <f t="shared" ref="S11:AC11" si="5">S5</f>
         <v>Q4 2024</v>
       </c>
       <c r="T11" s="12" t="str">
-        <f>T5</f>
+        <f t="shared" si="5"/>
         <v>Q1 2025</v>
       </c>
       <c r="U11" s="12" t="str">
-        <f>U5</f>
+        <f t="shared" si="5"/>
         <v>Q2 2025</v>
       </c>
       <c r="V11" s="12" t="str">
-        <f>V5</f>
+        <f t="shared" si="5"/>
         <v>Q3 2025</v>
       </c>
       <c r="W11" s="12" t="str">
-        <f>W5</f>
+        <f t="shared" si="5"/>
         <v>Q4 2025</v>
       </c>
       <c r="X11" s="12" t="str">
-        <f>X5</f>
+        <f t="shared" si="5"/>
         <v>Q1 2026</v>
       </c>
       <c r="Y11" s="12" t="str">
-        <f>Y5</f>
+        <f t="shared" si="5"/>
         <v>Q2 2026</v>
       </c>
       <c r="Z11" s="12" t="str">
-        <f>Z5</f>
+        <f t="shared" si="5"/>
         <v>Q3 2026</v>
       </c>
       <c r="AA11" s="12" t="str">
-        <f>AA5</f>
+        <f t="shared" si="5"/>
         <v>FQ1</v>
       </c>
       <c r="AB11" s="12" t="str">
-        <f>AB5</f>
+        <f t="shared" si="5"/>
         <v>FQ2</v>
       </c>
       <c r="AC11" s="12" t="str">
-        <f>AC5</f>
+        <f t="shared" si="5"/>
         <v>FQ3</v>
       </c>
     </row>
@@ -14748,39 +14777,39 @@
       </c>
       <c r="C12" s="47"/>
       <c r="D12" s="95" t="e">
-        <f>D6/C6-1</f>
+        <f t="shared" ref="D12:L12" si="6">D6/C6-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E12" s="95" t="e">
-        <f>E6/D6-1</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F12" s="95" t="e">
-        <f>F6/E6-1</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G12" s="96" t="e">
-        <f>G6/F6-1</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H12" s="95">
-        <f>H6/G6-1</f>
+        <f t="shared" si="6"/>
         <v>0.32500000000000018</v>
       </c>
       <c r="I12" s="95">
-        <f>I6/H6-1</f>
+        <f t="shared" si="6"/>
         <v>0.36499999999999999</v>
       </c>
       <c r="J12" s="95">
-        <f>J6/I6-1</f>
+        <f t="shared" si="6"/>
         <v>4.5000000000000151E-2</v>
       </c>
       <c r="K12" s="95">
-        <f>K6/J6-1</f>
+        <f t="shared" si="6"/>
         <v>-5.0000000000000044E-2</v>
       </c>
       <c r="L12" s="95">
-        <f>L6/K6-1</f>
+        <f t="shared" si="6"/>
         <v>-0.14499999999999991</v>
       </c>
       <c r="O12" s="5"/>
@@ -14791,35 +14820,35 @@
       </c>
       <c r="S12" s="47"/>
       <c r="T12" s="95" t="e">
-        <f>T6/S6-1</f>
+        <f t="shared" ref="T12:AA12" si="7">T6/S6-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U12" s="95">
-        <f>U6/T6-1</f>
+        <f t="shared" si="7"/>
         <v>9.7345132743362761E-2</v>
       </c>
       <c r="V12" s="95">
-        <f>V6/U6-1</f>
+        <f t="shared" si="7"/>
         <v>-6.9700460829493105E-2</v>
       </c>
       <c r="W12" s="95">
-        <f>W6/V6-1</f>
+        <f t="shared" si="7"/>
         <v>0.15356037151702795</v>
       </c>
       <c r="X12" s="95">
-        <f>X6/W6-1</f>
+        <f t="shared" si="7"/>
         <v>0.13472893183038104</v>
       </c>
       <c r="Y12" s="95">
-        <f>Y6/X6-1</f>
+        <f t="shared" si="7"/>
         <v>5.2034058656575288E-2</v>
       </c>
       <c r="Z12" s="96">
-        <f>Z6/Y6-1</f>
+        <f t="shared" si="7"/>
         <v>0.12410071942446033</v>
       </c>
       <c r="AA12" s="95">
-        <f>AA6/Z6-1</f>
+        <f t="shared" si="7"/>
         <v>8.1500000000000128E-2</v>
       </c>
       <c r="AB12" s="95"/>
@@ -14832,19 +14861,19 @@
       </c>
       <c r="C13" s="47"/>
       <c r="D13" s="95" t="e">
-        <f>D7/C7-1</f>
+        <f t="shared" ref="D13:G14" si="8">D7/C7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E13" s="95" t="e">
-        <f>E7/D7-1</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F13" s="95" t="e">
-        <f>F7/E7-1</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G13" s="96" t="e">
-        <f>G7/F7-1</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H13" s="97">
@@ -14870,31 +14899,31 @@
       </c>
       <c r="S13" s="47"/>
       <c r="T13" s="95" t="e">
-        <f>T7/S7-1</f>
+        <f t="shared" ref="T13:Z14" si="9">T7/S7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U13" s="95">
-        <f>U7/T7-1</f>
+        <f t="shared" si="9"/>
         <v>6.8376068376068133E-3</v>
       </c>
       <c r="V13" s="95">
-        <f>V7/U7-1</f>
+        <f t="shared" si="9"/>
         <v>-7.4702886247877798E-2</v>
       </c>
       <c r="W13" s="95">
-        <f>W7/V7-1</f>
+        <f t="shared" si="9"/>
         <v>6.6055045871559637E-2</v>
       </c>
       <c r="X13" s="95">
-        <f>X7/W7-1</f>
+        <f t="shared" si="9"/>
         <v>-0.11359724612736666</v>
       </c>
       <c r="Y13" s="95">
-        <f>Y7/X7-1</f>
+        <f t="shared" si="9"/>
         <v>0.16699029126213594</v>
       </c>
       <c r="Z13" s="96">
-        <f>Z7/Y7-1</f>
+        <f t="shared" si="9"/>
         <v>1.830282861896837E-2</v>
       </c>
       <c r="AA13" s="97">
@@ -14910,19 +14939,19 @@
       </c>
       <c r="C14" s="47"/>
       <c r="D14" s="103">
-        <f>D8/C8-1</f>
+        <f t="shared" si="8"/>
         <v>9.1751708641512941E-2</v>
       </c>
       <c r="E14" s="103">
-        <f>E8/D8-1</f>
+        <f t="shared" si="8"/>
         <v>-0.36677814938684505</v>
       </c>
       <c r="F14" s="103">
-        <f>F8/E8-1</f>
+        <f t="shared" si="8"/>
         <v>-0.11281148429035748</v>
       </c>
       <c r="G14" s="104">
-        <f>G8/F8-1</f>
+        <f t="shared" si="8"/>
         <v>0.38864295527400405</v>
       </c>
       <c r="H14" s="103">
@@ -14953,31 +14982,31 @@
       </c>
       <c r="S14" s="47"/>
       <c r="T14" s="103">
-        <f>T8/S8-1</f>
+        <f t="shared" si="9"/>
         <v>0.14891361950185478</v>
       </c>
       <c r="U14" s="103">
-        <f>U8/T8-1</f>
+        <f t="shared" si="9"/>
         <v>7.2416974169741799E-2</v>
       </c>
       <c r="V14" s="103">
-        <f>V8/U8-1</f>
+        <f t="shared" si="9"/>
         <v>-7.096774193548383E-2</v>
       </c>
       <c r="W14" s="103">
-        <f>W8/V8-1</f>
+        <f t="shared" si="9"/>
         <v>0.13148148148148153</v>
       </c>
       <c r="X14" s="103">
-        <f>X8/W8-1</f>
+        <f t="shared" si="9"/>
         <v>7.5695581014729951E-2</v>
       </c>
       <c r="Y14" s="103">
-        <f>Y8/X8-1</f>
+        <f t="shared" si="9"/>
         <v>7.4553062000760839E-2</v>
       </c>
       <c r="Z14" s="104">
-        <f>Z8/Y8-1</f>
+        <f t="shared" si="9"/>
         <v>0.10159292035398226</v>
       </c>
       <c r="AA14" s="103">
@@ -15029,89 +15058,89 @@
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B18" s="16"/>
       <c r="C18" s="12">
-        <f>C5</f>
+        <f t="shared" ref="C18:L18" si="10">C5</f>
         <v>2021</v>
       </c>
       <c r="D18" s="12">
-        <f>D5</f>
+        <f t="shared" si="10"/>
         <v>2022</v>
       </c>
       <c r="E18" s="12">
-        <f>E5</f>
+        <f t="shared" si="10"/>
         <v>2023</v>
       </c>
       <c r="F18" s="12">
-        <f>F5</f>
+        <f t="shared" si="10"/>
         <v>2024</v>
       </c>
       <c r="G18" s="12">
-        <f>G5</f>
+        <f t="shared" si="10"/>
         <v>2025</v>
       </c>
       <c r="H18" s="12">
-        <f>H5</f>
+        <f t="shared" si="10"/>
         <v>2026</v>
       </c>
       <c r="I18" s="12">
-        <f>I5</f>
+        <f t="shared" si="10"/>
         <v>2027</v>
       </c>
       <c r="J18" s="12">
-        <f>J5</f>
+        <f t="shared" si="10"/>
         <v>2028</v>
       </c>
       <c r="K18" s="12">
-        <f>K5</f>
+        <f t="shared" si="10"/>
         <v>2029</v>
       </c>
       <c r="L18" s="12">
-        <f>L5</f>
+        <f t="shared" si="10"/>
         <v>2030</v>
       </c>
       <c r="O18" s="5"/>
       <c r="R18" s="16"/>
       <c r="S18" s="12" t="str">
-        <f>S5</f>
+        <f t="shared" ref="S18:AC18" si="11">S5</f>
         <v>Q4 2024</v>
       </c>
       <c r="T18" s="12" t="str">
-        <f>T5</f>
+        <f t="shared" si="11"/>
         <v>Q1 2025</v>
       </c>
       <c r="U18" s="12" t="str">
-        <f>U5</f>
+        <f t="shared" si="11"/>
         <v>Q2 2025</v>
       </c>
       <c r="V18" s="12" t="str">
-        <f>V5</f>
+        <f t="shared" si="11"/>
         <v>Q3 2025</v>
       </c>
       <c r="W18" s="12" t="str">
-        <f>W5</f>
+        <f t="shared" si="11"/>
         <v>Q4 2025</v>
       </c>
       <c r="X18" s="12" t="str">
-        <f>X5</f>
+        <f t="shared" si="11"/>
         <v>Q1 2026</v>
       </c>
       <c r="Y18" s="12" t="str">
-        <f>Y5</f>
+        <f t="shared" si="11"/>
         <v>Q2 2026</v>
       </c>
       <c r="Z18" s="12" t="str">
-        <f>Z5</f>
+        <f t="shared" si="11"/>
         <v>Q3 2026</v>
       </c>
       <c r="AA18" s="12" t="str">
-        <f>AA5</f>
+        <f t="shared" si="11"/>
         <v>FQ1</v>
       </c>
       <c r="AB18" s="12" t="str">
-        <f>AB5</f>
+        <f t="shared" si="11"/>
         <v>FQ2</v>
       </c>
       <c r="AC18" s="12" t="str">
-        <f>AC5</f>
+        <f t="shared" si="11"/>
         <v>FQ3</v>
       </c>
       <c r="AE18" s="8" t="str">
@@ -15149,19 +15178,19 @@
         <v>620.75</v>
       </c>
       <c r="I19" s="240">
-        <f t="shared" ref="I19:L19" si="4">H19*(1+I21)</f>
+        <f t="shared" ref="I19:L19" si="12">H19*(1+I21)</f>
         <v>806.97500000000002</v>
       </c>
       <c r="J19" s="240">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>887.67250000000013</v>
       </c>
       <c r="K19" s="240">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>887.67250000000013</v>
       </c>
       <c r="L19" s="240">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>798.90525000000014</v>
       </c>
       <c r="N19" s="90" t="s">
@@ -15248,19 +15277,19 @@
         <v>14.506161900926299</v>
       </c>
       <c r="I20" s="241">
-        <f t="shared" ref="I20:L20" si="5">H20*(1+I22)</f>
+        <f t="shared" ref="I20:L20" si="13">H20*(1+I22)</f>
         <v>15.231469995972615</v>
       </c>
       <c r="J20" s="241">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>14.469896496173984</v>
       </c>
       <c r="K20" s="241">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>13.746401671365284</v>
       </c>
       <c r="L20" s="241">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>13.059081587797019</v>
       </c>
       <c r="N20" s="90" t="s">
@@ -15271,7 +15300,7 @@
         <v>407</v>
       </c>
       <c r="R20" s="1" t="str">
-        <f t="shared" ref="R20" si="6">B20</f>
+        <f t="shared" ref="R20" si="14">B20</f>
         <v>Price per Exabyte</v>
       </c>
       <c r="S20" s="237">
@@ -15328,11 +15357,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="E21" s="95" t="e">
-        <f t="shared" ref="E21:F21" si="7">E19/D19-1</f>
+        <f t="shared" ref="E21:F21" si="15">E19/D19-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F21" s="95" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G21" s="96" t="e">
@@ -15365,27 +15394,27 @@
         <v>0.26666666666666661</v>
       </c>
       <c r="U21" s="95">
-        <f t="shared" ref="U21:Y21" si="8">U19/T19-1</f>
+        <f t="shared" ref="U21:Y21" si="16">U19/T19-1</f>
         <v>0.10526315789473695</v>
       </c>
       <c r="V21" s="95">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>-5.0793650793650835E-2</v>
       </c>
       <c r="W21" s="95">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>0.14548494983277593</v>
       </c>
       <c r="X21" s="95">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>0.16058394160583944</v>
       </c>
       <c r="Y21" s="95">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>3.7735849056603765E-2</v>
       </c>
       <c r="Z21" s="96">
-        <f t="shared" ref="Z21" si="9">Z19/Y19-1</f>
+        <f t="shared" ref="Z21" si="17">Z19/Y19-1</f>
         <v>6.3030303030302992E-2</v>
       </c>
       <c r="AA21" s="97">
@@ -15399,15 +15428,15 @@
       </c>
       <c r="C22" s="47"/>
       <c r="D22" s="95" t="e">
-        <f t="shared" ref="D22:F22" si="10">D20/C20-1</f>
+        <f t="shared" ref="D22:F22" si="18">D20/C20-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E22" s="95" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F22" s="95" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G22" s="96" t="e">
@@ -15436,31 +15465,31 @@
       </c>
       <c r="S22" s="47"/>
       <c r="T22" s="95" t="e">
-        <f t="shared" ref="T22:Y22" si="11">T20/S20-1</f>
+        <f t="shared" ref="T22:Y22" si="19">T20/S20-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U22" s="95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>-7.1639275179097295E-3</v>
       </c>
       <c r="V22" s="95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>-1.9918545689934231E-2</v>
       </c>
       <c r="W22" s="95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>7.0497841856680399E-3</v>
       </c>
       <c r="X22" s="95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>-2.2277587039231328E-2</v>
       </c>
       <c r="Y22" s="95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>1.3778274705426918E-2</v>
       </c>
       <c r="Z22" s="96">
-        <f t="shared" ref="Z22" si="12">Z20/Y20-1</f>
+        <f t="shared" ref="Z22" si="20">Z20/Y20-1</f>
         <v>5.7449365479110392E-2</v>
       </c>
       <c r="AA22" s="97">
@@ -19345,7 +19374,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>747.3</v>
+        <v>870.57989999999995</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19354,7 +19383,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>173373.59999999998</v>
+        <v>201974.5368</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19372,7 +19401,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.6039999999999998E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19381,7 +19410,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.0962000000000001</v>
+        <v>2.1261000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19424,7 +19453,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>2.1795723908041569E-2</v>
+        <v>1.8767228077323162E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19433,7 +19462,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.97820427609195848</v>
+        <v>0.98123277192267688</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19451,7 +19480,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14036899999999999</v>
+        <v>0.1423045</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19460,7 +19489,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.13830823610021858</v>
+        <v>0.14049375338257353</v>
       </c>
     </row>
   </sheetData>
@@ -19711,7 +19740,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>25070.072585901384</v>
+        <v>24633.468568334494</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19765,23 +19794,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>2996.5677071030923</v>
+        <v>2990.82541303774</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3691.0811317747316</v>
+        <v>3676.9483190385477</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3499.5152060894929</v>
+        <v>3479.4354712418976</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>2754.7783660289747</v>
+        <v>2733.7231627514634</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>1593.6107242397616</v>
+        <v>1578.400027265104</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -19800,7 +19829,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>13117.654880641754</v>
+        <v>12766.181459168549</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -19823,7 +19852,7 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13830823610021858</v>
+        <v>0.14049375338257353</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -19838,7 +19867,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>14535.553135236052</v>
+        <v>14459.332393334753</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -19847,7 +19876,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>13117.654880641754</v>
+        <v>12766.181459168549</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -19856,7 +19885,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>27653.208015877804</v>
+        <v>27225.513852503303</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -19883,7 +19912,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>24936.208015877804</v>
+        <v>24508.513852503303</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -19901,7 +19930,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>107.4836552408526</v>
+        <v>105.64014591596252</v>
       </c>
     </row>
   </sheetData>
@@ -20910,7 +20939,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13830823610021858</v>
+        <v>0.14049375338257353</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -20936,7 +20965,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>23948.735668585578</v>
+        <v>23680.977893694482</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -20963,7 +20992,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>21231.735668585578</v>
+        <v>20963.977893694482</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -20981,7 +21010,7 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>91.516102019765427</v>
+        <v>90.361973679717593</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21005,7 +21034,7 @@
       </c>
       <c r="C51" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14036899999999999</v>
+        <v>0.1423045</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21040,7 +21069,7 @@
       </c>
       <c r="C55" s="142">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>90.660639619070309</v>
+        <v>89.895169309350294</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -21064,7 +21093,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13830823610021858</v>
+        <v>0.14049375338257353</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21090,7 +21119,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>27768.214484795233</v>
+        <v>27464.000545302079</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21117,7 +21146,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>25051.214484795233</v>
+        <v>24747.000545302079</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21135,7 +21164,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>107.9793727792898</v>
+        <v>106.66810579871586</v>
       </c>
     </row>
   </sheetData>
@@ -21199,7 +21228,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>107.4836552408526</v>
+        <v>105.64014591596252</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21208,7 +21237,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>91.516102019765427</v>
+        <v>90.361973679717593</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21217,7 +21246,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C55</f>
-        <v>90.660639619070309</v>
+        <v>89.895169309350294</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21226,7 +21255,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>107.9793727792898</v>
+        <v>106.66810579871586</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21235,7 +21264,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>99.409942414744535</v>
+        <v>98.14134867593657</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21244,7 +21273,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>747.3</v>
+        <v>870.57989999999995</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21253,7 +21282,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.8669745183798413</v>
+        <v>-0.88726899314360852</v>
       </c>
     </row>
   </sheetData>
@@ -21723,7 +21752,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14036899999999999</v>
+        <v>0.1423045</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -21740,7 +21769,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C23/(C24-C25)</f>
-        <v>24.473078616587326</v>
+        <v>24.08578588686434</v>
       </c>
     </row>
   </sheetData>
@@ -21977,7 +22006,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>254439.60834786072</v>
+        <v>250008.45423563471</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22031,23 +22060,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>1697.1917056315767</v>
+        <v>1693.9393933824952</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>2981.9545388620963</v>
+        <v>2970.5369071219648</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>5239.2742919582288</v>
+        <v>5209.212059797248</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>9205.3700848334265</v>
+        <v>9135.0119969483803</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>16173.774014621062</v>
+        <v>16019.398562868028</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22066,7 +22095,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>133132.88020354122</v>
+        <v>129565.72819798155</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22082,7 +22111,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>747.3</v>
+        <v>870.57989999999995</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22091,7 +22120,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>739.79216446181977</v>
+        <v>722.66440677723062</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22130,7 +22159,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13830823610021858</v>
+        <v>0.14049375338257353</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22148,7 +22177,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>167395.19999999998</v>
+        <v>195009.8976</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22175,7 +22204,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>170112.19999999998</v>
+        <v>197726.8976</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22191,7 +22220,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>35297.56463590639</v>
+        <v>35028.098920118122</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22200,7 +22229,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>133132.88020354122</v>
+        <v>129565.72819798155</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22209,7 +22238,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>168430.44483944762</v>
+        <v>164593.82711809967</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22236,7 +22265,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>165713.44483944762</v>
+        <v>161876.82711809967</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22254,7 +22283,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>739.79216446181977</v>
+        <v>722.66440677723062</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -29210,17 +29239,33 @@
       <c r="Q114" s="26">
         <v>141.44</v>
       </c>
-      <c r="T114" s="68"/>
-      <c r="U114" s="68"/>
-      <c r="V114" s="68"/>
-      <c r="W114" s="68"/>
-      <c r="X114" s="68"/>
-      <c r="Y114" s="68"/>
-      <c r="Z114" s="68"/>
-      <c r="AA114" s="68"/>
+      <c r="T114" s="26">
+        <v>103.27</v>
+      </c>
+      <c r="U114" s="26">
+        <v>108.74</v>
+      </c>
+      <c r="V114" s="26">
+        <v>87.39</v>
+      </c>
+      <c r="W114" s="26">
+        <v>84.92</v>
+      </c>
+      <c r="X114" s="26">
+        <v>141.44</v>
+      </c>
+      <c r="Y114" s="26">
+        <v>252.79</v>
+      </c>
+      <c r="Z114" s="26">
+        <v>286.83999999999997</v>
+      </c>
+      <c r="AA114" s="26">
+        <v>375.01</v>
+      </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>747.3</v>
+        <v>870.57989999999995</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29257,17 +29302,41 @@
         <f>Q114/Q84</f>
         <v>141.44</v>
       </c>
-      <c r="T115" s="68"/>
-      <c r="U115" s="68"/>
-      <c r="V115" s="68"/>
-      <c r="W115" s="68"/>
-      <c r="X115" s="68"/>
-      <c r="Y115" s="68"/>
-      <c r="Z115" s="68"/>
-      <c r="AA115" s="68"/>
+      <c r="T115" s="65">
+        <f t="shared" ref="T115:AA115" si="69">T114/T84</f>
+        <v>103.27</v>
+      </c>
+      <c r="U115" s="65">
+        <f t="shared" si="69"/>
+        <v>108.74</v>
+      </c>
+      <c r="V115" s="65">
+        <f t="shared" si="69"/>
+        <v>87.39</v>
+      </c>
+      <c r="W115" s="65">
+        <f t="shared" si="69"/>
+        <v>84.92</v>
+      </c>
+      <c r="X115" s="65">
+        <f t="shared" si="69"/>
+        <v>141.44</v>
+      </c>
+      <c r="Y115" s="65">
+        <f t="shared" si="69"/>
+        <v>252.79</v>
+      </c>
+      <c r="Z115" s="65">
+        <f t="shared" si="69"/>
+        <v>286.83999999999997</v>
+      </c>
+      <c r="AA115" s="65">
+        <f t="shared" si="69"/>
+        <v>375.01</v>
+      </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>747.3</v>
+        <v>870.57989999999995</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29381,19 +29450,19 @@
         <v>101</v>
       </c>
       <c r="M121" s="76">
-        <f t="shared" ref="M121:P121" si="69">M119*M120</f>
+        <f t="shared" ref="M121:P121" si="70">M119*M120</f>
         <v>0.15146974063400578</v>
       </c>
       <c r="N121" s="76">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.18436940966010734</v>
       </c>
       <c r="O121" s="76">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-7.0010587612493388E-2</v>
       </c>
       <c r="P121" s="76">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>4.3287246414265401E-2</v>
       </c>
       <c r="Q121" s="76">
@@ -29455,19 +29524,19 @@
         <v>103</v>
       </c>
       <c r="M123" s="76">
-        <f t="shared" ref="M123:P123" si="70">M121*M122</f>
+        <f t="shared" ref="M123:P123" si="71">M121*M122</f>
         <v>2.0824088748019021</v>
       </c>
       <c r="N123" s="76">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>15.128440366972477</v>
       </c>
       <c r="O123" s="76">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.44120100083402836</v>
       </c>
       <c r="P123" s="76">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>-0.22468142186452042</v>
       </c>
       <c r="Q123" s="76">
@@ -29629,35 +29698,35 @@
       <c r="P129" s="49"/>
       <c r="Q129" s="49"/>
       <c r="T129" s="25">
-        <f t="shared" ref="T129:AA129" si="71">U5</f>
+        <f t="shared" ref="T129:AA129" si="72">U5</f>
         <v>2168</v>
       </c>
       <c r="U129" s="25">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>2325</v>
       </c>
       <c r="V129" s="25">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>2160</v>
       </c>
       <c r="W129" s="25">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>2444</v>
       </c>
       <c r="X129" s="25">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>2629</v>
       </c>
       <c r="Y129" s="25">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>2825</v>
       </c>
       <c r="Z129" s="25">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>3112</v>
       </c>
       <c r="AA129" s="25">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AC129" s="49"/>
@@ -29682,31 +29751,31 @@
       <c r="P130" s="49"/>
       <c r="Q130" s="49"/>
       <c r="T130" s="225" t="str">
-        <f t="shared" ref="T130:Z130" si="72">IF(T129&gt;T128, "BEAT", IF(T129&lt;T127, "MISSED", "MET"))</f>
+        <f t="shared" ref="T130:Z130" si="73">IF(T129&gt;T128, "BEAT", IF(T129&lt;T127, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
       <c r="U130" s="225" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>MET</v>
       </c>
       <c r="V130" s="225" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>MET</v>
       </c>
       <c r="W130" s="225" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>MET</v>
       </c>
       <c r="X130" s="225" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>MET</v>
       </c>
       <c r="Y130" s="225" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
       <c r="Z130" s="225" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
       <c r="AA130" s="225" t="str">
@@ -29825,35 +29894,35 @@
       <c r="P133" s="49"/>
       <c r="Q133" s="49"/>
       <c r="T133" s="229">
-        <f t="shared" ref="T133:AA133" si="73">U24</f>
+        <f t="shared" ref="T133:AA133" si="74">U24</f>
         <v>1.41</v>
       </c>
       <c r="U133" s="229">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>1.55</v>
       </c>
       <c r="V133" s="229">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>1.57</v>
       </c>
       <c r="W133" s="229">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>2.2400000000000002</v>
       </c>
       <c r="X133" s="229">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>2.4300000000000002</v>
       </c>
       <c r="Y133" s="229">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>2.6</v>
       </c>
       <c r="Z133" s="229">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>3.27</v>
       </c>
       <c r="AA133" s="229">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AC133" s="49"/>
@@ -29878,31 +29947,31 @@
       <c r="P134" s="49"/>
       <c r="Q134" s="49"/>
       <c r="T134" s="225" t="str">
-        <f t="shared" ref="T134:Z134" si="74">IF(T133&gt;T132, "BEAT", IF(T133&lt;T131, "MISSED", "MET"))</f>
+        <f t="shared" ref="T134:Z134" si="75">IF(T133&gt;T132, "BEAT", IF(T133&lt;T131, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
       <c r="U134" s="225" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>MET</v>
       </c>
       <c r="V134" s="225" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>MET</v>
       </c>
       <c r="W134" s="225" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>MET</v>
       </c>
       <c r="X134" s="225" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>BEAT</v>
       </c>
       <c r="Y134" s="225" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>MET</v>
       </c>
       <c r="Z134" s="225" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>MET</v>
       </c>
       <c r="AA134" s="225" t="str">
@@ -29995,55 +30064,55 @@
         <v>138</v>
       </c>
       <c r="M139" s="118">
-        <f t="shared" ref="M139:Q140" si="75">M29/M5*365</f>
+        <f t="shared" ref="M139:Q140" si="76">M29/M5*365</f>
         <v>39.572137440314577</v>
       </c>
       <c r="N139" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>47.953005745647879</v>
       </c>
       <c r="O139" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>30.696776814734559</v>
       </c>
       <c r="P139" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>23.902457640054951</v>
       </c>
       <c r="Q139" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>38.478069693305486</v>
       </c>
       <c r="T139" s="118">
-        <f t="shared" ref="T139:AA139" si="76">T29/T5*90</f>
+        <f t="shared" ref="T139:AA139" si="77">T29/T5*90</f>
         <v>20.461049284578696</v>
       </c>
       <c r="U139" s="118">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>26.070110701107012</v>
       </c>
       <c r="V139" s="118">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>22.722580645161294</v>
       </c>
       <c r="W139" s="118">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>25.916666666666668</v>
       </c>
       <c r="X139" s="118">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>35.315057283142387</v>
       </c>
       <c r="Y139" s="118">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>36.732597945987067</v>
       </c>
       <c r="Z139" s="118">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>39.69557522123894</v>
       </c>
       <c r="AA139" s="118">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>34.617609254498717</v>
       </c>
       <c r="AC139" s="118">
@@ -30056,55 +30125,55 @@
         <v>139</v>
       </c>
       <c r="M140" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>56.602266872746</v>
       </c>
       <c r="N140" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>69.7296142578125</v>
       </c>
       <c r="O140" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>68.97066136250622</v>
       </c>
       <c r="P140" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>90.176470588235304</v>
       </c>
       <c r="Q140" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>89.130066135323048</v>
       </c>
       <c r="T140" s="118">
-        <f t="shared" ref="T140:AA140" si="77">T30/T6*365</f>
+        <f t="shared" ref="T140:AA140" si="78">T30/T6*365</f>
         <v>351.38694638694642</v>
       </c>
       <c r="U140" s="118">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>347.17675378266847</v>
       </c>
       <c r="V140" s="118">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>355.35029742233974</v>
       </c>
       <c r="W140" s="118">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>383.77142857142854</v>
       </c>
       <c r="X140" s="118">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>343.52941176470586</v>
       </c>
       <c r="Y140" s="118">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>342.9899497487437</v>
       </c>
       <c r="Z140" s="118">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>331.57671315949062</v>
       </c>
       <c r="AA140" s="118">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>335.40540540540542</v>
       </c>
       <c r="AC140" s="118">
@@ -30137,35 +30206,35 @@
         <v>99.280990334068164</v>
       </c>
       <c r="T141" s="118">
-        <f t="shared" ref="T141:AA141" si="78">T37/T6*90</f>
+        <f t="shared" ref="T141:AA141" si="79">T37/T6*90</f>
         <v>124.89510489510489</v>
       </c>
       <c r="U141" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>110.05502063273727</v>
       </c>
       <c r="V141" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>93.212161269001996</v>
       </c>
       <c r="W141" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>94.30714285714285</v>
       </c>
       <c r="X141" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>94.352941176470594</v>
       </c>
       <c r="Y141" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>94.579145728643212</v>
       </c>
       <c r="Z141" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>96.658580958156449</v>
       </c>
       <c r="AA141" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>91.567567567567565</v>
       </c>
       <c r="AC141" s="118">
@@ -30182,55 +30251,55 @@
         <v>15.078963818470157</v>
       </c>
       <c r="N142" s="118">
-        <f t="shared" ref="N142:Q142" si="79">N139+N140-N141</f>
+        <f t="shared" ref="N142:Q142" si="80">N139+N140-N141</f>
         <v>25.987063362835386</v>
       </c>
       <c r="O142" s="118">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>2.6850082087342457</v>
       </c>
       <c r="P142" s="118">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>-15.90910766403276</v>
       </c>
       <c r="Q142" s="118">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>28.327145494560369</v>
       </c>
       <c r="T142" s="118">
-        <f t="shared" ref="T142" si="80">T139+T140-T141</f>
+        <f t="shared" ref="T142" si="81">T139+T140-T141</f>
         <v>246.95289077642019</v>
       </c>
       <c r="U142" s="118">
-        <f t="shared" ref="U142" si="81">U139+U140-U141</f>
+        <f t="shared" ref="U142" si="82">U139+U140-U141</f>
         <v>263.19184385103824</v>
       </c>
       <c r="V142" s="118">
-        <f t="shared" ref="V142" si="82">V139+V140-V141</f>
+        <f t="shared" ref="V142" si="83">V139+V140-V141</f>
         <v>284.86071679849908</v>
       </c>
       <c r="W142" s="118">
-        <f t="shared" ref="W142" si="83">W139+W140-W141</f>
+        <f t="shared" ref="W142" si="84">W139+W140-W141</f>
         <v>315.38095238095241</v>
       </c>
       <c r="X142" s="118">
-        <f t="shared" ref="X142" si="84">X139+X140-X141</f>
+        <f t="shared" ref="X142" si="85">X139+X140-X141</f>
         <v>284.49152787137763</v>
       </c>
       <c r="Y142" s="118">
-        <f t="shared" ref="Y142" si="85">Y139+Y140-Y141</f>
+        <f t="shared" ref="Y142" si="86">Y139+Y140-Y141</f>
         <v>285.14340196608759</v>
       </c>
       <c r="Z142" s="118">
-        <f t="shared" ref="Z142:AA142" si="86">Z139+Z140-Z141</f>
+        <f t="shared" ref="Z142:AA142" si="87">Z139+Z140-Z141</f>
         <v>274.6137074225731</v>
       </c>
       <c r="AA142" s="118">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>278.45544709233656</v>
       </c>
       <c r="AC142" s="118">
-        <f t="shared" ref="AC142" si="87">AC139+AC140-AC141</f>
+        <f t="shared" ref="AC142" si="88">AC139+AC140-AC141</f>
         <v>30.381753352650207</v>
       </c>
     </row>
@@ -30259,35 +30328,35 @@
         <v>-11.026490066225165</v>
       </c>
       <c r="T143" s="118">
-        <f t="shared" ref="T143:AA143" si="88">T106/T48</f>
+        <f t="shared" ref="T143:AA143" si="89">T106/T48</f>
         <v>-3.8054996646545942</v>
       </c>
       <c r="U143" s="118">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>-4.3661538461538463</v>
       </c>
       <c r="V143" s="118">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>-5.2632066728452269</v>
       </c>
       <c r="W143" s="118">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>-6.2074788902291917</v>
       </c>
       <c r="X143" s="118">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>-11.026490066225165</v>
       </c>
       <c r="Y143" s="118">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>-79.269841269841265</v>
       </c>
       <c r="Z143" s="118">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>9.8017429193899783</v>
       </c>
       <c r="AA143" s="118">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>3.5278538812785389</v>
       </c>
       <c r="AC143" s="118">
@@ -30320,35 +30389,35 @@
         <v>-9.0596026490066226</v>
       </c>
       <c r="T144" s="179">
-        <f t="shared" ref="T144:AA144" si="89">(T106-T105)/T48</f>
+        <f t="shared" ref="T144:AA144" si="90">(T106-T105)/T48</f>
         <v>-2.8947015425888667</v>
       </c>
       <c r="U144" s="179">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>-3.4130769230769231</v>
       </c>
       <c r="V144" s="179">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>-4.1158480074142725</v>
       </c>
       <c r="W144" s="179">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>-5.2255729794933652</v>
       </c>
       <c r="X144" s="179">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>-9.0596026490066226</v>
       </c>
       <c r="Y144" s="179">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>-61.61904761904762</v>
       </c>
       <c r="Z144" s="179">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>7.522875816993464</v>
       </c>
       <c r="AA144" s="179">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>2.4812785388127856</v>
       </c>
       <c r="AC144" s="179">
@@ -30381,35 +30450,35 @@
         <v>0.69864048338368578</v>
       </c>
       <c r="T145" s="118">
-        <f t="shared" ref="T145:AA145" si="90">(T105+T29)/T39</f>
+        <f t="shared" ref="T145:AA145" si="91">(T105+T29)/T39</f>
         <v>0.57663762504033556</v>
       </c>
       <c r="U145" s="118">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0.5906358747231889</v>
       </c>
       <c r="V145" s="118">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0.61468507915122939</v>
       </c>
       <c r="W145" s="118">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0.59535655058043113</v>
       </c>
       <c r="X145" s="118">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0.69864048338368578</v>
       </c>
       <c r="Y145" s="118">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0.53072625698324027</v>
       </c>
       <c r="Z145" s="118">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0.6094123903217229</v>
       </c>
       <c r="AA145" s="118">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0.72292502314100582</v>
       </c>
       <c r="AC145" s="118">
@@ -30442,35 +30511,35 @@
         <v>1.3795317220543806</v>
       </c>
       <c r="T146" s="118">
-        <f t="shared" ref="T146:AA146" si="91">T31/T39</f>
+        <f t="shared" ref="T146:AA146" si="92">T31/T39</f>
         <v>1.0751855437237818</v>
       </c>
       <c r="U146" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1.1414109459031951</v>
       </c>
       <c r="V146" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1.2334119232064669</v>
       </c>
       <c r="W146" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1.3606965174129353</v>
       </c>
       <c r="X146" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1.3795317220543806</v>
       </c>
       <c r="Y146" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.97935389846975951</v>
       </c>
       <c r="Z146" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1.1191172560489231</v>
       </c>
       <c r="AA146" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1.3264424560320889</v>
       </c>
       <c r="AC146" s="118">
@@ -30503,35 +30572,35 @@
         <v>6.3851351351351351</v>
       </c>
       <c r="T147" s="181">
-        <f t="shared" ref="T147:AA147" si="92">IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
+        <f t="shared" ref="T147:AA147" si="93">IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
         <v>4.1866666666666665</v>
       </c>
       <c r="U147" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>5.166666666666667</v>
       </c>
       <c r="V147" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>6.4210526315789478</v>
       </c>
       <c r="W147" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>5.904109589041096</v>
       </c>
       <c r="X147" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>8.2318840579710137</v>
       </c>
       <c r="Y147" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>9.506849315068493</v>
       </c>
       <c r="Z147" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>12.969230769230769</v>
       </c>
       <c r="AA147" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>16.096774193548388</v>
       </c>
       <c r="AC147" s="181">
@@ -30573,7 +30642,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>70.901328273244786</v>
+        <v>82.597713472485765</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -30610,7 +30679,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>15.28876702997275</v>
+        <v>17.810910306539508</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -30637,17 +30706,41 @@
         <f>Q115/(Statement!Q48/Statement!Q74)</f>
         <v>-66.504900662251657</v>
       </c>
-      <c r="T150" s="49"/>
-      <c r="U150" s="49"/>
-      <c r="V150" s="49"/>
-      <c r="W150" s="49"/>
-      <c r="X150" s="49"/>
-      <c r="Y150" s="49"/>
-      <c r="Z150" s="49"/>
-      <c r="AA150" s="49"/>
+      <c r="T150" s="72">
+        <f>T115/(Statement!T48/Statement!T74)</f>
+        <v>-14.545070422535211</v>
+      </c>
+      <c r="U150" s="72">
+        <f>U115/(Statement!U48/Statement!U74)</f>
+        <v>-17.732984615384616</v>
+      </c>
+      <c r="V150" s="72">
+        <f>V115/(Statement!V48/Statement!V74)</f>
+        <v>-17.170231696014827</v>
+      </c>
+      <c r="W150" s="72">
+        <f>W115/(Statement!W48/Statement!W74)</f>
+        <v>-21.716574185765982</v>
+      </c>
+      <c r="X150" s="72">
+        <f>X115/(Statement!X48/Statement!X74)</f>
+        <v>-66.504900662251657</v>
+      </c>
+      <c r="Y150" s="72">
+        <f>Y115/(Statement!Y48/Statement!Y74)</f>
+        <v>-858.68349206349205</v>
+      </c>
+      <c r="Z150" s="72">
+        <f>Z115/(Statement!Z48/Statement!Z74)</f>
+        <v>136.23337690631809</v>
+      </c>
+      <c r="AA150" s="72">
+        <f>AA115/(Statement!AA48/Statement!AA74)</f>
+        <v>76.714374429223753</v>
+      </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>152.87232876712329</v>
+        <v>178.0912306849315</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30674,17 +30767,41 @@
         <f>Statement!Q115*Statement!Q77</f>
         <v>30833.919999999998</v>
       </c>
-      <c r="T151" s="49"/>
-      <c r="U151" s="49"/>
-      <c r="V151" s="49"/>
-      <c r="W151" s="49"/>
-      <c r="X151" s="49"/>
-      <c r="Y151" s="49"/>
-      <c r="Z151" s="49"/>
-      <c r="AA151" s="49"/>
+      <c r="T151" s="143">
+        <f>Statement!T115*Statement!T77</f>
+        <v>21996.51</v>
+      </c>
+      <c r="U151" s="143">
+        <f>Statement!U115*Statement!U77</f>
+        <v>23596.579999999998</v>
+      </c>
+      <c r="V151" s="143">
+        <f>Statement!V115*Statement!V77</f>
+        <v>18963.63</v>
+      </c>
+      <c r="W151" s="143">
+        <f>Statement!W115*Statement!W77</f>
+        <v>18342.72</v>
+      </c>
+      <c r="X151" s="143">
+        <f>Statement!X115*Statement!X77</f>
+        <v>30833.919999999998</v>
+      </c>
+      <c r="Y151" s="143">
+        <f>Statement!Y115*Statement!Y77</f>
+        <v>57383.33</v>
+      </c>
+      <c r="Z151" s="143">
+        <f>Statement!Z115*Statement!Z77</f>
+        <v>65973.2</v>
+      </c>
+      <c r="AA151" s="143">
+        <f>Statement!AA115*Statement!AA77</f>
+        <v>87002.319999999992</v>
+      </c>
       <c r="AC151" s="143">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>173373.59999999998</v>
+        <v>201974.5368</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30711,17 +30828,41 @@
         <f>Q151+Q106-Q105+Q47+Q44</f>
         <v>34937.919999999998</v>
       </c>
-      <c r="T152" s="49"/>
-      <c r="U152" s="49"/>
-      <c r="V152" s="49"/>
-      <c r="W152" s="49"/>
-      <c r="X152" s="49"/>
-      <c r="Y152" s="49"/>
-      <c r="Z152" s="49"/>
-      <c r="AA152" s="49"/>
+      <c r="T152" s="143">
+        <f t="shared" ref="T152:AA152" si="94">T151+T106-T105+T47+T44</f>
+        <v>26312.51</v>
+      </c>
+      <c r="U152" s="143">
+        <f t="shared" si="94"/>
+        <v>28033.579999999998</v>
+      </c>
+      <c r="V152" s="143">
+        <f t="shared" si="94"/>
+        <v>23404.63</v>
+      </c>
+      <c r="W152" s="143">
+        <f t="shared" si="94"/>
+        <v>22674.720000000001</v>
+      </c>
+      <c r="X152" s="143">
+        <f t="shared" si="94"/>
+        <v>34937.919999999998</v>
+      </c>
+      <c r="Y152" s="143">
+        <f t="shared" si="94"/>
+        <v>61265.33</v>
+      </c>
+      <c r="Z152" s="143">
+        <f t="shared" si="94"/>
+        <v>69426.2</v>
+      </c>
+      <c r="AA152" s="143">
+        <f t="shared" si="94"/>
+        <v>89719.319999999992</v>
+      </c>
       <c r="AC152" s="143">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>176090.59999999998</v>
+        <v>204691.5368</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30758,7 +30899,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="183">
         <f ca="1">AC152/AC5</f>
-        <v>15.993696639418708</v>
+        <v>18.591420236148956</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30795,7 +30936,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="183">
         <f ca="1">AC152/AC11</f>
-        <v>56.748501450209467</v>
+        <v>65.965690235256204</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30823,35 +30964,35 @@
         <v>618</v>
       </c>
       <c r="T155" s="64">
-        <f t="shared" ref="T155:AA155" si="93">T58-T53+T108+T64</f>
+        <f t="shared" ref="T155:AA155" si="95">T58-T53+T108+T64</f>
         <v>0</v>
       </c>
       <c r="U155" s="64">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>-11</v>
       </c>
       <c r="V155" s="64">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>101</v>
       </c>
       <c r="W155" s="64">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>162</v>
       </c>
       <c r="X155" s="64">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>366</v>
       </c>
       <c r="Y155" s="64">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>375</v>
       </c>
       <c r="Z155" s="64">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>554</v>
       </c>
       <c r="AA155" s="64">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>899</v>
       </c>
       <c r="AC155" s="64">
@@ -30905,19 +31046,19 @@
         <v>19.701673228346458</v>
       </c>
       <c r="N157" s="72">
-        <f t="shared" ref="N157:Q157" si="94">N151/N155</f>
+        <f t="shared" ref="N157:Q157" si="96">N151/N155</f>
         <v>13.011644562334217</v>
       </c>
       <c r="O157" s="72">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>25.062798434442271</v>
       </c>
       <c r="P157" s="72">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>40.961843575418989</v>
       </c>
       <c r="Q157" s="72">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>49.893074433656956</v>
       </c>
       <c r="T157" s="49"/>
@@ -30929,8 +31070,8 @@
       <c r="Z157" s="49"/>
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
-        <f t="shared" ref="AC157:AC158" ca="1" si="95">AC151/AC155</f>
-        <v>79.021695533272549</v>
+        <f t="shared" ref="AC157:AC158" ca="1" si="97">AC151/AC155</f>
+        <v>92.057674020054691</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -30942,19 +31083,19 @@
         <v>19.801169652343109</v>
       </c>
       <c r="N158" s="72">
-        <f t="shared" ref="N158:Q158" si="96">N152/N156</f>
+        <f t="shared" ref="N158:Q158" si="98">N152/N156</f>
         <v>14.659365949397982</v>
       </c>
       <c r="O158" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>17.180029498525073</v>
       </c>
       <c r="P158" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>35.737599041631057</v>
       </c>
       <c r="Q158" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>40.813593878239608</v>
       </c>
       <c r="T158" s="49"/>
@@ -30966,8 +31107,8 @@
       <c r="Z158" s="49"/>
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
-        <f t="shared" ca="1" si="95"/>
-        <v>71.250804105024955</v>
+        <f t="shared" ca="1" si="97"/>
+        <v>82.823481721871062</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -30979,19 +31120,19 @@
         <v>5.0757110241845635E-2</v>
       </c>
       <c r="N159" s="74">
-        <f t="shared" ref="N159:Q159" si="97">N155/N151</f>
+        <f t="shared" ref="N159:Q159" si="99">N155/N151</f>
         <v>7.685423585076824E-2</v>
       </c>
       <c r="O159" s="74">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>3.9899774265660659E-2</v>
       </c>
       <c r="P159" s="74">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>2.4412963692876734E-2</v>
       </c>
       <c r="Q159" s="74">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>2.0042861887168417E-2</v>
       </c>
       <c r="T159" s="49"/>
@@ -31003,8 +31144,8 @@
       <c r="Z159" s="49"/>
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
-        <f t="shared" ref="AC159" ca="1" si="98">AC155/AC151</f>
-        <v>1.2654752511339675E-2</v>
+        <f t="shared" ref="AC159" ca="1" si="100">AC155/AC151</f>
+        <v>1.0862755448091711E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31041,7 +31182,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.4104108122574602E-2</v>
+        <v>1.210687267188227E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31078,7 +31219,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">AC81/AC115</f>
-        <v>3.9073999732369864E-3</v>
+        <v>3.3540861671628305E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31115,7 +31256,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="154">
         <f ca="1">-AC62/AC151</f>
-        <v>3.4030555978534221E-4</v>
+        <v>2.9211603073719738E-4</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31152,7 +31293,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="154">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>3.9221657737971644E-3</v>
+        <v>3.3667610322253255E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31402,35 +31543,35 @@
         <v>4.183098591549296</v>
       </c>
       <c r="T170" s="72">
-        <f t="shared" ref="T170:AA170" si="99">T105/T74</f>
+        <f t="shared" ref="T170:AA170" si="101">T105/T74</f>
         <v>6.4666666666666668</v>
       </c>
       <c r="U170" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>5.8443396226415096</v>
       </c>
       <c r="V170" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>5.8396226415094343</v>
       </c>
       <c r="W170" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>3.8396226415094339</v>
       </c>
       <c r="X170" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>4.183098591549296</v>
       </c>
       <c r="Y170" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>5.1962616822429908</v>
       </c>
       <c r="Z170" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>4.7981651376146788</v>
       </c>
       <c r="AA170" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>5.1160714285714288</v>
       </c>
       <c r="AC170" s="72">
@@ -31463,35 +31604,35 @@
         <v>0.18467220683287167</v>
       </c>
       <c r="T171" s="154" t="e">
-        <f t="shared" ref="T171:AA171" si="100">T53/T58</f>
+        <f t="shared" ref="T171:AA171" si="102">T53/T58</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U171" s="154">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0.4</v>
       </c>
       <c r="V171" s="154">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0.22171945701357465</v>
       </c>
       <c r="W171" s="154">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0.20849420849420849</v>
       </c>
       <c r="X171" s="154">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0.11614173228346457</v>
       </c>
       <c r="Y171" s="154">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>9.7744360902255634E-2</v>
       </c>
       <c r="Z171" s="154">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>7.3305670816044263E-2</v>
       </c>
       <c r="AA171" s="154">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>4.8473967684021541E-2</v>
       </c>
       <c r="AC171" s="154">
@@ -31524,35 +31665,35 @@
         <v>2.1985269869187644E-2</v>
       </c>
       <c r="T172" s="154">
-        <f t="shared" ref="T172:AA172" si="101">T53/T5</f>
+        <f t="shared" ref="T172:AA172" si="103">T53/T5</f>
         <v>0</v>
       </c>
       <c r="U172" s="154">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>1.7527675276752766E-2</v>
       </c>
       <c r="V172" s="154">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>2.1075268817204302E-2</v>
       </c>
       <c r="W172" s="154">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="X172" s="154">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>2.4140752864157119E-2</v>
       </c>
       <c r="Y172" s="154">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>1.9779383796120199E-2</v>
       </c>
       <c r="Z172" s="154">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>1.8761061946902656E-2</v>
       </c>
       <c r="AA172" s="154">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>1.7352185089974295E-2</v>
       </c>
       <c r="AC172" s="154">
@@ -31585,35 +31726,35 @@
         <v>-19.267605633802816</v>
       </c>
       <c r="T173" s="72">
-        <f t="shared" ref="T173:AA173" si="102">(T105-T106)/T74</f>
+        <f t="shared" ref="T173:AA173" si="104">(T105-T106)/T74</f>
         <v>-20.552380952380954</v>
       </c>
       <c r="U173" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-20.929245283018869</v>
       </c>
       <c r="V173" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-20.94811320754717</v>
       </c>
       <c r="W173" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-20.433962264150942</v>
       </c>
       <c r="X173" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-19.267605633802816</v>
       </c>
       <c r="Y173" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-18.140186915887849</v>
       </c>
       <c r="Z173" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-15.839449541284404</v>
       </c>
       <c r="AA173" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-12.129464285714286</v>
       </c>
       <c r="AC173" s="72">
@@ -31655,7 +31796,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="154">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-1.56713594226572E-2</v>
+        <v>-1.345219077140619E-2</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -31683,35 +31824,35 @@
         <v>2.9130482576673628E-2</v>
       </c>
       <c r="T175" s="154">
-        <f t="shared" ref="T175:AA175" si="103">-T108/T5</f>
+        <f t="shared" ref="T175:AA175" si="105">-T108/T5</f>
         <v>0</v>
       </c>
       <c r="U175" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>3.136531365313653E-2</v>
       </c>
       <c r="V175" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>3.053763440860215E-2</v>
       </c>
       <c r="W175" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>1.9907407407407408E-2</v>
       </c>
       <c r="X175" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>3.3960720130932896E-2</v>
       </c>
       <c r="Y175" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>3.9939140357550397E-2</v>
       </c>
       <c r="Z175" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>4.1061946902654869E-2</v>
       </c>
       <c r="AA175" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>5.1735218508997427E-2</v>
       </c>
       <c r="AC175" s="154">
@@ -31744,35 +31885,35 @@
         <v>0.24469067405355494</v>
       </c>
       <c r="T176" s="154" t="e">
-        <f t="shared" ref="T176:AA176" si="104">-(T108/T58)</f>
+        <f t="shared" ref="T176:AA176" si="106">-(T108/T58)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U176" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.71578947368421053</v>
       </c>
       <c r="V176" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.32126696832579188</v>
       </c>
       <c r="W176" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.16602316602316602</v>
       </c>
       <c r="X176" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.16338582677165353</v>
       </c>
       <c r="Y176" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.19736842105263158</v>
       </c>
       <c r="Z176" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.16044260027662519</v>
       </c>
       <c r="AA176" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.14452423698384201</v>
       </c>
       <c r="AC176" s="154">
@@ -31805,35 +31946,35 @@
         <v>1.0557768924302788</v>
       </c>
       <c r="T177" s="154" t="e">
-        <f t="shared" ref="T177:AA177" si="105">-T108/T52</f>
+        <f t="shared" ref="T177:AA177" si="107">-T108/T52</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>1.0625</v>
       </c>
       <c r="V177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>1.126984126984127</v>
       </c>
       <c r="W177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.68253968253968256</v>
       </c>
       <c r="X177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>1.360655737704918</v>
       </c>
       <c r="Y177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>1.4583333333333333</v>
       </c>
       <c r="Z177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>1.7058823529411764</v>
       </c>
       <c r="AA177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>2.4393939393939394</v>
       </c>
       <c r="AC177" s="154">
@@ -32115,7 +32256,7 @@
         <v>612</v>
       </c>
       <c r="AC186" s="62">
-        <f t="shared" ref="AC186" si="106">SUM(X186:AA186)</f>
+        <f t="shared" ref="AC186" si="108">SUM(X186:AA186)</f>
         <v>2309</v>
       </c>
     </row>
@@ -32181,61 +32322,61 @@
       <c r="K190" s="81"/>
       <c r="L190" s="81"/>
       <c r="M190" s="81">
-        <f t="shared" ref="M190:Q191" si="107">IF(L185=0,
+        <f t="shared" ref="M190:Q191" si="109">IF(L185=0,
 IF(M185=0,0,IF(M185&gt;0,1,-1)),
 (M185-L185)/ABS(L185)
 )</f>
         <v>0</v>
       </c>
       <c r="N190" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="O190" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="P190" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Q190" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>1</v>
       </c>
       <c r="T190" s="81">
-        <f t="shared" ref="T190:AA191" si="108">IF(S185=0,
+        <f t="shared" ref="T190:AA191" si="110">IF(S185=0,
 IF(T185=0,0,IF(T185&gt;0,1,-1)),
 (T185-S185)/ABS(S185)
 )</f>
         <v>0</v>
       </c>
       <c r="U190" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>1</v>
       </c>
       <c r="V190" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>9.7345132743362831E-2</v>
       </c>
       <c r="W190" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>-6.9700460829493091E-2</v>
       </c>
       <c r="X190" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.15356037151702787</v>
       </c>
       <c r="Y190" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.13472893183038109</v>
       </c>
       <c r="Z190" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>5.2034058656575212E-2</v>
       </c>
       <c r="AA190" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.12410071942446044</v>
       </c>
       <c r="AC190" s="49"/>
@@ -32246,55 +32387,55 @@
         <v>Edge &amp; IoT</v>
       </c>
       <c r="M191" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="N191" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="O191" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="P191" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Q191" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>1</v>
       </c>
       <c r="T191" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="U191" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>1</v>
       </c>
       <c r="V191" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>6.8376068376068376E-3</v>
       </c>
       <c r="W191" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>-7.4702886247877756E-2</v>
       </c>
       <c r="X191" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>6.6055045871559637E-2</v>
       </c>
       <c r="Y191" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>-0.11359724612736662</v>
       </c>
       <c r="Z191" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.16699029126213591</v>
       </c>
       <c r="AA191" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>1.8302828618968387E-2</v>
       </c>
       <c r="AC191" s="49"/>
@@ -32647,7 +32788,7 @@
         <v>175.4</v>
       </c>
       <c r="AC206" s="62">
-        <f t="shared" ref="AC206:AC207" si="109">SUM(X206:AA206)</f>
+        <f t="shared" ref="AC206:AC207" si="111">SUM(X206:AA206)</f>
         <v>636.4</v>
       </c>
     </row>
@@ -32705,7 +32846,7 @@
         <v>24</v>
       </c>
       <c r="AC207" s="62">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>97</v>
       </c>
     </row>
@@ -32751,19 +32892,19 @@
       <c r="K209" s="62"/>
       <c r="L209" s="62"/>
       <c r="M209" s="63" t="e">
-        <f t="shared" ref="M209:P209" si="110">M185/M206</f>
+        <f t="shared" ref="M209:P209" si="112">M185/M206</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N209" s="63" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O209" s="63" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P209" s="63" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q209" s="63">
@@ -32771,39 +32912,39 @@
         <v>13.685058397100281</v>
       </c>
       <c r="T209" s="63">
-        <f t="shared" ref="T209:AC209" si="111">T185/T206</f>
+        <f t="shared" ref="T209:AC209" si="113">T185/T206</f>
         <v>0</v>
       </c>
       <c r="U209" s="63">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>13.87719298245614</v>
       </c>
       <c r="V209" s="63">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>13.777777777777779</v>
       </c>
       <c r="W209" s="63">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>13.503344481605351</v>
       </c>
       <c r="X209" s="63">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>13.598540145985401</v>
       </c>
       <c r="Y209" s="63">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>13.29559748427673</v>
       </c>
       <c r="Z209" s="63">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>13.478787878787879</v>
       </c>
       <c r="AA209" s="63">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>14.253135689851767</v>
       </c>
       <c r="AC209" s="63">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>13.672218730358265</v>
       </c>
     </row>
@@ -32904,7 +33045,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>747.3</v>
+        <v>870.57989999999995</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -32920,7 +33061,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>173373.59999999998</v>
+        <v>201974.5368</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32940,7 +33081,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>176090.59999999998</v>
+        <v>204691.5368</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -32960,7 +33101,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>70.901328273244786</v>
+        <v>82.597713472485765</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -32980,7 +33121,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>15.28876702997275</v>
+        <v>17.810910306539508</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -33000,7 +33141,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>152.87232876712329</v>
+        <v>178.0912306849315</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33020,7 +33161,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>15.993696639418708</v>
+        <v>18.591420236148956</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33029,7 +33170,7 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>56.748501450209467</v>
+        <v>65.965690235256204</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33265,7 +33406,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>1.4104108122574602E-2</v>
+        <v>1.210687267188227E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -33281,7 +33422,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC159</f>
-        <v>1.2654752511339675E-2</v>
+        <v>1.0862755448091711E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -33297,7 +33438,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>3.9073999732369864E-3</v>
+        <v>3.3540861671628305E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>277</v>
@@ -33313,7 +33454,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>3.4030555978534221E-4</v>
+        <v>2.9211603073719738E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33322,7 +33463,7 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>3.9221657737971644E-3</v>
+        <v>3.3667610322253255E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33366,7 +33507,7 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC174</f>
-        <v>-1.56713594226572E-2</v>
+        <v>-1.345219077140619E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33545,7 +33686,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC114</f>
-        <v>747.3</v>
+        <v>870.57989999999995</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33574,7 +33715,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>173373.59999999998</v>
+        <v>201974.5368</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33603,7 +33744,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>176090.59999999998</v>
+        <v>204691.5368</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33632,7 +33773,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>70.901328273244786</v>
+        <v>82.597713472485765</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33661,7 +33802,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>15.28876702997275</v>
+        <v>17.810910306539508</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33690,7 +33831,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>152.87232876712329</v>
+        <v>178.0912306849315</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33719,7 +33860,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>15.993696639418708</v>
+        <v>18.591420236148956</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33748,7 +33889,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>56.748501450209467</v>
+        <v>65.965690235256204</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34521,7 +34662,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>1.4104108122574602E-2</v>
+        <v>1.210687267188227E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34550,7 +34691,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC159</f>
-        <v>1.2654752511339675E-2</v>
+        <v>1.0862755448091711E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34579,7 +34720,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>3.9073999732369864E-3</v>
+        <v>3.3540861671628305E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34608,7 +34749,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>3.4030555978534221E-4</v>
+        <v>2.9211603073719738E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34637,7 +34778,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>3.9221657737971644E-3</v>
+        <v>3.3667610322253255E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34873,7 +35014,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC174</f>
-        <v>-1.56713594226572E-2</v>
+        <v>-1.345219077140619E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB67C1B-6CD6-394D-A84B-01824F4B75CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1B533A-3FBF-154A-99D7-92867F4A52DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,28 +148,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -179,21 +158,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2406,6 +2376,9 @@
     <xf numFmtId="37" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="171" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2415,15 +2388,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2431,6 +2395,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12626,7 +12596,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a23rjc&amp;q=XNAS%3aSTX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12645,9 +12615,11 @@
     <v>Powered by Refinitiv</v>
     <v>1145</v>
     <v>144.75</v>
-    <v>2.1261000000000001</v>
-    <v>18.899899999999999</v>
-    <v>2.2191000000000002E-2</v>
+    <v>2.0874999999999999</v>
+    <v>4.45</v>
+    <v>5.2249999999999996E-3</v>
+    <v>-8.1</v>
+    <v>-9.4610000000000007E-3</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12658,46 +12630,32 @@
     <v>921.77549999999997</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46234.70431959453</v>
+    <v>46234.999919501563</v>
     <v>0</v>
     <v>837.72839999999997</v>
-    <v>197621637300</v>
+    <v>194341510000</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
-    <v>900.44</v>
-    <v>62.614100000000001</v>
+    <v>901.68</v>
+    <v>61.254600000000003</v>
     <v>851.68</v>
-    <v>870.57989999999995</v>
+    <v>856.13</v>
+    <v>848.03</v>
     <v>227000000</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>3232234</v>
+    <v>6130389</v>
     <v>5503992</v>
     <v>2017</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12709,30 +12667,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>47.14</v>
+    <v>47.47</v>
     <v>39.47</v>
-    <v>0.41</v>
-    <v>8.8710000000000004E-3</v>
+    <v>0.82</v>
+    <v>1.7585E-2</v>
     <v>US</v>
-    <v>46.86</v>
+    <v>47.47</v>
     <v>Index</v>
-    <v>6</v>
-    <v>46.51</v>
+    <v>3</v>
+    <v>46.82</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.69</v>
-    <v>46.22</v>
+    <v>46.84</v>
     <v>46.63</v>
+    <v>47.45</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12754,6 +12712,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12774,6 +12734,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12783,11 +12744,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12823,7 +12779,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12834,13 +12790,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12934,13 +12893,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
+      <v>Delayed 15 minutes</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13012,6 +12977,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13019,6 +12987,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13509,18 +13480,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="243" t="s">
+      <c r="B2" s="244" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="244"/>
-      <c r="E2" s="243" t="s">
+      <c r="C2" s="245"/>
+      <c r="E2" s="244" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="244"/>
-      <c r="H2" s="243" t="s">
+      <c r="F2" s="245"/>
+      <c r="H2" s="244" t="s">
         <v>332</v>
       </c>
-      <c r="I2" s="244"/>
+      <c r="I2" s="245"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13535,7 +13506,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC151</f>
-        <v>201974.5368</v>
+        <v>198622.16</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13543,7 +13514,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>105.64014591596252</v>
+        <v>106.41659493050551</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13559,7 +13530,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC152</f>
-        <v>204691.5368</v>
+        <v>201339.16</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13567,7 +13538,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>90.361973679717593</v>
+        <v>90.851193321856215</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13576,7 +13547,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>870.57989999999995</v>
+        <v>856.13</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>247</v>
@@ -13591,23 +13562,23 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>89.895169309350294</v>
+        <v>90.25686256777162</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="208" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>848.03</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC148</f>
-        <v>82.597713472485765</v>
+        <v>81.226755218216326</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13615,7 +13586,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>106.66810579871586</v>
+        <v>107.22393441909092</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13624,14 +13595,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>18.899899999999999</v>
+        <v>4.45</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC149</f>
-        <v>17.810910306539508</v>
+        <v>17.515284514078111</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13639,23 +13610,23 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>98.14134867593657</v>
+        <v>98.687146309806067</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-8.1</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC159</f>
-        <v>1.0862755448091711E-2</v>
+        <v>1.1046098783740948E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13663,7 +13634,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.88726899314360852</v>
+        <v>-0.88472878381810471</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13672,37 +13643,37 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.2191000000000002E-2</v>
+        <v>5.2249999999999996E-3</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC160</f>
-        <v>1.210687267188227E-2</v>
+        <v>1.231121441837104E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-9.4610000000000007E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>2.9211603073719738E-4</v>
+        <v>2.9704641214253232E-4</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>372</v>
       </c>
       <c r="I10" s="212">
         <f ca="1">DDM!C26</f>
-        <v>24.08578588686434</v>
+        <v>24.267737617135207</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13718,7 +13689,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC161</f>
-        <v>3.3540861671628305E-3</v>
+        <v>3.4106969735904595E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13743,7 +13714,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1261000000000001</v>
+        <v>2.0874999999999999</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>103</v>
@@ -13775,7 +13746,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-1.345219077140619E-2</v>
+        <v>-1.3679239013411192E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13788,10 +13759,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="245" t="s">
+      <c r="B17" s="246" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="245"/>
+      <c r="C17" s="246"/>
       <c r="E17" s="184" t="s">
         <v>300</v>
       </c>
@@ -13864,14 +13835,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="245" t="s">
+      <c r="B25" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="245"/>
-      <c r="E25" s="243" t="s">
+      <c r="C25" s="246"/>
+      <c r="E25" s="244" t="s">
         <v>345</v>
       </c>
-      <c r="F25" s="244"/>
+      <c r="F25" s="245"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -13880,12 +13851,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="5">
+      <c r="E26" s="185" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>46.63</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13900,7 +13871,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.6630000000000005E-2</v>
+        <v>4.7450000000000006E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13920,15 +13891,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="246" t="s">
+      <c r="B33" s="243" t="s">
         <v>340</v>
       </c>
-      <c r="C33" s="246"/>
-      <c r="D33" s="246"/>
-      <c r="E33" s="246"/>
-      <c r="F33" s="246"/>
-      <c r="G33" s="246"/>
-      <c r="H33" s="246"/>
+      <c r="C33" s="243"/>
+      <c r="D33" s="243"/>
+      <c r="E33" s="243"/>
+      <c r="F33" s="243"/>
+      <c r="G33" s="243"/>
+      <c r="H33" s="243"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14013,24 +13984,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="246"/>
-      <c r="C49" s="246"/>
-      <c r="D49" s="246"/>
-      <c r="E49" s="246"/>
-      <c r="F49" s="246"/>
-      <c r="G49" s="246"/>
-      <c r="H49" s="246"/>
+      <c r="B49" s="243"/>
+      <c r="C49" s="243"/>
+      <c r="D49" s="243"/>
+      <c r="E49" s="243"/>
+      <c r="F49" s="243"/>
+      <c r="G49" s="243"/>
+      <c r="H49" s="243"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="246" t="s">
+      <c r="B52" s="243" t="s">
         <v>343</v>
       </c>
-      <c r="C52" s="246"/>
-      <c r="D52" s="246"/>
-      <c r="E52" s="246"/>
-      <c r="F52" s="246"/>
-      <c r="G52" s="246"/>
-      <c r="H52" s="246"/>
+      <c r="C52" s="243"/>
+      <c r="D52" s="243"/>
+      <c r="E52" s="243"/>
+      <c r="F52" s="243"/>
+      <c r="G52" s="243"/>
+      <c r="H52" s="243"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14069,24 +14040,24 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="246"/>
-      <c r="C59" s="246"/>
-      <c r="D59" s="246"/>
-      <c r="E59" s="246"/>
-      <c r="F59" s="246"/>
-      <c r="G59" s="246"/>
-      <c r="H59" s="246"/>
+      <c r="B59" s="243"/>
+      <c r="C59" s="243"/>
+      <c r="D59" s="243"/>
+      <c r="E59" s="243"/>
+      <c r="F59" s="243"/>
+      <c r="G59" s="243"/>
+      <c r="H59" s="243"/>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B62" s="246" t="s">
+      <c r="B62" s="243" t="s">
         <v>108</v>
       </c>
-      <c r="C62" s="246"/>
-      <c r="D62" s="246"/>
-      <c r="E62" s="246"/>
-      <c r="F62" s="246"/>
-      <c r="G62" s="246"/>
-      <c r="H62" s="246"/>
+      <c r="C62" s="243"/>
+      <c r="D62" s="243"/>
+      <c r="E62" s="243"/>
+      <c r="F62" s="243"/>
+      <c r="G62" s="243"/>
+      <c r="H62" s="243"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B64" s="41" t="s">
@@ -14101,28 +14072,28 @@
       </c>
     </row>
     <row r="69" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="246"/>
-      <c r="C69" s="246"/>
-      <c r="D69" s="246"/>
-      <c r="E69" s="246"/>
-      <c r="F69" s="246"/>
-      <c r="G69" s="246"/>
-      <c r="H69" s="246"/>
+      <c r="B69" s="243"/>
+      <c r="C69" s="243"/>
+      <c r="D69" s="243"/>
+      <c r="E69" s="243"/>
+      <c r="F69" s="243"/>
+      <c r="G69" s="243"/>
+      <c r="H69" s="243"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B62:H62"/>
     <mergeCell ref="B69:H69"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B49:H49"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14192,36 +14163,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="255"/>
       <c r="H2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="246" t="s">
+      <c r="S2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="246"/>
-      <c r="U2" s="246"/>
-      <c r="V2" s="246"/>
-      <c r="W2" s="246"/>
-      <c r="X2" s="246"/>
-      <c r="Y2" s="246"/>
-      <c r="Z2" s="246"/>
-      <c r="AA2" s="246" t="s">
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
+      <c r="AA2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="246"/>
-      <c r="AC2" s="246"/>
+      <c r="AB2" s="243"/>
+      <c r="AC2" s="243"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -15544,35 +15515,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="255"/>
       <c r="H2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
-      <c r="P2" s="246" t="s">
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="P2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="246"/>
-      <c r="R2" s="246"/>
-      <c r="S2" s="246"/>
-      <c r="T2" s="246"/>
-      <c r="U2" s="246"/>
-      <c r="V2" s="246"/>
-      <c r="W2" s="246"/>
-      <c r="X2" s="246" t="s">
+      <c r="Q2" s="243"/>
+      <c r="R2" s="243"/>
+      <c r="S2" s="243"/>
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="246"/>
-      <c r="Z2" s="246"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -16804,20 +16775,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="E3" s="246"/>
-      <c r="F3" s="246"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
       <c r="G3" s="255"/>
       <c r="H3" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="246"/>
-      <c r="J3" s="246"/>
-      <c r="K3" s="246"/>
-      <c r="L3" s="246"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="257"/>
       <c r="Q3" s="257"/>
       <c r="R3" s="257"/>
@@ -18210,12 +18181,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18223,6 +18188,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18260,20 +18231,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="255"/>
       <c r="H2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
       <c r="S2" s="257"/>
       <c r="T2" s="257"/>
       <c r="U2" s="257"/>
@@ -19282,16 +19253,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19354,10 +19325,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="246" t="s">
+      <c r="B4" s="243" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="246"/>
+      <c r="C4" s="243"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19374,7 +19345,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>870.57989999999995</v>
+        <v>856.13</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19383,7 +19354,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>201974.5368</v>
+        <v>198622.16</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19401,7 +19372,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.6630000000000005E-2</v>
+        <v>4.7450000000000006E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19410,7 +19381,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1261000000000001</v>
+        <v>2.0874999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19442,10 +19413,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="246" t="s">
+      <c r="B15" s="243" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="246"/>
+      <c r="C15" s="243"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19453,7 +19424,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.8767228077323162E-2</v>
+        <v>1.9077941316785883E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19462,7 +19433,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.98123277192267688</v>
+        <v>0.98092205868321414</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19480,7 +19451,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1423045</v>
+        <v>0.1413875</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19489,7 +19460,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14049375338257353</v>
+        <v>0.13956426884320808</v>
       </c>
     </row>
   </sheetData>
@@ -19534,20 +19505,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="E3" s="246"/>
-      <c r="F3" s="246"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
       <c r="G3" s="255"/>
       <c r="H3" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="246"/>
-      <c r="J3" s="246"/>
-      <c r="K3" s="246"/>
-      <c r="L3" s="246"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="257"/>
       <c r="Q3" s="257"/>
       <c r="R3" s="257"/>
@@ -19740,7 +19711,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>24633.468568334494</v>
+        <v>24817.280735321412</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19794,23 +19765,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>2990.82541303774</v>
+        <v>2993.2648770130199</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3676.9483190385477</v>
+        <v>3682.9489642261419</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3479.4354712418976</v>
+        <v>3487.9564125108141</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>2733.7231627514634</v>
+        <v>2742.6531159431652</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>1578.400027265104</v>
+        <v>1584.8476392614548</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -19829,14 +19800,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>12766.181459168549</v>
+        <v>12913.979014922683</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="246" t="s">
+      <c r="B13" s="243" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="246"/>
+      <c r="C13" s="243"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19852,14 +19823,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14049375338257353</v>
+        <v>0.13956426884320808</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="246" t="s">
+      <c r="B18" s="243" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="246"/>
+      <c r="C18" s="243"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19867,7 +19838,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>14459.332393334753</v>
+        <v>14491.671008954596</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -19876,7 +19847,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>12766.181459168549</v>
+        <v>12913.979014922683</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -19885,7 +19856,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>27225.513852503303</v>
+        <v>27405.650023877279</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -19912,7 +19883,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>24508.513852503303</v>
+        <v>24688.650023877279</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -19930,7 +19901,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>105.64014591596252</v>
+        <v>106.41659493050551</v>
       </c>
     </row>
   </sheetData>
@@ -19973,20 +19944,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="255"/>
       <c r="H2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20918,10 +20889,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="246" t="s">
+      <c r="B37" s="243" t="s">
         <v>204</v>
       </c>
-      <c r="C37" s="246"/>
+      <c r="C37" s="243"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -20939,7 +20910,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14049375338257353</v>
+        <v>0.13956426884320808</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -20965,7 +20936,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>23680.977893694482</v>
+        <v>23794.476850670642</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -20992,7 +20963,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>20963.977893694482</v>
+        <v>21077.476850670642</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21010,14 +20981,14 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>90.361973679717593</v>
+        <v>90.851193321856215</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="246" t="s">
+      <c r="B49" s="243" t="s">
         <v>209</v>
       </c>
-      <c r="C49" s="246"/>
+      <c r="C49" s="243"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21034,7 +21005,7 @@
       </c>
       <c r="C51" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1423045</v>
+        <v>0.1413875</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21069,14 +21040,14 @@
       </c>
       <c r="C55" s="142">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>89.895169309350294</v>
+        <v>90.25686256777162</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="246" t="s">
+      <c r="B57" s="243" t="s">
         <v>326</v>
       </c>
-      <c r="C57" s="246"/>
+      <c r="C57" s="243"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21093,7 +21064,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14049375338257353</v>
+        <v>0.13956426884320808</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21119,7 +21090,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>27464.000545302079</v>
+        <v>27592.952785229096</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21146,7 +21117,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>24747.000545302079</v>
+        <v>24875.952785229096</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21164,7 +21135,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>106.66810579871586</v>
+        <v>107.22393441909092</v>
       </c>
     </row>
   </sheetData>
@@ -21216,10 +21187,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="246" t="s">
+      <c r="B4" s="243" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="246"/>
+      <c r="C4" s="243"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21228,7 +21199,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>105.64014591596252</v>
+        <v>106.41659493050551</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21237,7 +21208,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>90.361973679717593</v>
+        <v>90.851193321856215</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21246,7 +21217,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C55</f>
-        <v>89.895169309350294</v>
+        <v>90.25686256777162</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21255,7 +21226,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>106.66810579871586</v>
+        <v>107.22393441909092</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21264,7 +21235,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>98.14134867593657</v>
+        <v>98.687146309806067</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21273,7 +21244,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>870.57989999999995</v>
+        <v>856.13</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21282,7 +21253,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.88726899314360852</v>
+        <v>-0.88472878381810471</v>
       </c>
     </row>
   </sheetData>
@@ -21338,20 +21309,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="246" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="255"/>
       <c r="H2" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21714,10 +21685,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="246" t="s">
+      <c r="B20" s="243" t="s">
         <v>377</v>
       </c>
-      <c r="C20" s="246"/>
+      <c r="C20" s="243"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -21752,7 +21723,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1423045</v>
+        <v>0.1413875</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -21769,7 +21740,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C23/(C24-C25)</f>
-        <v>24.08578588686434</v>
+        <v>24.267737617135207</v>
       </c>
     </row>
   </sheetData>
@@ -21818,20 +21789,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="E3" s="246"/>
-      <c r="F3" s="246"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
       <c r="G3" s="255"/>
       <c r="H3" s="256" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="246"/>
-      <c r="J3" s="246"/>
-      <c r="K3" s="246"/>
-      <c r="L3" s="246"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="257"/>
       <c r="Q3" s="257"/>
       <c r="R3" s="257"/>
@@ -22006,7 +21977,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>250008.45423563471</v>
+        <v>251873.98915251502</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22060,23 +22031,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>1693.9393933824952</v>
+        <v>1695.3210534782168</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>2970.5369071219648</v>
+        <v>2975.3847147193678</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>5209.212059797248</v>
+        <v>5221.9691263920258</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>9135.0119969483803</v>
+        <v>9164.8523372761392</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>16019.398562868028</v>
+        <v>16084.836262161052</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22095,7 +22066,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>129565.72819798155</v>
+        <v>131065.74588129696</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22111,7 +22082,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>870.57989999999995</v>
+        <v>856.13</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22120,7 +22091,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>722.66440677723062</v>
+        <v>729.87102399698108</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22159,7 +22130,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14049375338257353</v>
+        <v>0.13956426884320808</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22177,7 +22148,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>195009.8976</v>
+        <v>191773.12</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22204,7 +22175,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>197726.8976</v>
+        <v>194490.12</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22220,7 +22191,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>35028.098920118122</v>
+        <v>35142.363494026802</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22229,7 +22200,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>129565.72819798155</v>
+        <v>131065.74588129696</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22238,7 +22209,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>164593.82711809967</v>
+        <v>166208.10937532375</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22265,7 +22236,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>161876.82711809967</v>
+        <v>163491.10937532375</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22283,7 +22254,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>722.66440677723062</v>
+        <v>729.87102399698108</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -22730,17 +22701,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29265,7 +29236,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>870.57989999999995</v>
+        <v>856.13</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29336,7 +29307,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>870.57989999999995</v>
+        <v>856.13</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30642,7 +30613,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>82.597713472485765</v>
+        <v>81.226755218216326</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -30679,7 +30650,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>17.810910306539508</v>
+        <v>17.515284514078111</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -30740,7 +30711,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>178.0912306849315</v>
+        <v>175.13526940639269</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30801,7 +30772,7 @@
       </c>
       <c r="AC151" s="143">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>201974.5368</v>
+        <v>198622.16</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30862,7 +30833,7 @@
       </c>
       <c r="AC152" s="143">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>204691.5368</v>
+        <v>201339.16</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30899,7 +30870,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="183">
         <f ca="1">AC152/AC5</f>
-        <v>18.591420236148956</v>
+        <v>18.286935513169848</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30936,7 +30907,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="183">
         <f ca="1">AC152/AC11</f>
-        <v>65.965690235256204</v>
+        <v>64.885323880116019</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31071,7 +31042,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="97">AC151/AC155</f>
-        <v>92.057674020054691</v>
+        <v>90.529699179580675</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31108,7 +31079,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="97"/>
-        <v>82.823481721871062</v>
+        <v>81.467023497167247</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31145,7 +31116,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="100">AC155/AC151</f>
-        <v>1.0862755448091711E-2</v>
+        <v>1.1046098783740948E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31182,7 +31153,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.210687267188227E-2</v>
+        <v>1.231121441837104E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31219,7 +31190,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">AC81/AC115</f>
-        <v>3.3540861671628305E-3</v>
+        <v>3.4106969735904595E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31256,7 +31227,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="154">
         <f ca="1">-AC62/AC151</f>
-        <v>2.9211603073719738E-4</v>
+        <v>2.9704641214253232E-4</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31293,7 +31264,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="154">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>3.3667610322253255E-3</v>
+        <v>3.4235857670664744E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31796,7 +31767,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="154">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-1.345219077140619E-2</v>
+        <v>-1.3679239013411192E-2</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33029,15 +33000,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="246" t="s">
+      <c r="B4" s="243" t="s">
         <v>237</v>
       </c>
-      <c r="C4" s="246"/>
-      <c r="E4" s="246" t="s">
+      <c r="C4" s="243"/>
+      <c r="E4" s="243" t="s">
         <v>244</v>
       </c>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33045,7 +33016,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>870.57989999999995</v>
+        <v>856.13</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33061,7 +33032,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>201974.5368</v>
+        <v>198622.16</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33081,7 +33052,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>204691.5368</v>
+        <v>201339.16</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33101,7 +33072,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>82.597713472485765</v>
+        <v>81.226755218216326</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -33121,7 +33092,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>17.810910306539508</v>
+        <v>17.515284514078111</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -33141,7 +33112,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>178.0912306849315</v>
+        <v>175.13526940639269</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33161,7 +33132,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>18.591420236148956</v>
+        <v>18.286935513169848</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33170,18 +33141,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>65.965690235256204</v>
+        <v>64.885323880116019</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="246" t="s">
+      <c r="B15" s="243" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="246"/>
-      <c r="E15" s="246" t="s">
+      <c r="C15" s="243"/>
+      <c r="E15" s="243" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="246"/>
+      <c r="F15" s="243"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33232,14 +33203,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="246" t="s">
+      <c r="B21" s="243" t="s">
         <v>249</v>
       </c>
-      <c r="C21" s="246"/>
-      <c r="E21" s="246" t="s">
+      <c r="C21" s="243"/>
+      <c r="E21" s="243" t="s">
         <v>253</v>
       </c>
-      <c r="F21" s="246"/>
+      <c r="F21" s="243"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33308,14 +33279,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="246" t="s">
+      <c r="B29" s="243" t="s">
         <v>254</v>
       </c>
-      <c r="C29" s="246"/>
-      <c r="E29" s="246" t="s">
+      <c r="C29" s="243"/>
+      <c r="E29" s="243" t="s">
         <v>260</v>
       </c>
-      <c r="F29" s="246"/>
+      <c r="F29" s="243"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33391,14 +33362,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="246" t="s">
+      <c r="B37" s="243" t="s">
         <v>272</v>
       </c>
-      <c r="C37" s="246"/>
-      <c r="E37" s="246" t="s">
+      <c r="C37" s="243"/>
+      <c r="E37" s="243" t="s">
         <v>275</v>
       </c>
-      <c r="F37" s="246"/>
+      <c r="F37" s="243"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33406,7 +33377,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>1.210687267188227E-2</v>
+        <v>1.231121441837104E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -33422,7 +33393,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC159</f>
-        <v>1.0862755448091711E-2</v>
+        <v>1.1046098783740948E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -33438,7 +33409,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>3.3540861671628305E-3</v>
+        <v>3.4106969735904595E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>277</v>
@@ -33454,7 +33425,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>2.9211603073719738E-4</v>
+        <v>2.9704641214253232E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33463,18 +33434,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>3.3667610322253255E-3</v>
+        <v>3.4235857670664744E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="246" t="s">
+      <c r="B45" s="243" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="246"/>
-      <c r="E45" s="246" t="s">
+      <c r="C45" s="243"/>
+      <c r="E45" s="243" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="246"/>
+      <c r="F45" s="243"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33507,18 +33478,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC174</f>
-        <v>-1.345219077140619E-2</v>
+        <v>-1.3679239013411192E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="246" t="s">
+      <c r="B51" s="243" t="s">
         <v>286</v>
       </c>
-      <c r="C51" s="246"/>
-      <c r="E51" s="246" t="s">
+      <c r="C51" s="243"/>
+      <c r="E51" s="243" t="s">
         <v>307</v>
       </c>
-      <c r="F51" s="246"/>
+      <c r="F51" s="243"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33686,7 +33657,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC114</f>
-        <v>870.57989999999995</v>
+        <v>856.13</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33715,7 +33686,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>201974.5368</v>
+        <v>198622.16</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33744,7 +33715,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>204691.5368</v>
+        <v>201339.16</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33773,7 +33744,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>82.597713472485765</v>
+        <v>81.226755218216326</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33802,7 +33773,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>17.810910306539508</v>
+        <v>17.515284514078111</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33831,7 +33802,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>178.0912306849315</v>
+        <v>175.13526940639269</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33860,7 +33831,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>18.591420236148956</v>
+        <v>18.286935513169848</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33889,7 +33860,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>65.965690235256204</v>
+        <v>64.885323880116019</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34662,7 +34633,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>1.210687267188227E-2</v>
+        <v>1.231121441837104E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34691,7 +34662,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC159</f>
-        <v>1.0862755448091711E-2</v>
+        <v>1.1046098783740948E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34720,7 +34691,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>3.3540861671628305E-3</v>
+        <v>3.4106969735904595E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34749,7 +34720,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>2.9211603073719738E-4</v>
+        <v>2.9704641214253232E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34778,7 +34749,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>3.3667610322253255E-3</v>
+        <v>3.4235857670664744E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35014,7 +34985,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC174</f>
-        <v>-1.345219077140619E-2</v>
+        <v>-1.3679239013411192E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35476,14 +35447,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="247" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="250"/>
-      <c r="F3" s="251" t="s">
+      <c r="D3" s="248"/>
+      <c r="F3" s="249" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="250"/>
+      <c r="G3" s="248"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35550,19 +35521,19 @@
       <c r="B7" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="247">
+      <c r="C7" s="250">
         <f>Statement!AA88</f>
         <v>0.10159292035398231</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="F7" s="247">
+      <c r="D7" s="251"/>
+      <c r="F7" s="250">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.44074074074074077</v>
       </c>
-      <c r="G7" s="248"/>
+      <c r="G7" s="251"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -35589,19 +35560,19 @@
       <c r="B9" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="247">
+      <c r="C9" s="250">
         <f>Statement!AA89</f>
         <v>9.7028502122498486E-3</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="F9" s="247">
+      <c r="D9" s="251"/>
+      <c r="F9" s="250">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.18928571428571428</v>
       </c>
-      <c r="G9" s="248"/>
+      <c r="G9" s="251"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -35628,19 +35599,19 @@
       <c r="B11" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="247">
+      <c r="C11" s="250">
         <f>Statement!AA90</f>
         <v>0.23044217687074831</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="F11" s="247">
+      <c r="D11" s="251"/>
+      <c r="F11" s="250">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.90394736842105261</v>
       </c>
-      <c r="G11" s="248"/>
+      <c r="G11" s="251"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -35667,19 +35638,19 @@
       <c r="B13" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="247">
+      <c r="C13" s="250">
         <f>Statement!AA93</f>
         <v>0.34834834834834832</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="F13" s="247">
+      <c r="D13" s="251"/>
+      <c r="F13" s="250">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.36474164133738601</v>
       </c>
-      <c r="G13" s="248"/>
+      <c r="G13" s="251"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -35706,19 +35677,19 @@
       <c r="B15" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="247">
+      <c r="C15" s="250">
         <f>Statement!AA94</f>
         <v>0.18386714116251482</v>
       </c>
-      <c r="D15" s="248"/>
-      <c r="F15" s="247">
+      <c r="D15" s="251"/>
+      <c r="F15" s="250">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.3155452436194897</v>
       </c>
-      <c r="G15" s="248"/>
+      <c r="G15" s="251"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -35745,19 +35716,19 @@
       <c r="B17" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="247">
+      <c r="C17" s="250">
         <f>Statement!AA96</f>
         <v>0.26138279932546377</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="F17" s="247">
+      <c r="D17" s="251"/>
+      <c r="F17" s="250">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2</v>
       </c>
-      <c r="G17" s="248"/>
+      <c r="G17" s="251"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -35784,22 +35755,22 @@
       <c r="B19" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="247">
+      <c r="C19" s="250">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.3859649122807015E-3</v>
       </c>
-      <c r="D19" s="248"/>
-      <c r="F19" s="247">
+      <c r="D19" s="251"/>
+      <c r="F19" s="250">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>6.0185185185185182E-2</v>
       </c>
-      <c r="G19" s="248"/>
+      <c r="G19" s="251"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -35826,22 +35797,22 @@
       <c r="B21" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="247">
+      <c r="C21" s="250">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.25769230769230766</v>
       </c>
-      <c r="D21" s="248"/>
-      <c r="F21" s="247">
+      <c r="D21" s="251"/>
+      <c r="F21" s="250">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.0828025477707006</v>
       </c>
-      <c r="G21" s="248"/>
+      <c r="G21" s="251"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35890,22 +35861,22 @@
       <c r="B25" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="247">
+      <c r="C25" s="250">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.12410071942446044</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="F25" s="247">
+      <c r="D25" s="251"/>
+      <c r="F25" s="250">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.54798761609907121</v>
       </c>
-      <c r="G25" s="248"/>
+      <c r="G25" s="251"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -35933,37 +35904,25 @@
       <c r="B27" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="247">
+      <c r="C27" s="250">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>1.8302828618968387E-2</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="F27" s="247">
+      <c r="D27" s="251"/>
+      <c r="F27" s="250">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.12293577981651377</v>
       </c>
-      <c r="G27" s="248"/>
+      <c r="G27" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
@@ -35974,6 +35933,18 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
